--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-02_v3_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-02_v3_final.xlsx
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <f>SUM('SO_260217_Sklad'!I34:I106)</f>
+        <f>SUM('SO_260217_Sklad'!I34:I110)</f>
         <v/>
       </c>
       <c r="E15" s="7">
@@ -15954,7 +15954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L107"/>
+  <dimension ref="B2:L111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -16115,7 +16115,7 @@
         </is>
       </c>
       <c r="D16" s="7">
-        <f>SUMIFS(I32:I107,L32:L107,C16)</f>
+        <f>SUMIFS(I32:I111,L32:L111,C16)</f>
         <v/>
       </c>
     </row>
@@ -16127,7 +16127,7 @@
         </is>
       </c>
       <c r="D17" s="7">
-        <f>SUMIFS(I32:I107,L32:L107,C17)</f>
+        <f>SUMIFS(I32:I111,L32:L111,C17)</f>
         <v/>
       </c>
     </row>
@@ -16139,7 +16139,7 @@
         </is>
       </c>
       <c r="D18" s="7">
-        <f>SUMIFS(I32:I107,L32:L107,C18)</f>
+        <f>SUMIFS(I32:I111,L32:L111,C18)</f>
         <v/>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
         </is>
       </c>
       <c r="D19" s="7">
-        <f>SUMIFS(I32:I107,L32:L107,C19)</f>
+        <f>SUMIFS(I32:I111,L32:L111,C19)</f>
         <v/>
       </c>
     </row>
@@ -16163,7 +16163,7 @@
         </is>
       </c>
       <c r="D20" s="7">
-        <f>SUMIFS(I32:I107,L32:L107,C20)</f>
+        <f>SUMIFS(I32:I111,L32:L111,C20)</f>
         <v/>
       </c>
     </row>
@@ -16175,7 +16175,7 @@
         </is>
       </c>
       <c r="D21" s="7">
-        <f>SUMIFS(I32:I107,L32:L107,C21)</f>
+        <f>SUMIFS(I32:I111,L32:L111,C21)</f>
         <v/>
       </c>
     </row>
@@ -16187,7 +16187,7 @@
         </is>
       </c>
       <c r="D22" s="7">
-        <f>SUMIFS(I32:I107,L32:L107,C22)</f>
+        <f>SUMIFS(I32:I111,L32:L111,C22)</f>
         <v/>
       </c>
     </row>
@@ -16199,7 +16199,7 @@
         </is>
       </c>
       <c r="D23" s="7">
-        <f>SUMIFS(I32:I107,L32:L107,C23)</f>
+        <f>SUMIFS(I32:I111,L32:L111,C23)</f>
         <v/>
       </c>
     </row>
@@ -16211,7 +16211,7 @@
         </is>
       </c>
       <c r="D24" s="7">
-        <f>SUMIFS(I32:I107,L32:L107,C24)</f>
+        <f>SUMIFS(I32:I111,L32:L111,C24)</f>
         <v/>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
         </is>
       </c>
       <c r="D25" s="7">
-        <f>SUMIFS(I32:I107,L32:L107,C25)</f>
+        <f>SUMIFS(I32:I111,L32:L111,C25)</f>
         <v/>
       </c>
     </row>
@@ -16235,7 +16235,7 @@
         </is>
       </c>
       <c r="D26" s="7">
-        <f>SUMIFS(I32:I107,L32:L107,C26)</f>
+        <f>SUMIFS(I32:I111,L32:L111,C26)</f>
         <v/>
       </c>
     </row>
@@ -16674,7 +16674,7 @@
         </is>
       </c>
       <c r="G42" s="25" t="n">
-        <v>2.64</v>
+        <v>3.54</v>
       </c>
       <c r="H42" s="26" t="n"/>
       <c r="I42" s="26">
@@ -16707,12 +16707,12 @@
       <c r="D43" s="17" t="n"/>
       <c r="E43" s="29" t="inlineStr">
         <is>
-          <t>podlaha sklad 17.6 m² (legenda místností) × 0.15 m podkladní kamenná drť</t>
+          <t>S01 plocha 23.6 m² (místnost 17.6 + vynos za stěnu 6.0 dle řezu) × 0.15 m podkladní drť 4-8 = 3.54 m³</t>
         </is>
       </c>
       <c r="F43" s="17" t="n"/>
       <c r="G43" s="30" t="n">
-        <v>2.64</v>
+        <v>3.54</v>
       </c>
       <c r="H43" s="17" t="n"/>
       <c r="I43" s="17" t="n"/>
@@ -16787,167 +16787,171 @@
       <c r="L45" s="17" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="21" t="n"/>
-      <c r="C46" s="22" t="inlineStr">
+      <c r="B46" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>564231111</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>Kladecí lože z kamenné drti 4-8 mm tl. 40 mm pod betonovou dlažbu skladu</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G46" s="25" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H46" s="26" t="n"/>
+      <c r="I46" s="26">
+        <f>IF(H46="",0,G46*H46)</f>
+        <v/>
+      </c>
+      <c r="J46" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K46" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="29" t="inlineStr">
+        <is>
+          <t>S01 plocha 23.6 m² × 0.04 m = 0.94 m³</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="n"/>
+      <c r="G47" s="30" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H47" s="17" t="n"/>
+      <c r="I47" s="17" t="n"/>
+      <c r="J47" s="17" t="n"/>
+      <c r="K47" s="17" t="n"/>
+      <c r="L47" s="17" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C48" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>174101101</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>Zásyp za prefabrikovanou opěrnou stěnou S04 — materiál dle PD (NEuveden v legendě, OVĚŘIT)</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G48" s="25" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H48" s="26" t="n"/>
+      <c r="I48" s="26">
+        <f>IF(H48="",0,G48*H48)</f>
+        <v/>
+      </c>
+      <c r="J48" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K48" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="29" t="inlineStr">
+        <is>
+          <t>průřez zásypu 3.61 m² (řez A-A) × délka 6.5 m = 23.5 m³</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="n"/>
+      <c r="G49" s="30" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H49" s="17" t="n"/>
+      <c r="I49" s="17" t="n"/>
+      <c r="J49" s="17" t="n"/>
+      <c r="K49" s="17" t="n"/>
+      <c r="L49" s="17" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="21" t="n"/>
+      <c r="C50" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D46" s="22" t="inlineStr">
+      <c r="D50" s="22" t="inlineStr">
         <is>
           <t>HSV-2</t>
         </is>
       </c>
-      <c r="E46" s="22" t="inlineStr">
+      <c r="E50" s="22" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="F46" s="21" t="n"/>
-      <c r="G46" s="21" t="n"/>
-      <c r="H46" s="21" t="n"/>
-      <c r="I46" s="21" t="n"/>
-      <c r="J46" s="21" t="n"/>
-      <c r="K46" s="21" t="n"/>
-      <c r="L46" s="21" t="n"/>
-    </row>
-    <row r="47">
-      <c r="B47" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="C47" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="inlineStr"/>
-      <c r="E47" s="24" t="inlineStr">
-        <is>
-          <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G47" s="25" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="H47" s="26" t="n"/>
-      <c r="I47" s="26">
-        <f>IF(H47="",0,G47*H47)</f>
-        <v/>
-      </c>
-      <c r="J47" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K47" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="17" t="n"/>
-      <c r="C48" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="n"/>
-      <c r="E48" s="29" t="inlineStr">
-        <is>
-          <t>0.5 × 0.5 × 19.4 obvod = 4.85</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="n"/>
-      <c r="G48" s="30" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="H48" s="17" t="n"/>
-      <c r="I48" s="17" t="n"/>
-      <c r="J48" s="17" t="n"/>
-      <c r="K48" s="17" t="n"/>
-      <c r="L48" s="17" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="C49" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="inlineStr">
-        <is>
-          <t>273313811</t>
-        </is>
-      </c>
-      <c r="E49" s="24" t="inlineStr">
-        <is>
-          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
-        </is>
-      </c>
-      <c r="F49" s="23" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G49" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="H49" s="26" t="n"/>
-      <c r="I49" s="26">
-        <f>IF(H49="",0,G49*H49)</f>
-        <v/>
-      </c>
-      <c r="J49" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K49" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/podminky/cu202/801-1-Budovy-a-haly---z]</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="17" t="n"/>
-      <c r="C50" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="n"/>
-      <c r="E50" s="29" t="inlineStr">
-        <is>
-          <t>6 ks (výkres D.1.1.02 — 6 štvercových patek pod IPE180)</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="n"/>
-      <c r="G50" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="H50" s="17" t="n"/>
-      <c r="I50" s="17" t="n"/>
-      <c r="J50" s="17" t="n"/>
-      <c r="K50" s="17" t="n"/>
-      <c r="L50" s="17" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="21" t="n"/>
+      <c r="H50" s="21" t="n"/>
+      <c r="I50" s="21" t="n"/>
+      <c r="J50" s="21" t="n"/>
+      <c r="K50" s="21" t="n"/>
+      <c r="L50" s="21" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="23" t="n">
@@ -16958,23 +16962,19 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D51" s="24" t="inlineStr">
-        <is>
-          <t>311233812</t>
-        </is>
-      </c>
+      <c r="D51" s="24" t="inlineStr"/>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G51" s="25" t="n">
-        <v>6</v>
+        <v>4.84</v>
       </c>
       <c r="H51" s="26" t="n"/>
       <c r="I51" s="26">
@@ -16986,9 +16986,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K51" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K51" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -17007,12 +17007,12 @@
       <c r="D52" s="17" t="n"/>
       <c r="E52" s="29" t="inlineStr">
         <is>
-          <t>6 ks (= spodní, výkres D.1.1.02)</t>
+          <t>0.5 × 0.5 × 19.4 obvod = 4.85</t>
         </is>
       </c>
       <c r="F52" s="17" t="n"/>
       <c r="G52" s="30" t="n">
-        <v>6</v>
+        <v>4.84</v>
       </c>
       <c r="H52" s="17" t="n"/>
       <c r="I52" s="17" t="n"/>
@@ -17031,21 +17031,21 @@
       </c>
       <c r="D53" s="24" t="inlineStr">
         <is>
-          <t>273321321</t>
+          <t>273313811</t>
         </is>
       </c>
       <c r="E53" s="24" t="inlineStr">
         <is>
-          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
+          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G53" s="25" t="n">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="H53" s="26" t="n"/>
       <c r="I53" s="26">
@@ -17057,9 +17057,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K53" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K53" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/podminky/cu202/801-1-Budovy-a-haly---z]</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -17078,12 +17078,12 @@
       <c r="D54" s="17" t="n"/>
       <c r="E54" s="29" t="inlineStr">
         <is>
-          <t>patky horní (0.3×0.3×0.5×6 = 0.27) + zídka lemující + věnec nad patkami (odhad ~1.5 m³) = ~1.75 m³</t>
+          <t>6 ks (výkres D.1.1.02 — 6 štvercových patek pod IPE180)</t>
         </is>
       </c>
       <c r="F54" s="17" t="n"/>
       <c r="G54" s="30" t="n">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="H54" s="17" t="n"/>
       <c r="I54" s="17" t="n"/>
@@ -17102,21 +17102,21 @@
       </c>
       <c r="D55" s="24" t="inlineStr">
         <is>
-          <t>174101101</t>
+          <t>311233812</t>
         </is>
       </c>
       <c r="E55" s="24" t="inlineStr">
         <is>
-          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
+          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G55" s="25" t="n">
-        <v>1.76</v>
+        <v>6</v>
       </c>
       <c r="H55" s="26" t="n"/>
       <c r="I55" s="26">
@@ -17128,9 +17128,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K55" s="27" t="inlineStr">
-        <is>
-          <t>✓ cross-discipline OK [evidence: https://www.cs-urs.cz/podminky/cu201/800-1-Zemni-prace-(2020]</t>
+      <c r="K55" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -17149,12 +17149,12 @@
       <c r="D56" s="17" t="n"/>
       <c r="E56" s="29" t="inlineStr">
         <is>
-          <t>podlaha sklad 17.6 m² (legenda) × 0.10 m kladecí kamenná drť</t>
+          <t>6 ks (= spodní, výkres D.1.1.02)</t>
         </is>
       </c>
       <c r="F56" s="17" t="n"/>
       <c r="G56" s="30" t="n">
-        <v>1.76</v>
+        <v>6</v>
       </c>
       <c r="H56" s="17" t="n"/>
       <c r="I56" s="17" t="n"/>
@@ -17173,12 +17173,12 @@
       </c>
       <c r="D57" s="24" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>273321321</t>
         </is>
       </c>
       <c r="E57" s="24" t="inlineStr">
         <is>
-          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
+          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
@@ -17187,7 +17187,7 @@
         </is>
       </c>
       <c r="G57" s="25" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
       <c r="H57" s="26" t="n"/>
       <c r="I57" s="26">
@@ -17220,12 +17220,12 @@
       <c r="D58" s="17" t="n"/>
       <c r="E58" s="29" t="inlineStr">
         <is>
-          <t>odhad 3 m schodů × 0.8 × 0.30 = 0.72 (ručně)</t>
+          <t>patky horní (0.3×0.3×0.5×6 = 0.27) + zídka lemující + věnec nad patkami (odhad ~1.5 m³) = ~1.75 m³</t>
         </is>
       </c>
       <c r="F58" s="17" t="n"/>
       <c r="G58" s="30" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
       <c r="H58" s="17" t="n"/>
       <c r="I58" s="17" t="n"/>
@@ -17234,171 +17234,171 @@
       <c r="L58" s="17" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="21" t="n"/>
-      <c r="C59" s="22" t="inlineStr">
+      <c r="B59" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="C59" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>174101101</t>
+        </is>
+      </c>
+      <c r="E59" s="24" t="inlineStr">
+        <is>
+          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G59" s="25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H59" s="26" t="n"/>
+      <c r="I59" s="26">
+        <f>IF(H59="",0,G59*H59)</f>
+        <v/>
+      </c>
+      <c r="J59" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K59" s="27" t="inlineStr">
+        <is>
+          <t>✓ cross-discipline OK [evidence: https://www.cs-urs.cz/podminky/cu201/800-1-Zemni-prace-(2020]</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="17" t="n"/>
+      <c r="C60" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="n"/>
+      <c r="E60" s="29" t="inlineStr">
+        <is>
+          <t>podlaha sklad 17.6 m² (legenda) × 0.10 m kladecí kamenná drť</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="n"/>
+      <c r="G60" s="30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H60" s="17" t="n"/>
+      <c r="I60" s="17" t="n"/>
+      <c r="J60" s="17" t="n"/>
+      <c r="K60" s="17" t="n"/>
+      <c r="L60" s="17" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="C61" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
+      <c r="E61" s="24" t="inlineStr">
+        <is>
+          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
+        </is>
+      </c>
+      <c r="F61" s="23" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G61" s="25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H61" s="26" t="n"/>
+      <c r="I61" s="26">
+        <f>IF(H61="",0,G61*H61)</f>
+        <v/>
+      </c>
+      <c r="J61" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K61" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="17" t="n"/>
+      <c r="C62" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="n"/>
+      <c r="E62" s="29" t="inlineStr">
+        <is>
+          <t>odhad 3 m schodů × 0.8 × 0.30 = 0.72 (ručně)</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="n"/>
+      <c r="G62" s="30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H62" s="17" t="n"/>
+      <c r="I62" s="17" t="n"/>
+      <c r="J62" s="17" t="n"/>
+      <c r="K62" s="17" t="n"/>
+      <c r="L62" s="17" t="n"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="21" t="n"/>
+      <c r="C63" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D59" s="22" t="inlineStr">
+      <c r="D63" s="22" t="inlineStr">
         <is>
           <t>HSV-3</t>
         </is>
       </c>
-      <c r="E59" s="22" t="inlineStr">
+      <c r="E63" s="22" t="inlineStr">
         <is>
           <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
-      <c r="F59" s="21" t="n"/>
-      <c r="G59" s="21" t="n"/>
-      <c r="H59" s="21" t="n"/>
-      <c r="I59" s="21" t="n"/>
-      <c r="J59" s="21" t="n"/>
-      <c r="K59" s="21" t="n"/>
-      <c r="L59" s="21" t="n"/>
-    </row>
-    <row r="60">
-      <c r="B60" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="C60" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D60" s="24" t="inlineStr">
-        <is>
-          <t>311233815</t>
-        </is>
-      </c>
-      <c r="E60" s="24" t="inlineStr">
-        <is>
-          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
-        </is>
-      </c>
-      <c r="F60" s="23" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G60" s="25" t="n">
-        <v>18</v>
-      </c>
-      <c r="H60" s="26" t="n"/>
-      <c r="I60" s="26">
-        <f>IF(H60="",0,G60*H60)</f>
-        <v/>
-      </c>
-      <c r="J60" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K60" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L60" s="5" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="17" t="n"/>
-      <c r="C61" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="n"/>
-      <c r="E61" s="29" t="inlineStr">
-        <is>
-          <t>S04 líc 6.35 × 3.0 m = 19.05 m²; blok 1800×600 mm (výkres D.1.1.02/03: délka 1800, 5 řad × 600 výška = 3000) → 3 celé (1800×3=5400) + 1 kus 950 mm na řadu, vazba na zámek; 5 řad × ~3.5 bloku ≈ 18 ks</t>
-        </is>
-      </c>
-      <c r="F61" s="17" t="n"/>
-      <c r="G61" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="H61" s="17" t="n"/>
-      <c r="I61" s="17" t="n"/>
-      <c r="J61" s="17" t="n"/>
-      <c r="K61" s="17" t="n"/>
-      <c r="L61" s="17" t="n"/>
-    </row>
-    <row r="62">
-      <c r="B62" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="C62" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D62" s="24" t="inlineStr">
-        <is>
-          <t>311233811</t>
-        </is>
-      </c>
-      <c r="E62" s="24" t="inlineStr">
-        <is>
-          <t>Obvodové stěny skladu — tvarovky ztraceného bednění tl. 250 mm × výška 2.4 m + zalití C25/30</t>
-        </is>
-      </c>
-      <c r="F62" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G62" s="25" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="H62" s="26" t="n"/>
-      <c r="I62" s="26">
-        <f>IF(H62="",0,G62*H62)</f>
-        <v/>
-      </c>
-      <c r="J62" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K62" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L62" s="5" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="17" t="n"/>
-      <c r="C63" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="n"/>
-      <c r="E63" s="29" t="inlineStr">
-        <is>
-          <t>obvod 19.4 m × výška 2.4 m = 46.6</t>
-        </is>
-      </c>
-      <c r="F63" s="17" t="n"/>
-      <c r="G63" s="30" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="H63" s="17" t="n"/>
-      <c r="I63" s="17" t="n"/>
-      <c r="J63" s="17" t="n"/>
-      <c r="K63" s="17" t="n"/>
-      <c r="L63" s="17" t="n"/>
+      <c r="F63" s="21" t="n"/>
+      <c r="G63" s="21" t="n"/>
+      <c r="H63" s="21" t="n"/>
+      <c r="I63" s="21" t="n"/>
+      <c r="J63" s="21" t="n"/>
+      <c r="K63" s="21" t="n"/>
+      <c r="L63" s="21" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="23" t="n">
@@ -17411,21 +17411,21 @@
       </c>
       <c r="D64" s="24" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>311233815</t>
         </is>
       </c>
       <c r="E64" s="24" t="inlineStr">
         <is>
-          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
         </is>
       </c>
       <c r="F64" s="23" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G64" s="25" t="n">
-        <v>1398</v>
+        <v>18</v>
       </c>
       <c r="H64" s="26" t="n"/>
       <c r="I64" s="26">
@@ -17437,9 +17437,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K64" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
+      <c r="K64" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
@@ -17458,12 +17458,12 @@
       <c r="D65" s="17" t="n"/>
       <c r="E65" s="29" t="inlineStr">
         <is>
-          <t>46.6 × 30 kg/m² = 1398</t>
+          <t>S04 líc 6.35 × 3.0 m = 19.05 m²; blok 1800×600 mm (výkres D.1.1.02/03: délka 1800, 5 řad × 600 výška = 3000) → 3 celé (1800×3=5400) + 1 kus 950 mm na řadu, vazba na zámek; 5 řad × ~3.5 bloku ≈ 18 ks</t>
         </is>
       </c>
       <c r="F65" s="17" t="n"/>
       <c r="G65" s="30" t="n">
-        <v>1398</v>
+        <v>18</v>
       </c>
       <c r="H65" s="17" t="n"/>
       <c r="I65" s="17" t="n"/>
@@ -17480,10 +17480,14 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D66" s="24" t="inlineStr"/>
+      <c r="D66" s="24" t="inlineStr">
+        <is>
+          <t>311233811</t>
+        </is>
+      </c>
       <c r="E66" s="24" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="F66" s="23" t="inlineStr">
@@ -17492,7 +17496,7 @@
         </is>
       </c>
       <c r="G66" s="25" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H66" s="26" t="n"/>
       <c r="I66" s="26">
@@ -17504,9 +17508,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K66" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
+      <c r="K66" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
@@ -17523,13 +17527,14 @@
         </is>
       </c>
       <c r="D67" s="17" t="n"/>
-      <c r="E67" s="29">
-        <f> S04 6.35×3.0 ≈19 + S03a 2×3.6×~2.0 ≈14 = 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
-        <v/>
+      <c r="E67" s="29" t="inlineStr">
+        <is>
+          <t>3 strany trapézu (6010-1000 dveře)+(7000-600 prefa)+(7033-600 prefa)=17843 mm = 17.84 m × výška 14 řad×0.25 = 3.5 m = 62.5 m²</t>
+        </is>
       </c>
       <c r="F67" s="17" t="n"/>
       <c r="G67" s="30" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H67" s="17" t="n"/>
       <c r="I67" s="17" t="n"/>
@@ -17546,19 +17551,23 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D68" s="24" t="inlineStr"/>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
       <c r="E68" s="24" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
         </is>
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G68" s="25" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H68" s="26" t="n"/>
       <c r="I68" s="26">
@@ -17570,9 +17579,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K68" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
+      <c r="K68" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
@@ -17589,13 +17598,14 @@
         </is>
       </c>
       <c r="D69" s="17" t="n"/>
-      <c r="E69" s="29">
-        <f> plocha stěn pod terénem 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
-        <v/>
+      <c r="E69" s="29" t="inlineStr">
+        <is>
+          <t>62.5 m² × 30 kg/m² (zalití C25/30) = 1875 kg</t>
+        </is>
       </c>
       <c r="F69" s="17" t="n"/>
       <c r="G69" s="30" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H69" s="17" t="n"/>
       <c r="I69" s="17" t="n"/>
@@ -17604,170 +17614,161 @@
       <c r="L69" s="17" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="21" t="n"/>
-      <c r="C70" s="22" t="inlineStr">
+      <c r="B70" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="C70" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D70" s="24" t="inlineStr"/>
+      <c r="E70" s="24" t="inlineStr">
+        <is>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+        </is>
+      </c>
+      <c r="F70" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G70" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="H70" s="26" t="n"/>
+      <c r="I70" s="26">
+        <f>IF(H70="",0,G70*H70)</f>
+        <v/>
+      </c>
+      <c r="J70" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K70" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="17" t="n"/>
+      <c r="C71" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D71" s="17" t="n"/>
+      <c r="E71" s="29">
+        <f> S04 6.35×3.0 ≈19 + S03a 2×3.6×~2.0 ≈14 = 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="F71" s="17" t="n"/>
+      <c r="G71" s="30" t="n">
+        <v>33</v>
+      </c>
+      <c r="H71" s="17" t="n"/>
+      <c r="I71" s="17" t="n"/>
+      <c r="J71" s="17" t="n"/>
+      <c r="K71" s="17" t="n"/>
+      <c r="L71" s="17" t="n"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="C72" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D72" s="24" t="inlineStr"/>
+      <c r="E72" s="24" t="inlineStr">
+        <is>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+        </is>
+      </c>
+      <c r="F72" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G72" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="H72" s="26" t="n"/>
+      <c r="I72" s="26">
+        <f>IF(H72="",0,G72*H72)</f>
+        <v/>
+      </c>
+      <c r="J72" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K72" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="17" t="n"/>
+      <c r="C73" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D73" s="17" t="n"/>
+      <c r="E73" s="29">
+        <f> plocha stěn pod terénem 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="F73" s="17" t="n"/>
+      <c r="G73" s="30" t="n">
+        <v>33</v>
+      </c>
+      <c r="H73" s="17" t="n"/>
+      <c r="I73" s="17" t="n"/>
+      <c r="J73" s="17" t="n"/>
+      <c r="K73" s="17" t="n"/>
+      <c r="L73" s="17" t="n"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="21" t="n"/>
+      <c r="C74" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D70" s="22" t="inlineStr">
+      <c r="D74" s="22" t="inlineStr">
         <is>
           <t>HSV-4</t>
         </is>
       </c>
-      <c r="E70" s="22" t="inlineStr">
+      <c r="E74" s="22" t="inlineStr">
         <is>
           <t>HSV-4 Vodorovné</t>
         </is>
       </c>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-    </row>
-    <row r="71">
-      <c r="B71" s="23" t="n">
-        <v>18</v>
-      </c>
-      <c r="C71" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D71" s="24" t="inlineStr">
-        <is>
-          <t>762341110</t>
-        </is>
-      </c>
-      <c r="E71" s="24" t="inlineStr">
-        <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
-        </is>
-      </c>
-      <c r="F71" s="23" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G71" s="25" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="H71" s="26" t="n"/>
-      <c r="I71" s="26">
-        <f>IF(H71="",0,G71*H71)</f>
-        <v/>
-      </c>
-      <c r="J71" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L71" s="5" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="17" t="n"/>
-      <c r="C72" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D72" s="17" t="n"/>
-      <c r="E72" s="29" t="inlineStr">
-        <is>
-          <t>6.35/0.625 = 10.16 → 11 ks × 3.34 m (rozpon 3.1 + uložení) = 36.74 bm</t>
-        </is>
-      </c>
-      <c r="F72" s="17" t="n"/>
-      <c r="G72" s="30" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="H72" s="17" t="n"/>
-      <c r="I72" s="17" t="n"/>
-      <c r="J72" s="17" t="n"/>
-      <c r="K72" s="17" t="n"/>
-      <c r="L72" s="17" t="n"/>
-    </row>
-    <row r="73">
-      <c r="B73" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="C73" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D73" s="24" t="inlineStr">
-        <is>
-          <t>762331110</t>
-        </is>
-      </c>
-      <c r="E73" s="24" t="inlineStr">
-        <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
-        </is>
-      </c>
-      <c r="F73" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G73" s="25" t="n">
-        <v>21.209</v>
-      </c>
-      <c r="H73" s="26" t="n"/>
-      <c r="I73" s="26">
-        <f>IF(H73="",0,G73*H73)</f>
-        <v/>
-      </c>
-      <c r="J73" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L73" s="5" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="17" t="n"/>
-      <c r="C74" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D74" s="17" t="n"/>
-      <c r="E74" s="29">
-        <f> 21.2 m² strop skladu</f>
-        <v/>
-      </c>
-      <c r="F74" s="17" t="n"/>
-      <c r="G74" s="30" t="n">
-        <v>21.209</v>
-      </c>
-      <c r="H74" s="17" t="n"/>
-      <c r="I74" s="17" t="n"/>
-      <c r="J74" s="17" t="n"/>
-      <c r="K74" s="17" t="n"/>
-      <c r="L74" s="17" t="n"/>
+      <c r="F74" s="21" t="n"/>
+      <c r="G74" s="21" t="n"/>
+      <c r="H74" s="21" t="n"/>
+      <c r="I74" s="21" t="n"/>
+      <c r="J74" s="21" t="n"/>
+      <c r="K74" s="21" t="n"/>
+      <c r="L74" s="21" t="n"/>
     </row>
     <row r="75">
       <c r="B75" s="23" t="n">
@@ -17780,21 +17781,21 @@
       </c>
       <c r="D75" s="24" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E75" s="24" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G75" s="25" t="n">
-        <v>22.26945</v>
+        <v>36.74</v>
       </c>
       <c r="H75" s="26" t="n"/>
       <c r="I75" s="26">
@@ -17827,12 +17828,12 @@
       <c r="D76" s="17" t="n"/>
       <c r="E76" s="29" t="inlineStr">
         <is>
-          <t>21.2 × 1.05 přesah</t>
+          <t>6.35/0.625 = 10.16 → 11 ks × 3.34 m (rozpon 3.1 + uložení) = 36.74 bm</t>
         </is>
       </c>
       <c r="F76" s="17" t="n"/>
       <c r="G76" s="30" t="n">
-        <v>22.26945</v>
+        <v>36.74</v>
       </c>
       <c r="H76" s="17" t="n"/>
       <c r="I76" s="17" t="n"/>
@@ -17851,21 +17852,21 @@
       </c>
       <c r="D77" s="24" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E77" s="24" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G77" s="25" t="n">
-        <v>790</v>
+        <v>21.209</v>
       </c>
       <c r="H77" s="26" t="n"/>
       <c r="I77" s="26">
@@ -17896,14 +17897,13 @@
         </is>
       </c>
       <c r="D78" s="17" t="n"/>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>6 ks IPE180 × 7.0 m × 18.8 kg/m = 789.6 → 790 kg (výkres D.1.1.02: 6 nosníků)</t>
-        </is>
+      <c r="E78" s="29">
+        <f> 21.2 m² strop skladu</f>
+        <v/>
       </c>
       <c r="F78" s="17" t="n"/>
       <c r="G78" s="30" t="n">
-        <v>790</v>
+        <v>21.209</v>
       </c>
       <c r="H78" s="17" t="n"/>
       <c r="I78" s="17" t="n"/>
@@ -17922,12 +17922,12 @@
       </c>
       <c r="D79" s="24" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E79" s="24" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
@@ -17936,7 +17936,7 @@
         </is>
       </c>
       <c r="G79" s="25" t="n">
-        <v>44.6</v>
+        <v>22.26945</v>
       </c>
       <c r="H79" s="26" t="n"/>
       <c r="I79" s="26">
@@ -17948,9 +17948,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L79" s="5" t="inlineStr">
@@ -17969,12 +17969,12 @@
       <c r="D80" s="17" t="n"/>
       <c r="E80" s="29" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
+          <t>21.2 × 1.05 přesah</t>
         </is>
       </c>
       <c r="F80" s="17" t="n"/>
       <c r="G80" s="30" t="n">
-        <v>44.6</v>
+        <v>22.26945</v>
       </c>
       <c r="H80" s="17" t="n"/>
       <c r="I80" s="17" t="n"/>
@@ -17993,12 +17993,12 @@
       </c>
       <c r="D81" s="24" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E81" s="24" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="G81" s="25" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H81" s="26" t="n"/>
       <c r="I81" s="26">
@@ -18040,12 +18040,12 @@
       <c r="D82" s="17" t="n"/>
       <c r="E82" s="29" t="inlineStr">
         <is>
-          <t>IPE 790 kg + pororošt 630 kg = 1420 kg žárově zinkováno (IPE 6 ks)</t>
+          <t>6 ks IPE180 × 7.0 m × 18.8 kg/m = 789.6 → 790 kg (výkres D.1.1.02: 6 nosníků)</t>
         </is>
       </c>
       <c r="F82" s="17" t="n"/>
       <c r="G82" s="30" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H82" s="17" t="n"/>
       <c r="I82" s="17" t="n"/>
@@ -18054,125 +18054,146 @@
       <c r="L82" s="17" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" s="21" t="n"/>
-      <c r="C83" s="22" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D83" s="22" t="inlineStr">
-        <is>
-          <t>HSV-5</t>
-        </is>
-      </c>
-      <c r="E83" s="22" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + schodiště</t>
-        </is>
-      </c>
-      <c r="F83" s="21" t="n"/>
-      <c r="G83" s="21" t="n"/>
-      <c r="H83" s="21" t="n"/>
-      <c r="I83" s="21" t="n"/>
-      <c r="J83" s="21" t="n"/>
-      <c r="K83" s="21" t="n"/>
-      <c r="L83" s="21" t="n"/>
+      <c r="B83" s="23" t="n">
+        <v>24</v>
+      </c>
+      <c r="C83" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>411321515</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+        </is>
+      </c>
+      <c r="F83" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G83" s="25" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H83" s="26" t="n"/>
+      <c r="I83" s="26">
+        <f>IF(H83="",0,G83*H83)</f>
+        <v/>
+      </c>
+      <c r="J83" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K83" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="B84" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="C84" s="23" t="inlineStr">
+      <c r="B84" s="17" t="n"/>
+      <c r="C84" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="n"/>
+      <c r="E84" s="29" t="inlineStr">
+        <is>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="n"/>
+      <c r="G84" s="30" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H84" s="17" t="n"/>
+      <c r="I84" s="17" t="n"/>
+      <c r="J84" s="17" t="n"/>
+      <c r="K84" s="17" t="n"/>
+      <c r="L84" s="17" t="n"/>
+    </row>
+    <row r="85">
+      <c r="B85" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="C85" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D84" s="24" t="inlineStr">
-        <is>
-          <t>121301101</t>
-        </is>
-      </c>
-      <c r="E84" s="24" t="inlineStr">
-        <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
-        </is>
-      </c>
-      <c r="F84" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G84" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H84" s="26" t="n"/>
-      <c r="I84" s="26">
-        <f>IF(H84="",0,G84*H84)</f>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>783201001</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G85" s="25" t="n">
+        <v>1420</v>
+      </c>
+      <c r="H85" s="26" t="n"/>
+      <c r="I85" s="26">
+        <f>IF(H85="",0,G85*H85)</f>
         <v/>
       </c>
-      <c r="J84" s="23" t="inlineStr">
+      <c r="J85" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K84" s="32" t="inlineStr">
+      <c r="K85" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L84" s="5" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + schodiště</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="17" t="n"/>
-      <c r="C85" s="28" t="inlineStr">
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="17" t="n"/>
+      <c r="C86" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D85" s="17" t="n"/>
-      <c r="E85" s="29" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
-        </is>
-      </c>
-      <c r="F85" s="17" t="n"/>
-      <c r="G85" s="30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H85" s="17" t="n"/>
-      <c r="I85" s="17" t="n"/>
-      <c r="J85" s="17" t="n"/>
-      <c r="K85" s="17" t="n"/>
-      <c r="L85" s="17" t="n"/>
-    </row>
-    <row r="86">
-      <c r="B86" s="19" t="n"/>
-      <c r="C86" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D86" s="20" t="inlineStr">
-        <is>
-          <t>PSV</t>
-        </is>
-      </c>
-      <c r="E86" s="20" t="inlineStr">
-        <is>
-          <t>Práce a dodávky PSV</t>
-        </is>
-      </c>
-      <c r="F86" s="19" t="n"/>
-      <c r="G86" s="19" t="n"/>
-      <c r="H86" s="19" t="n"/>
-      <c r="I86" s="19" t="n"/>
-      <c r="J86" s="19" t="n"/>
-      <c r="K86" s="19" t="n"/>
-      <c r="L86" s="19" t="n"/>
+      <c r="D86" s="17" t="n"/>
+      <c r="E86" s="29" t="inlineStr">
+        <is>
+          <t>IPE 790 kg + pororošt 630 kg = 1420 kg žárově zinkováno (IPE 6 ks)</t>
+        </is>
+      </c>
+      <c r="F86" s="17" t="n"/>
+      <c r="G86" s="30" t="n">
+        <v>1420</v>
+      </c>
+      <c r="H86" s="17" t="n"/>
+      <c r="I86" s="17" t="n"/>
+      <c r="J86" s="17" t="n"/>
+      <c r="K86" s="17" t="n"/>
+      <c r="L86" s="17" t="n"/>
     </row>
     <row r="87">
       <c r="B87" s="21" t="n"/>
@@ -18183,12 +18204,12 @@
       </c>
       <c r="D87" s="22" t="inlineStr">
         <is>
-          <t>PSV-76</t>
+          <t>HSV-5</t>
         </is>
       </c>
       <c r="E87" s="22" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="F87" s="21" t="n"/>
@@ -18201,7 +18222,7 @@
     </row>
     <row r="88">
       <c r="B88" s="23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C88" s="23" t="inlineStr">
         <is>
@@ -18210,21 +18231,21 @@
       </c>
       <c r="D88" s="24" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E88" s="24" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G88" s="25" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="H88" s="26" t="n"/>
       <c r="I88" s="26">
@@ -18243,7 +18264,7 @@
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
     </row>
@@ -18257,12 +18278,12 @@
       <c r="D89" s="17" t="n"/>
       <c r="E89" s="29" t="inlineStr">
         <is>
-          <t>1 ks vstupní dveře skladu</t>
+          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
         </is>
       </c>
       <c r="F89" s="17" t="n"/>
       <c r="G89" s="30" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="H89" s="17" t="n"/>
       <c r="I89" s="17" t="n"/>
@@ -18271,212 +18292,216 @@
       <c r="L89" s="17" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="21" t="n"/>
-      <c r="C90" s="22" t="inlineStr">
+      <c r="B90" s="19" t="n"/>
+      <c r="C90" s="20" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D90" s="22" t="inlineStr">
+      <c r="D90" s="20" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="E90" s="20" t="inlineStr">
+        <is>
+          <t>Práce a dodávky PSV</t>
+        </is>
+      </c>
+      <c r="F90" s="19" t="n"/>
+      <c r="G90" s="19" t="n"/>
+      <c r="H90" s="19" t="n"/>
+      <c r="I90" s="19" t="n"/>
+      <c r="J90" s="19" t="n"/>
+      <c r="K90" s="19" t="n"/>
+      <c r="L90" s="19" t="n"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="21" t="n"/>
+      <c r="C91" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D91" s="22" t="inlineStr">
         <is>
           <t>PSV-76</t>
         </is>
       </c>
-      <c r="E90" s="22" t="inlineStr">
+      <c r="E91" s="22" t="inlineStr">
+        <is>
+          <t>PSV-76 Výplně otvorů</t>
+        </is>
+      </c>
+      <c r="F91" s="21" t="n"/>
+      <c r="G91" s="21" t="n"/>
+      <c r="H91" s="21" t="n"/>
+      <c r="I91" s="21" t="n"/>
+      <c r="J91" s="21" t="n"/>
+      <c r="K91" s="21" t="n"/>
+      <c r="L91" s="21" t="n"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="23" t="n">
+        <v>27</v>
+      </c>
+      <c r="C92" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D92" s="24" t="inlineStr">
+        <is>
+          <t>766682111</t>
+        </is>
+      </c>
+      <c r="E92" s="24" t="inlineStr">
+        <is>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+        </is>
+      </c>
+      <c r="F92" s="23" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G92" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="26" t="n"/>
+      <c r="I92" s="26">
+        <f>IF(H92="",0,G92*H92)</f>
+        <v/>
+      </c>
+      <c r="J92" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K92" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>PSV-76 Výplně otvorů</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="17" t="n"/>
+      <c r="C93" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D93" s="17" t="n"/>
+      <c r="E93" s="29" t="inlineStr">
+        <is>
+          <t>1 ks vstupní dveře skladu</t>
+        </is>
+      </c>
+      <c r="F93" s="17" t="n"/>
+      <c r="G93" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="17" t="n"/>
+      <c r="I93" s="17" t="n"/>
+      <c r="J93" s="17" t="n"/>
+      <c r="K93" s="17" t="n"/>
+      <c r="L93" s="17" t="n"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="21" t="n"/>
+      <c r="C94" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D94" s="22" t="inlineStr">
+        <is>
+          <t>PSV-76</t>
+        </is>
+      </c>
+      <c r="E94" s="22" t="inlineStr">
         <is>
           <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
-      <c r="F90" s="21" t="n"/>
-      <c r="G90" s="21" t="n"/>
-      <c r="H90" s="21" t="n"/>
-      <c r="I90" s="21" t="n"/>
-      <c r="J90" s="21" t="n"/>
-      <c r="K90" s="21" t="n"/>
-      <c r="L90" s="21" t="n"/>
-    </row>
-    <row r="91">
-      <c r="B91" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="C91" s="23" t="inlineStr">
+      <c r="F94" s="21" t="n"/>
+      <c r="G94" s="21" t="n"/>
+      <c r="H94" s="21" t="n"/>
+      <c r="I94" s="21" t="n"/>
+      <c r="J94" s="21" t="n"/>
+      <c r="K94" s="21" t="n"/>
+      <c r="L94" s="21" t="n"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="C95" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D91" s="24" t="inlineStr"/>
-      <c r="E91" s="24" t="inlineStr">
+      <c r="D95" s="24" t="inlineStr"/>
+      <c r="E95" s="24" t="inlineStr">
         <is>
           <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
-      <c r="F91" s="23" t="inlineStr">
+      <c r="F95" s="23" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="G91" s="25" t="n">
+      <c r="G95" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H91" s="26" t="n"/>
-      <c r="I91" s="26">
-        <f>IF(H91="",0,G91*H91)</f>
+      <c r="H95" s="26" t="n"/>
+      <c r="I95" s="26">
+        <f>IF(H95="",0,G95*H95)</f>
         <v/>
       </c>
-      <c r="J91" s="23" t="inlineStr">
+      <c r="J95" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K91" s="33" t="inlineStr">
+      <c r="K95" s="33" t="inlineStr">
         <is>
           <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
-      <c r="L91" s="5" t="inlineStr">
+      <c r="L95" s="5" t="inlineStr">
         <is>
           <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" s="17" t="n"/>
-      <c r="C92" s="28" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="17" t="n"/>
+      <c r="C96" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D92" s="17" t="n"/>
-      <c r="E92" s="29">
+      <c r="D96" s="17" t="n"/>
+      <c r="E96" s="29">
         <f> 1 brána (Dodatek PD č.1)</f>
         <v/>
       </c>
-      <c r="F92" s="17" t="n"/>
-      <c r="G92" s="30" t="n">
+      <c r="F96" s="17" t="n"/>
+      <c r="G96" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H92" s="17" t="n"/>
-      <c r="I92" s="17" t="n"/>
-      <c r="J92" s="17" t="n"/>
-      <c r="K92" s="17" t="n"/>
-      <c r="L92" s="17" t="n"/>
-    </row>
-    <row r="93">
-      <c r="B93" s="21" t="n"/>
-      <c r="C93" s="22" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D93" s="22" t="inlineStr">
-        <is>
-          <t>PSV-77</t>
-        </is>
-      </c>
-      <c r="E93" s="22" t="inlineStr">
-        <is>
-          <t>PSV-77 Podlahy</t>
-        </is>
-      </c>
-      <c r="F93" s="21" t="n"/>
-      <c r="G93" s="21" t="n"/>
-      <c r="H93" s="21" t="n"/>
-      <c r="I93" s="21" t="n"/>
-      <c r="J93" s="21" t="n"/>
-      <c r="K93" s="21" t="n"/>
-      <c r="L93" s="21" t="n"/>
-    </row>
-    <row r="94">
-      <c r="B94" s="23" t="n">
-        <v>27</v>
-      </c>
-      <c r="C94" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D94" s="24" t="inlineStr"/>
-      <c r="E94" s="24" t="inlineStr">
-        <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
-        </is>
-      </c>
-      <c r="F94" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G94" s="25" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="H94" s="26" t="n"/>
-      <c r="I94" s="26">
-        <f>IF(H94="",0,G94*H94)</f>
-        <v/>
-      </c>
-      <c r="J94" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K94" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
-        </is>
-      </c>
-      <c r="L94" s="5" t="inlineStr">
-        <is>
-          <t>PSV-77 Podlahy</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="17" t="n"/>
-      <c r="C95" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D95" s="17" t="n"/>
-      <c r="E95" s="29" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 0.01 (sklad zahradní techniky) = 17.60 m² (inner usable area per DXF room table, walls excluded). Prior estimate 21.209 m² (outer 6.35×3.34) over-counted by 17.0% — walls of tvarovky ZB tl. 250 mm take ~3.6 m² of outer footprint.</t>
-        </is>
-      </c>
-      <c r="F95" s="17" t="n"/>
-      <c r="G95" s="30" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="H95" s="17" t="n"/>
-      <c r="I95" s="17" t="n"/>
-      <c r="J95" s="17" t="n"/>
-      <c r="K95" s="17" t="n"/>
-      <c r="L95" s="17" t="n"/>
-    </row>
-    <row r="96">
-      <c r="B96" s="19" t="n"/>
-      <c r="C96" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D96" s="20" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E96" s="20" t="inlineStr">
-        <is>
-          <t>Vedlejší rozpočtové náklady</t>
-        </is>
-      </c>
-      <c r="F96" s="19" t="n"/>
-      <c r="G96" s="19" t="n"/>
-      <c r="H96" s="19" t="n"/>
-      <c r="I96" s="19" t="n"/>
-      <c r="J96" s="19" t="n"/>
-      <c r="K96" s="19" t="n"/>
-      <c r="L96" s="19" t="n"/>
+      <c r="H96" s="17" t="n"/>
+      <c r="I96" s="17" t="n"/>
+      <c r="J96" s="17" t="n"/>
+      <c r="K96" s="17" t="n"/>
+      <c r="L96" s="17" t="n"/>
     </row>
     <row r="97">
       <c r="B97" s="21" t="n"/>
@@ -18487,12 +18512,12 @@
       </c>
       <c r="D97" s="22" t="inlineStr">
         <is>
-          <t>VRN</t>
+          <t>PSV-77</t>
         </is>
       </c>
       <c r="E97" s="22" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="F97" s="21" t="n"/>
@@ -18505,30 +18530,26 @@
     </row>
     <row r="98">
       <c r="B98" s="23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C98" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D98" s="24" t="inlineStr">
-        <is>
-          <t>030001000</t>
-        </is>
-      </c>
+      <c r="D98" s="24" t="inlineStr"/>
       <c r="E98" s="24" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G98" s="25" t="n">
-        <v>1</v>
+        <v>23.6</v>
       </c>
       <c r="H98" s="26" t="n"/>
       <c r="I98" s="26">
@@ -18540,14 +18561,14 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K98" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K98" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
     </row>
@@ -18561,12 +18582,12 @@
       <c r="D99" s="17" t="n"/>
       <c r="E99" s="29" t="inlineStr">
         <is>
-          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+          <t>plocha S01 = místnost 17.6 (legenda) + vynos za stěnu 6.0 (6010×1000 řez) = 23.6 m²</t>
         </is>
       </c>
       <c r="F99" s="17" t="n"/>
       <c r="G99" s="30" t="n">
-        <v>1</v>
+        <v>23.6</v>
       </c>
       <c r="H99" s="17" t="n"/>
       <c r="I99" s="17" t="n"/>
@@ -18575,267 +18596,388 @@
       <c r="L99" s="17" t="n"/>
     </row>
     <row r="100">
-      <c r="B100" s="21" t="n"/>
-      <c r="C100" s="22" t="inlineStr">
+      <c r="B100" s="19" t="n"/>
+      <c r="C100" s="20" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D100" s="22" t="inlineStr">
+      <c r="D100" s="20" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E100" s="22" t="inlineStr">
+      <c r="E100" s="20" t="inlineStr">
+        <is>
+          <t>Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="F100" s="19" t="n"/>
+      <c r="G100" s="19" t="n"/>
+      <c r="H100" s="19" t="n"/>
+      <c r="I100" s="19" t="n"/>
+      <c r="J100" s="19" t="n"/>
+      <c r="K100" s="19" t="n"/>
+      <c r="L100" s="19" t="n"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="21" t="n"/>
+      <c r="C101" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D101" s="22" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E101" s="22" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="F101" s="21" t="n"/>
+      <c r="G101" s="21" t="n"/>
+      <c r="H101" s="21" t="n"/>
+      <c r="I101" s="21" t="n"/>
+      <c r="J101" s="21" t="n"/>
+      <c r="K101" s="21" t="n"/>
+      <c r="L101" s="21" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="C102" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D102" s="24" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E102" s="24" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F102" s="23" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G102" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="26" t="n"/>
+      <c r="I102" s="26">
+        <f>IF(H102="",0,G102*H102)</f>
+        <v/>
+      </c>
+      <c r="J102" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K102" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L102" s="5" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="17" t="n"/>
+      <c r="C103" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D103" s="17" t="n"/>
+      <c r="E103" s="29" t="inlineStr">
+        <is>
+          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+        </is>
+      </c>
+      <c r="F103" s="17" t="n"/>
+      <c r="G103" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="17" t="n"/>
+      <c r="I103" s="17" t="n"/>
+      <c r="J103" s="17" t="n"/>
+      <c r="K103" s="17" t="n"/>
+      <c r="L103" s="17" t="n"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="21" t="n"/>
+      <c r="C104" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E104" s="22" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
-      <c r="F100" s="21" t="n"/>
-      <c r="G100" s="21" t="n"/>
-      <c r="H100" s="21" t="n"/>
-      <c r="I100" s="21" t="n"/>
-      <c r="J100" s="21" t="n"/>
-      <c r="K100" s="21" t="n"/>
-      <c r="L100" s="21" t="n"/>
-    </row>
-    <row r="101">
-      <c r="B101" s="23" t="n">
-        <v>29</v>
-      </c>
-      <c r="C101" s="23" t="inlineStr">
+      <c r="F104" s="21" t="n"/>
+      <c r="G104" s="21" t="n"/>
+      <c r="H104" s="21" t="n"/>
+      <c r="I104" s="21" t="n"/>
+      <c r="J104" s="21" t="n"/>
+      <c r="K104" s="21" t="n"/>
+      <c r="L104" s="21" t="n"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="C105" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D101" s="24" t="inlineStr">
+      <c r="D105" s="24" t="inlineStr">
         <is>
           <t>031032000</t>
         </is>
       </c>
-      <c r="E101" s="24" t="inlineStr">
+      <c r="E105" s="24" t="inlineStr">
         <is>
           <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
-      <c r="F101" s="23" t="inlineStr">
+      <c r="F105" s="23" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="G101" s="25" t="n">
+      <c r="G105" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H101" s="26" t="n"/>
-      <c r="I101" s="26">
-        <f>IF(H101="",0,G101*H101)</f>
+      <c r="H105" s="26" t="n"/>
+      <c r="I105" s="26">
+        <f>IF(H105="",0,G105*H105)</f>
         <v/>
       </c>
-      <c r="J101" s="23" t="inlineStr">
+      <c r="J105" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K101" s="32" t="inlineStr">
+      <c r="K105" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L101" s="5" t="inlineStr">
+      <c r="L105" s="5" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="B102" s="17" t="n"/>
-      <c r="C102" s="28" t="inlineStr">
+    <row r="106">
+      <c r="B106" s="17" t="n"/>
+      <c r="C106" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D102" s="17" t="n"/>
-      <c r="E102" s="29" t="inlineStr">
+      <c r="D106" s="17" t="n"/>
+      <c r="E106" s="29" t="inlineStr">
         <is>
           <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
         </is>
       </c>
-      <c r="F102" s="17" t="n"/>
-      <c r="G102" s="30" t="n">
+      <c r="F106" s="17" t="n"/>
+      <c r="G106" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H102" s="17" t="n"/>
-      <c r="I102" s="17" t="n"/>
-      <c r="J102" s="17" t="n"/>
-      <c r="K102" s="17" t="n"/>
-      <c r="L102" s="17" t="n"/>
-    </row>
-    <row r="103">
-      <c r="B103" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="C103" s="23" t="inlineStr">
+      <c r="H106" s="17" t="n"/>
+      <c r="I106" s="17" t="n"/>
+      <c r="J106" s="17" t="n"/>
+      <c r="K106" s="17" t="n"/>
+      <c r="L106" s="17" t="n"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="C107" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D103" s="24" t="inlineStr">
+      <c r="D107" s="24" t="inlineStr">
         <is>
           <t>997013211</t>
         </is>
       </c>
-      <c r="E103" s="24" t="inlineStr">
+      <c r="E107" s="24" t="inlineStr">
         <is>
           <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
-      <c r="F103" s="23" t="inlineStr">
+      <c r="F107" s="23" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
-      <c r="G103" s="25" t="n">
+      <c r="G107" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="H103" s="26" t="n"/>
-      <c r="I103" s="26">
-        <f>IF(H103="",0,G103*H103)</f>
+      <c r="H107" s="26" t="n"/>
+      <c r="I107" s="26">
+        <f>IF(H107="",0,G107*H107)</f>
         <v/>
       </c>
-      <c r="J103" s="23" t="inlineStr">
+      <c r="J107" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K103" s="32" t="inlineStr">
+      <c r="K107" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L103" s="5" t="inlineStr">
+      <c r="L107" s="5" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="B104" s="17" t="n"/>
-      <c r="C104" s="28" t="inlineStr">
+    <row r="108">
+      <c r="B108" s="17" t="n"/>
+      <c r="C108" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D104" s="17" t="n"/>
-      <c r="E104" s="29" t="inlineStr">
+      <c r="D108" s="17" t="n"/>
+      <c r="E108" s="29" t="inlineStr">
         <is>
           <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
         </is>
       </c>
-      <c r="F104" s="17" t="n"/>
-      <c r="G104" s="30" t="n">
+      <c r="F108" s="17" t="n"/>
+      <c r="G108" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="H104" s="17" t="n"/>
-      <c r="I104" s="17" t="n"/>
-      <c r="J104" s="17" t="n"/>
-      <c r="K104" s="17" t="n"/>
-      <c r="L104" s="17" t="n"/>
-    </row>
-    <row r="105">
-      <c r="B105" s="21" t="n"/>
-      <c r="C105" s="22" t="inlineStr">
+      <c r="H108" s="17" t="n"/>
+      <c r="I108" s="17" t="n"/>
+      <c r="J108" s="17" t="n"/>
+      <c r="K108" s="17" t="n"/>
+      <c r="L108" s="17" t="n"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="21" t="n"/>
+      <c r="C109" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D105" s="22" t="inlineStr">
+      <c r="D109" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E105" s="22" t="inlineStr">
+      <c r="E109" s="22" t="inlineStr">
         <is>
           <t>VRN — Geodet</t>
         </is>
       </c>
-      <c r="F105" s="21" t="n"/>
-      <c r="G105" s="21" t="n"/>
-      <c r="H105" s="21" t="n"/>
-      <c r="I105" s="21" t="n"/>
-      <c r="J105" s="21" t="n"/>
-      <c r="K105" s="21" t="n"/>
-      <c r="L105" s="21" t="n"/>
-    </row>
-    <row r="106">
-      <c r="B106" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="C106" s="23" t="inlineStr">
+      <c r="F109" s="21" t="n"/>
+      <c r="G109" s="21" t="n"/>
+      <c r="H109" s="21" t="n"/>
+      <c r="I109" s="21" t="n"/>
+      <c r="J109" s="21" t="n"/>
+      <c r="K109" s="21" t="n"/>
+      <c r="L109" s="21" t="n"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="23" t="n">
+        <v>33</v>
+      </c>
+      <c r="C110" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D106" s="24" t="inlineStr">
+      <c r="D110" s="24" t="inlineStr">
         <is>
           <t>030141000</t>
         </is>
       </c>
-      <c r="E106" s="24" t="inlineStr">
+      <c r="E110" s="24" t="inlineStr">
         <is>
           <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
-      <c r="F106" s="23" t="inlineStr">
+      <c r="F110" s="23" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="G106" s="25" t="n">
+      <c r="G110" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H106" s="26" t="n"/>
-      <c r="I106" s="26">
-        <f>IF(H106="",0,G106*H106)</f>
+      <c r="H110" s="26" t="n"/>
+      <c r="I110" s="26">
+        <f>IF(H110="",0,G110*H110)</f>
         <v/>
       </c>
-      <c r="J106" s="23" t="inlineStr">
+      <c r="J110" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K106" s="32" t="inlineStr">
+      <c r="K110" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L106" s="5" t="inlineStr">
+      <c r="L110" s="5" t="inlineStr">
         <is>
           <t>VRN — Geodet</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="B107" s="17" t="n"/>
-      <c r="C107" s="28" t="inlineStr">
+    <row r="111">
+      <c r="B111" s="17" t="n"/>
+      <c r="C111" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D107" s="17" t="n"/>
-      <c r="E107" s="29" t="inlineStr">
+      <c r="D111" s="17" t="n"/>
+      <c r="E111" s="29" t="inlineStr">
         <is>
           <t>Standard geodet vytýčení pro nový objekt</t>
         </is>
       </c>
-      <c r="F107" s="17" t="n"/>
-      <c r="G107" s="30" t="n">
+      <c r="F111" s="17" t="n"/>
+      <c r="G111" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H107" s="17" t="n"/>
-      <c r="I107" s="17" t="n"/>
-      <c r="J107" s="17" t="n"/>
-      <c r="K107" s="17" t="n"/>
-      <c r="L107" s="17" t="n"/>
+      <c r="H111" s="17" t="n"/>
+      <c r="I111" s="17" t="n"/>
+      <c r="J111" s="17" t="n"/>
+      <c r="K111" s="17" t="n"/>
+      <c r="L111" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -18861,7 +19003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H253"/>
+  <dimension ref="B2:H257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -18940,7 +19082,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10">
@@ -18950,7 +19092,7 @@
         </is>
       </c>
       <c r="C10" s="34" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13">
@@ -21167,7 +21309,7 @@
       </c>
       <c r="G83" s="24" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za st</t>
         </is>
       </c>
       <c r="H83" s="24" t="inlineStr">
@@ -21875,7 +22017,7 @@
       <c r="F106" s="24" t="inlineStr"/>
       <c r="G106" s="24" t="inlineStr">
         <is>
-          <t>Obvodové stěny skladu — tvarovky ztraceného bednění tl. 250 mm × výška</t>
+          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm,</t>
         </is>
       </c>
       <c r="H106" s="24" t="inlineStr">
@@ -26658,6 +26800,130 @@
         </is>
       </c>
       <c r="H253" s="24" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV1.007</t>
+        </is>
+      </c>
+      <c r="C254" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D254" s="24" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="E254" s="24" t="inlineStr">
+        <is>
+          <t>564231111</t>
+        </is>
+      </c>
+      <c r="F254" s="24" t="inlineStr"/>
+      <c r="G254" s="24" t="inlineStr">
+        <is>
+          <t>Kladecí lože z kamenné drti 4-8 mm tl. 40 mm pod betonovou dlažbu skla</t>
+        </is>
+      </c>
+      <c r="H254" s="24" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV1.008</t>
+        </is>
+      </c>
+      <c r="C255" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D255" s="24" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="E255" s="24" t="inlineStr">
+        <is>
+          <t>174101101</t>
+        </is>
+      </c>
+      <c r="F255" s="24" t="inlineStr"/>
+      <c r="G255" s="24" t="inlineStr">
+        <is>
+          <t>Zásyp za prefabrikovanou opěrnou stěnou S04 — materiál dle PD (NEuvede</t>
+        </is>
+      </c>
+      <c r="H255" s="24" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.PSV76.003</t>
+        </is>
+      </c>
+      <c r="C256" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D256" s="24" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="E256" s="24" t="inlineStr"/>
+      <c r="F256" s="24" t="inlineStr"/>
+      <c r="G256" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo </t>
+        </is>
+      </c>
+      <c r="H256" s="24" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.PSV76.004</t>
+        </is>
+      </c>
+      <c r="C257" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D257" s="24" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="E257" s="24" t="inlineStr"/>
+      <c r="F257" s="24" t="inlineStr"/>
+      <c r="G257" s="24" t="inlineStr">
+        <is>
+          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuve</t>
+        </is>
+      </c>
+      <c r="H257" s="24" t="inlineStr">
         <is>
           <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
@@ -26685,7 +26951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N234"/>
+  <dimension ref="B2:N238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -28736,7 +29002,7 @@
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>Obvodové stěny skladu — tvarovky ztraceného bednění tl. 250 mm × výška 2.4 m + z</t>
+          <t xml:space="preserve">Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 </t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
@@ -33208,7 +33474,7 @@
       </c>
       <c r="D146" s="24" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
         </is>
       </c>
       <c r="E146" s="24" t="inlineStr"/>
@@ -36728,6 +36994,146 @@
       <c r="M234" s="24" t="inlineStr"/>
       <c r="N234" s="24" t="inlineStr"/>
     </row>
+    <row r="235">
+      <c r="B235" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV1.007</t>
+        </is>
+      </c>
+      <c r="C235" s="24" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="D235" s="24" t="inlineStr">
+        <is>
+          <t>Kladecí lože z kamenné drti 4-8 mm tl. 40 mm pod betonovou dlažbu skladu</t>
+        </is>
+      </c>
+      <c r="E235" s="24" t="inlineStr">
+        <is>
+          <t>564231111</t>
+        </is>
+      </c>
+      <c r="F235" s="24" t="inlineStr"/>
+      <c r="G235" s="24" t="inlineStr"/>
+      <c r="H235" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I235" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J235" s="32" t="inlineStr"/>
+      <c r="K235" s="24" t="inlineStr"/>
+      <c r="L235" s="24" t="inlineStr"/>
+      <c r="M235" s="24" t="inlineStr"/>
+      <c r="N235" s="24" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="B236" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV1.008</t>
+        </is>
+      </c>
+      <c r="C236" s="24" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="D236" s="24" t="inlineStr">
+        <is>
+          <t>Zásyp za prefabrikovanou opěrnou stěnou S04 — materiál dle PD (NEuveden v legend</t>
+        </is>
+      </c>
+      <c r="E236" s="24" t="inlineStr">
+        <is>
+          <t>174101101</t>
+        </is>
+      </c>
+      <c r="F236" s="24" t="inlineStr"/>
+      <c r="G236" s="24" t="inlineStr"/>
+      <c r="H236" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I236" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J236" s="32" t="inlineStr"/>
+      <c r="K236" s="24" t="inlineStr"/>
+      <c r="L236" s="24" t="inlineStr"/>
+      <c r="M236" s="24" t="inlineStr"/>
+      <c r="N236" s="24" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="B237" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.PSV76.003</t>
+        </is>
+      </c>
+      <c r="C237" s="24" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="D237" s="24" t="inlineStr">
+        <is>
+          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
+        </is>
+      </c>
+      <c r="E237" s="24" t="inlineStr"/>
+      <c r="F237" s="24" t="inlineStr"/>
+      <c r="G237" s="24" t="inlineStr"/>
+      <c r="H237" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I237" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J237" s="33" t="inlineStr"/>
+      <c r="K237" s="24" t="inlineStr"/>
+      <c r="L237" s="24" t="inlineStr"/>
+      <c r="M237" s="24" t="inlineStr"/>
+      <c r="N237" s="24" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="B238" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.PSV76.004</t>
+        </is>
+      </c>
+      <c r="C238" s="24" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="D238" s="24" t="inlineStr">
+        <is>
+          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
+        </is>
+      </c>
+      <c r="E238" s="24" t="inlineStr"/>
+      <c r="F238" s="24" t="inlineStr"/>
+      <c r="G238" s="24" t="inlineStr"/>
+      <c r="H238" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I238" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J238" s="33" t="inlineStr"/>
+      <c r="K238" s="24" t="inlineStr"/>
+      <c r="L238" s="24" t="inlineStr"/>
+      <c r="M238" s="24" t="inlineStr"/>
+      <c r="N238" s="24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-02_v3_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-02_v3_final.xlsx
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <f>SUM('SO_260217_Sklad'!I34:I110)</f>
+        <f>SUM('SO_260217_Sklad'!I34:I114)</f>
         <v/>
       </c>
       <c r="E15" s="7">
@@ -15954,7 +15954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L111"/>
+  <dimension ref="B2:L115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -16115,7 +16115,7 @@
         </is>
       </c>
       <c r="D16" s="7">
-        <f>SUMIFS(I32:I111,L32:L111,C16)</f>
+        <f>SUMIFS(I32:I115,L32:L115,C16)</f>
         <v/>
       </c>
     </row>
@@ -16127,7 +16127,7 @@
         </is>
       </c>
       <c r="D17" s="7">
-        <f>SUMIFS(I32:I111,L32:L111,C17)</f>
+        <f>SUMIFS(I32:I115,L32:L115,C17)</f>
         <v/>
       </c>
     </row>
@@ -16139,7 +16139,7 @@
         </is>
       </c>
       <c r="D18" s="7">
-        <f>SUMIFS(I32:I111,L32:L111,C18)</f>
+        <f>SUMIFS(I32:I115,L32:L115,C18)</f>
         <v/>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
         </is>
       </c>
       <c r="D19" s="7">
-        <f>SUMIFS(I32:I111,L32:L111,C19)</f>
+        <f>SUMIFS(I32:I115,L32:L115,C19)</f>
         <v/>
       </c>
     </row>
@@ -16163,7 +16163,7 @@
         </is>
       </c>
       <c r="D20" s="7">
-        <f>SUMIFS(I32:I111,L32:L111,C20)</f>
+        <f>SUMIFS(I32:I115,L32:L115,C20)</f>
         <v/>
       </c>
     </row>
@@ -16175,7 +16175,7 @@
         </is>
       </c>
       <c r="D21" s="7">
-        <f>SUMIFS(I32:I111,L32:L111,C21)</f>
+        <f>SUMIFS(I32:I115,L32:L115,C21)</f>
         <v/>
       </c>
     </row>
@@ -16187,7 +16187,7 @@
         </is>
       </c>
       <c r="D22" s="7">
-        <f>SUMIFS(I32:I111,L32:L111,C22)</f>
+        <f>SUMIFS(I32:I115,L32:L115,C22)</f>
         <v/>
       </c>
     </row>
@@ -16199,7 +16199,7 @@
         </is>
       </c>
       <c r="D23" s="7">
-        <f>SUMIFS(I32:I111,L32:L111,C23)</f>
+        <f>SUMIFS(I32:I115,L32:L115,C23)</f>
         <v/>
       </c>
     </row>
@@ -16211,7 +16211,7 @@
         </is>
       </c>
       <c r="D24" s="7">
-        <f>SUMIFS(I32:I111,L32:L111,C24)</f>
+        <f>SUMIFS(I32:I115,L32:L115,C24)</f>
         <v/>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
         </is>
       </c>
       <c r="D25" s="7">
-        <f>SUMIFS(I32:I111,L32:L111,C25)</f>
+        <f>SUMIFS(I32:I115,L32:L115,C25)</f>
         <v/>
       </c>
     </row>
@@ -16235,7 +16235,7 @@
         </is>
       </c>
       <c r="D26" s="7">
-        <f>SUMIFS(I32:I111,L32:L111,C26)</f>
+        <f>SUMIFS(I32:I115,L32:L115,C26)</f>
         <v/>
       </c>
     </row>
@@ -16929,167 +16929,163 @@
       <c r="L49" s="17" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="21" t="n"/>
-      <c r="C50" s="22" t="inlineStr">
+      <c r="B50" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="C50" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr"/>
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>Trubka Ø ~150 mm v štěrkovém obsypu podél vysokého pasu — drenáž/odvětrání radonu (OVĚŘIT)</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G50" s="25" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="H50" s="26" t="n"/>
+      <c r="I50" s="26">
+        <f>IF(H50="",0,G50*H50)</f>
+        <v/>
+      </c>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K50" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="29" t="inlineStr">
+        <is>
+          <t>délka jako prefa stěna ≈ 6.35 m; Ø ~150 mm (měřeno z řezu, nepopsáno)</t>
+        </is>
+      </c>
+      <c r="F51" s="17" t="n"/>
+      <c r="G51" s="30" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="H51" s="17" t="n"/>
+      <c r="I51" s="17" t="n"/>
+      <c r="J51" s="17" t="n"/>
+      <c r="K51" s="17" t="n"/>
+      <c r="L51" s="17" t="n"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr"/>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>Trubka Ø 120-130 mm v štěrkovém obsypu podél stěny — drenáž/odvětrání radonu (OVĚŘIT)</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G52" s="25" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H52" s="26" t="n"/>
+      <c r="I52" s="26">
+        <f>IF(H52="",0,G52*H52)</f>
+        <v/>
+      </c>
+      <c r="J52" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K52" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="17" t="n"/>
+      <c r="C53" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="n"/>
+      <c r="E53" s="29" t="inlineStr">
+        <is>
+          <t>délka 6010 mm; Ø 120-130 mm (měřeno z řezu, nepopsáno)</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="n"/>
+      <c r="G53" s="30" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H53" s="17" t="n"/>
+      <c r="I53" s="17" t="n"/>
+      <c r="J53" s="17" t="n"/>
+      <c r="K53" s="17" t="n"/>
+      <c r="L53" s="17" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="21" t="n"/>
+      <c r="C54" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D50" s="22" t="inlineStr">
+      <c r="D54" s="22" t="inlineStr">
         <is>
           <t>HSV-2</t>
         </is>
       </c>
-      <c r="E50" s="22" t="inlineStr">
+      <c r="E54" s="22" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="F50" s="21" t="n"/>
-      <c r="G50" s="21" t="n"/>
-      <c r="H50" s="21" t="n"/>
-      <c r="I50" s="21" t="n"/>
-      <c r="J50" s="21" t="n"/>
-      <c r="K50" s="21" t="n"/>
-      <c r="L50" s="21" t="n"/>
-    </row>
-    <row r="51">
-      <c r="B51" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="C51" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="inlineStr"/>
-      <c r="E51" s="24" t="inlineStr">
-        <is>
-          <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
-        </is>
-      </c>
-      <c r="F51" s="23" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G51" s="25" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="H51" s="26" t="n"/>
-      <c r="I51" s="26">
-        <f>IF(H51="",0,G51*H51)</f>
-        <v/>
-      </c>
-      <c r="J51" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K51" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="17" t="n"/>
-      <c r="C52" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="n"/>
-      <c r="E52" s="29" t="inlineStr">
-        <is>
-          <t>0.5 × 0.5 × 19.4 obvod = 4.85</t>
-        </is>
-      </c>
-      <c r="F52" s="17" t="n"/>
-      <c r="G52" s="30" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="H52" s="17" t="n"/>
-      <c r="I52" s="17" t="n"/>
-      <c r="J52" s="17" t="n"/>
-      <c r="K52" s="17" t="n"/>
-      <c r="L52" s="17" t="n"/>
-    </row>
-    <row r="53">
-      <c r="B53" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="C53" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D53" s="24" t="inlineStr">
-        <is>
-          <t>273313811</t>
-        </is>
-      </c>
-      <c r="E53" s="24" t="inlineStr">
-        <is>
-          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
-        </is>
-      </c>
-      <c r="F53" s="23" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G53" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="H53" s="26" t="n"/>
-      <c r="I53" s="26">
-        <f>IF(H53="",0,G53*H53)</f>
-        <v/>
-      </c>
-      <c r="J53" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K53" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/podminky/cu202/801-1-Budovy-a-haly---z]</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="17" t="n"/>
-      <c r="C54" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="n"/>
-      <c r="E54" s="29" t="inlineStr">
-        <is>
-          <t>6 ks (výkres D.1.1.02 — 6 štvercových patek pod IPE180)</t>
-        </is>
-      </c>
-      <c r="F54" s="17" t="n"/>
-      <c r="G54" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="H54" s="17" t="n"/>
-      <c r="I54" s="17" t="n"/>
-      <c r="J54" s="17" t="n"/>
-      <c r="K54" s="17" t="n"/>
-      <c r="L54" s="17" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="21" t="n"/>
+      <c r="I54" s="21" t="n"/>
+      <c r="J54" s="21" t="n"/>
+      <c r="K54" s="21" t="n"/>
+      <c r="L54" s="21" t="n"/>
     </row>
     <row r="55">
       <c r="B55" s="23" t="n">
@@ -17100,23 +17096,19 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D55" s="24" t="inlineStr">
-        <is>
-          <t>311233812</t>
-        </is>
-      </c>
+      <c r="D55" s="24" t="inlineStr"/>
       <c r="E55" s="24" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G55" s="25" t="n">
-        <v>6</v>
+        <v>4.84</v>
       </c>
       <c r="H55" s="26" t="n"/>
       <c r="I55" s="26">
@@ -17128,9 +17120,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K55" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K55" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -17149,12 +17141,12 @@
       <c r="D56" s="17" t="n"/>
       <c r="E56" s="29" t="inlineStr">
         <is>
-          <t>6 ks (= spodní, výkres D.1.1.02)</t>
+          <t>0.5 × 0.5 × 19.4 obvod = 4.85</t>
         </is>
       </c>
       <c r="F56" s="17" t="n"/>
       <c r="G56" s="30" t="n">
-        <v>6</v>
+        <v>4.84</v>
       </c>
       <c r="H56" s="17" t="n"/>
       <c r="I56" s="17" t="n"/>
@@ -17173,21 +17165,21 @@
       </c>
       <c r="D57" s="24" t="inlineStr">
         <is>
-          <t>273321321</t>
+          <t>273313811</t>
         </is>
       </c>
       <c r="E57" s="24" t="inlineStr">
         <is>
-          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
+          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G57" s="25" t="n">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="H57" s="26" t="n"/>
       <c r="I57" s="26">
@@ -17199,9 +17191,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K57" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K57" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/podminky/cu202/801-1-Budovy-a-haly---z]</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -17220,12 +17212,12 @@
       <c r="D58" s="17" t="n"/>
       <c r="E58" s="29" t="inlineStr">
         <is>
-          <t>patky horní (0.3×0.3×0.5×6 = 0.27) + zídka lemující + věnec nad patkami (odhad ~1.5 m³) = ~1.75 m³</t>
+          <t>6 ks (výkres D.1.1.02 — 6 štvercových patek pod IPE180)</t>
         </is>
       </c>
       <c r="F58" s="17" t="n"/>
       <c r="G58" s="30" t="n">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="H58" s="17" t="n"/>
       <c r="I58" s="17" t="n"/>
@@ -17244,21 +17236,21 @@
       </c>
       <c r="D59" s="24" t="inlineStr">
         <is>
-          <t>174101101</t>
+          <t>311233812</t>
         </is>
       </c>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
+          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G59" s="25" t="n">
-        <v>1.76</v>
+        <v>6</v>
       </c>
       <c r="H59" s="26" t="n"/>
       <c r="I59" s="26">
@@ -17270,9 +17262,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K59" s="27" t="inlineStr">
-        <is>
-          <t>✓ cross-discipline OK [evidence: https://www.cs-urs.cz/podminky/cu201/800-1-Zemni-prace-(2020]</t>
+      <c r="K59" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -17291,12 +17283,12 @@
       <c r="D60" s="17" t="n"/>
       <c r="E60" s="29" t="inlineStr">
         <is>
-          <t>podlaha sklad 17.6 m² (legenda) × 0.10 m kladecí kamenná drť</t>
+          <t>6 ks (= spodní, výkres D.1.1.02)</t>
         </is>
       </c>
       <c r="F60" s="17" t="n"/>
       <c r="G60" s="30" t="n">
-        <v>1.76</v>
+        <v>6</v>
       </c>
       <c r="H60" s="17" t="n"/>
       <c r="I60" s="17" t="n"/>
@@ -17315,12 +17307,12 @@
       </c>
       <c r="D61" s="24" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>273321321</t>
         </is>
       </c>
       <c r="E61" s="24" t="inlineStr">
         <is>
-          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
+          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
@@ -17329,7 +17321,7 @@
         </is>
       </c>
       <c r="G61" s="25" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
       <c r="H61" s="26" t="n"/>
       <c r="I61" s="26">
@@ -17362,12 +17354,12 @@
       <c r="D62" s="17" t="n"/>
       <c r="E62" s="29" t="inlineStr">
         <is>
-          <t>odhad 3 m schodů × 0.8 × 0.30 = 0.72 (ručně)</t>
+          <t>patky horní (0.3×0.3×0.5×6 = 0.27) + věnec nad patkami 2 řady ztrac.bednění (0.5 v × 6.35 d × 0.3 š = 0.95) + zídka lemující (~0.5) = ~1.72 ≈ 1.75 m³</t>
         </is>
       </c>
       <c r="F62" s="17" t="n"/>
       <c r="G62" s="30" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
       <c r="H62" s="17" t="n"/>
       <c r="I62" s="17" t="n"/>
@@ -17376,171 +17368,171 @@
       <c r="L62" s="17" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" s="21" t="n"/>
-      <c r="C63" s="22" t="inlineStr">
+      <c r="B63" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="C63" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D63" s="24" t="inlineStr">
+        <is>
+          <t>174101101</t>
+        </is>
+      </c>
+      <c r="E63" s="24" t="inlineStr">
+        <is>
+          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
+        </is>
+      </c>
+      <c r="F63" s="23" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G63" s="25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H63" s="26" t="n"/>
+      <c r="I63" s="26">
+        <f>IF(H63="",0,G63*H63)</f>
+        <v/>
+      </c>
+      <c r="J63" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K63" s="27" t="inlineStr">
+        <is>
+          <t>✓ cross-discipline OK [evidence: https://www.cs-urs.cz/podminky/cu201/800-1-Zemni-prace-(2020]</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="n"/>
+      <c r="E64" s="29" t="inlineStr">
+        <is>
+          <t>podlaha sklad 17.6 m² (legenda) × 0.10 m kladecí kamenná drť</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="n"/>
+      <c r="G64" s="30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H64" s="17" t="n"/>
+      <c r="I64" s="17" t="n"/>
+      <c r="J64" s="17" t="n"/>
+      <c r="K64" s="17" t="n"/>
+      <c r="L64" s="17" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="C65" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D65" s="24" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
+      <c r="E65" s="24" t="inlineStr">
+        <is>
+          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G65" s="25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H65" s="26" t="n"/>
+      <c r="I65" s="26">
+        <f>IF(H65="",0,G65*H65)</f>
+        <v/>
+      </c>
+      <c r="J65" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="17" t="n"/>
+      <c r="C66" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="n"/>
+      <c r="E66" s="29" t="inlineStr">
+        <is>
+          <t>odhad 3 m schodů × 0.8 × 0.30 = 0.72 (ručně)</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="n"/>
+      <c r="G66" s="30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H66" s="17" t="n"/>
+      <c r="I66" s="17" t="n"/>
+      <c r="J66" s="17" t="n"/>
+      <c r="K66" s="17" t="n"/>
+      <c r="L66" s="17" t="n"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="21" t="n"/>
+      <c r="C67" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D63" s="22" t="inlineStr">
+      <c r="D67" s="22" t="inlineStr">
         <is>
           <t>HSV-3</t>
         </is>
       </c>
-      <c r="E63" s="22" t="inlineStr">
+      <c r="E67" s="22" t="inlineStr">
         <is>
           <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
-      <c r="F63" s="21" t="n"/>
-      <c r="G63" s="21" t="n"/>
-      <c r="H63" s="21" t="n"/>
-      <c r="I63" s="21" t="n"/>
-      <c r="J63" s="21" t="n"/>
-      <c r="K63" s="21" t="n"/>
-      <c r="L63" s="21" t="n"/>
-    </row>
-    <row r="64">
-      <c r="B64" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="C64" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D64" s="24" t="inlineStr">
-        <is>
-          <t>311233815</t>
-        </is>
-      </c>
-      <c r="E64" s="24" t="inlineStr">
-        <is>
-          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
-        </is>
-      </c>
-      <c r="F64" s="23" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G64" s="25" t="n">
-        <v>18</v>
-      </c>
-      <c r="H64" s="26" t="n"/>
-      <c r="I64" s="26">
-        <f>IF(H64="",0,G64*H64)</f>
-        <v/>
-      </c>
-      <c r="J64" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K64" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L64" s="5" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="17" t="n"/>
-      <c r="C65" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="n"/>
-      <c r="E65" s="29" t="inlineStr">
-        <is>
-          <t>S04 líc 6.35 × 3.0 m = 19.05 m²; blok 1800×600 mm (výkres D.1.1.02/03: délka 1800, 5 řad × 600 výška = 3000) → 3 celé (1800×3=5400) + 1 kus 950 mm na řadu, vazba na zámek; 5 řad × ~3.5 bloku ≈ 18 ks</t>
-        </is>
-      </c>
-      <c r="F65" s="17" t="n"/>
-      <c r="G65" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="H65" s="17" t="n"/>
-      <c r="I65" s="17" t="n"/>
-      <c r="J65" s="17" t="n"/>
-      <c r="K65" s="17" t="n"/>
-      <c r="L65" s="17" t="n"/>
-    </row>
-    <row r="66">
-      <c r="B66" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="C66" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D66" s="24" t="inlineStr">
-        <is>
-          <t>311233811</t>
-        </is>
-      </c>
-      <c r="E66" s="24" t="inlineStr">
-        <is>
-          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
-        </is>
-      </c>
-      <c r="F66" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G66" s="25" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="H66" s="26" t="n"/>
-      <c r="I66" s="26">
-        <f>IF(H66="",0,G66*H66)</f>
-        <v/>
-      </c>
-      <c r="J66" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="17" t="n"/>
-      <c r="C67" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="n"/>
-      <c r="E67" s="29" t="inlineStr">
-        <is>
-          <t>3 strany trapézu (6010-1000 dveře)+(7000-600 prefa)+(7033-600 prefa)=17843 mm = 17.84 m × výška 14 řad×0.25 = 3.5 m = 62.5 m²</t>
-        </is>
-      </c>
-      <c r="F67" s="17" t="n"/>
-      <c r="G67" s="30" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="H67" s="17" t="n"/>
-      <c r="I67" s="17" t="n"/>
-      <c r="J67" s="17" t="n"/>
-      <c r="K67" s="17" t="n"/>
-      <c r="L67" s="17" t="n"/>
+      <c r="F67" s="21" t="n"/>
+      <c r="G67" s="21" t="n"/>
+      <c r="H67" s="21" t="n"/>
+      <c r="I67" s="21" t="n"/>
+      <c r="J67" s="21" t="n"/>
+      <c r="K67" s="21" t="n"/>
+      <c r="L67" s="21" t="n"/>
     </row>
     <row r="68">
       <c r="B68" s="23" t="n">
@@ -17553,21 +17545,21 @@
       </c>
       <c r="D68" s="24" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>311233815</t>
         </is>
       </c>
       <c r="E68" s="24" t="inlineStr">
         <is>
-          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
         </is>
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G68" s="25" t="n">
-        <v>1875</v>
+        <v>18</v>
       </c>
       <c r="H68" s="26" t="n"/>
       <c r="I68" s="26">
@@ -17579,9 +17571,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K68" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
+      <c r="K68" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
@@ -17600,12 +17592,12 @@
       <c r="D69" s="17" t="n"/>
       <c r="E69" s="29" t="inlineStr">
         <is>
-          <t>62.5 m² × 30 kg/m² (zalití C25/30) = 1875 kg</t>
+          <t>S04 líc 6.35 × 3.0 m = 19.05 m²; blok 1800×600 mm (výkres D.1.1.02/03: délka 1800, 5 řad × 600 výška = 3000) → 3 celé (1800×3=5400) + 1 kus 950 mm na řadu, vazba na zámek; 5 řad × ~3.5 bloku ≈ 18 ks</t>
         </is>
       </c>
       <c r="F69" s="17" t="n"/>
       <c r="G69" s="30" t="n">
-        <v>1875</v>
+        <v>18</v>
       </c>
       <c r="H69" s="17" t="n"/>
       <c r="I69" s="17" t="n"/>
@@ -17622,10 +17614,14 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D70" s="24" t="inlineStr"/>
+      <c r="D70" s="24" t="inlineStr">
+        <is>
+          <t>311233811</t>
+        </is>
+      </c>
       <c r="E70" s="24" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="F70" s="23" t="inlineStr">
@@ -17634,7 +17630,7 @@
         </is>
       </c>
       <c r="G70" s="25" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H70" s="26" t="n"/>
       <c r="I70" s="26">
@@ -17646,9 +17642,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K70" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
@@ -17665,13 +17661,14 @@
         </is>
       </c>
       <c r="D71" s="17" t="n"/>
-      <c r="E71" s="29">
-        <f> S04 6.35×3.0 ≈19 + S03a 2×3.6×~2.0 ≈14 = 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
-        <v/>
+      <c r="E71" s="29" t="inlineStr">
+        <is>
+          <t>3 strany trapézu (6010-1000 dveře)+(7000-600 prefa)+(7033-600 prefa)=17843 mm = 17.84 m × výška 14 řad×0.25 = 3.5 m = 62.5 m²</t>
+        </is>
       </c>
       <c r="F71" s="17" t="n"/>
       <c r="G71" s="30" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H71" s="17" t="n"/>
       <c r="I71" s="17" t="n"/>
@@ -17688,19 +17685,23 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D72" s="24" t="inlineStr"/>
+      <c r="D72" s="24" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
       <c r="E72" s="24" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G72" s="25" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H72" s="26" t="n"/>
       <c r="I72" s="26">
@@ -17712,9 +17713,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K72" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
+      <c r="K72" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
         </is>
       </c>
       <c r="L72" s="5" t="inlineStr">
@@ -17731,13 +17732,14 @@
         </is>
       </c>
       <c r="D73" s="17" t="n"/>
-      <c r="E73" s="29">
-        <f> plocha stěn pod terénem 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
-        <v/>
+      <c r="E73" s="29" t="inlineStr">
+        <is>
+          <t>62.5 m² × 30 kg/m² (zalití C25/30) = 1875 kg</t>
+        </is>
       </c>
       <c r="F73" s="17" t="n"/>
       <c r="G73" s="30" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H73" s="17" t="n"/>
       <c r="I73" s="17" t="n"/>
@@ -17746,170 +17748,161 @@
       <c r="L73" s="17" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="21" t="n"/>
-      <c r="C74" s="22" t="inlineStr">
+      <c r="B74" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="C74" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D74" s="24" t="inlineStr"/>
+      <c r="E74" s="24" t="inlineStr">
+        <is>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+        </is>
+      </c>
+      <c r="F74" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G74" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="H74" s="26" t="n"/>
+      <c r="I74" s="26">
+        <f>IF(H74="",0,G74*H74)</f>
+        <v/>
+      </c>
+      <c r="J74" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K74" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="17" t="n"/>
+      <c r="C75" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D75" s="17" t="n"/>
+      <c r="E75" s="29">
+        <f> S04 6.35×3.0 ≈19 + S03a 2×3.6×~2.0 ≈14 = 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="F75" s="17" t="n"/>
+      <c r="G75" s="30" t="n">
+        <v>33</v>
+      </c>
+      <c r="H75" s="17" t="n"/>
+      <c r="I75" s="17" t="n"/>
+      <c r="J75" s="17" t="n"/>
+      <c r="K75" s="17" t="n"/>
+      <c r="L75" s="17" t="n"/>
+    </row>
+    <row r="76">
+      <c r="B76" s="23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C76" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D76" s="24" t="inlineStr"/>
+      <c r="E76" s="24" t="inlineStr">
+        <is>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+        </is>
+      </c>
+      <c r="F76" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G76" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="H76" s="26" t="n"/>
+      <c r="I76" s="26">
+        <f>IF(H76="",0,G76*H76)</f>
+        <v/>
+      </c>
+      <c r="J76" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K76" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="17" t="n"/>
+      <c r="C77" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D77" s="17" t="n"/>
+      <c r="E77" s="29">
+        <f> plocha stěn pod terénem 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="F77" s="17" t="n"/>
+      <c r="G77" s="30" t="n">
+        <v>33</v>
+      </c>
+      <c r="H77" s="17" t="n"/>
+      <c r="I77" s="17" t="n"/>
+      <c r="J77" s="17" t="n"/>
+      <c r="K77" s="17" t="n"/>
+      <c r="L77" s="17" t="n"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="21" t="n"/>
+      <c r="C78" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D74" s="22" t="inlineStr">
+      <c r="D78" s="22" t="inlineStr">
         <is>
           <t>HSV-4</t>
         </is>
       </c>
-      <c r="E74" s="22" t="inlineStr">
+      <c r="E78" s="22" t="inlineStr">
         <is>
           <t>HSV-4 Vodorovné</t>
         </is>
       </c>
-      <c r="F74" s="21" t="n"/>
-      <c r="G74" s="21" t="n"/>
-      <c r="H74" s="21" t="n"/>
-      <c r="I74" s="21" t="n"/>
-      <c r="J74" s="21" t="n"/>
-      <c r="K74" s="21" t="n"/>
-      <c r="L74" s="21" t="n"/>
-    </row>
-    <row r="75">
-      <c r="B75" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="C75" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D75" s="24" t="inlineStr">
-        <is>
-          <t>762341110</t>
-        </is>
-      </c>
-      <c r="E75" s="24" t="inlineStr">
-        <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
-        </is>
-      </c>
-      <c r="F75" s="23" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G75" s="25" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="H75" s="26" t="n"/>
-      <c r="I75" s="26">
-        <f>IF(H75="",0,G75*H75)</f>
-        <v/>
-      </c>
-      <c r="J75" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L75" s="5" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="17" t="n"/>
-      <c r="C76" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D76" s="17" t="n"/>
-      <c r="E76" s="29" t="inlineStr">
-        <is>
-          <t>6.35/0.625 = 10.16 → 11 ks × 3.34 m (rozpon 3.1 + uložení) = 36.74 bm</t>
-        </is>
-      </c>
-      <c r="F76" s="17" t="n"/>
-      <c r="G76" s="30" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="H76" s="17" t="n"/>
-      <c r="I76" s="17" t="n"/>
-      <c r="J76" s="17" t="n"/>
-      <c r="K76" s="17" t="n"/>
-      <c r="L76" s="17" t="n"/>
-    </row>
-    <row r="77">
-      <c r="B77" s="23" t="n">
-        <v>21</v>
-      </c>
-      <c r="C77" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D77" s="24" t="inlineStr">
-        <is>
-          <t>762331110</t>
-        </is>
-      </c>
-      <c r="E77" s="24" t="inlineStr">
-        <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
-        </is>
-      </c>
-      <c r="F77" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G77" s="25" t="n">
-        <v>21.209</v>
-      </c>
-      <c r="H77" s="26" t="n"/>
-      <c r="I77" s="26">
-        <f>IF(H77="",0,G77*H77)</f>
-        <v/>
-      </c>
-      <c r="J77" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L77" s="5" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="17" t="n"/>
-      <c r="C78" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D78" s="17" t="n"/>
-      <c r="E78" s="29">
-        <f> 21.2 m² strop skladu</f>
-        <v/>
-      </c>
-      <c r="F78" s="17" t="n"/>
-      <c r="G78" s="30" t="n">
-        <v>21.209</v>
-      </c>
-      <c r="H78" s="17" t="n"/>
-      <c r="I78" s="17" t="n"/>
-      <c r="J78" s="17" t="n"/>
-      <c r="K78" s="17" t="n"/>
-      <c r="L78" s="17" t="n"/>
+      <c r="F78" s="21" t="n"/>
+      <c r="G78" s="21" t="n"/>
+      <c r="H78" s="21" t="n"/>
+      <c r="I78" s="21" t="n"/>
+      <c r="J78" s="21" t="n"/>
+      <c r="K78" s="21" t="n"/>
+      <c r="L78" s="21" t="n"/>
     </row>
     <row r="79">
       <c r="B79" s="23" t="n">
@@ -17922,21 +17915,21 @@
       </c>
       <c r="D79" s="24" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E79" s="24" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G79" s="25" t="n">
-        <v>22.26945</v>
+        <v>31</v>
       </c>
       <c r="H79" s="26" t="n"/>
       <c r="I79" s="26">
@@ -17969,12 +17962,12 @@
       <c r="D80" s="17" t="n"/>
       <c r="E80" s="29" t="inlineStr">
         <is>
-          <t>21.2 × 1.05 přesah</t>
+          <t>10 ks (počítáno na výkrese D.1.1.02, rozteč 625 mm po 5850) × 3.1 m rozpon = 31 bm</t>
         </is>
       </c>
       <c r="F80" s="17" t="n"/>
       <c r="G80" s="30" t="n">
-        <v>22.26945</v>
+        <v>31</v>
       </c>
       <c r="H80" s="17" t="n"/>
       <c r="I80" s="17" t="n"/>
@@ -17993,21 +17986,21 @@
       </c>
       <c r="D81" s="24" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E81" s="24" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G81" s="25" t="n">
-        <v>790</v>
+        <v>18.1</v>
       </c>
       <c r="H81" s="26" t="n"/>
       <c r="I81" s="26">
@@ -18040,12 +18033,12 @@
       <c r="D82" s="17" t="n"/>
       <c r="E82" s="29" t="inlineStr">
         <is>
-          <t>6 ks IPE180 × 7.0 m × 18.8 kg/m = 789.6 → 790 kg (výkres D.1.1.02: 6 nosníků)</t>
+          <t>strop skladu nad trámy = 5.85 × 3.1 = 18.1 m² (báze 10 trámů)</t>
         </is>
       </c>
       <c r="F82" s="17" t="n"/>
       <c r="G82" s="30" t="n">
-        <v>790</v>
+        <v>18.1</v>
       </c>
       <c r="H82" s="17" t="n"/>
       <c r="I82" s="17" t="n"/>
@@ -18064,12 +18057,12 @@
       </c>
       <c r="D83" s="24" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E83" s="24" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
@@ -18078,7 +18071,7 @@
         </is>
       </c>
       <c r="G83" s="25" t="n">
-        <v>44.6</v>
+        <v>19</v>
       </c>
       <c r="H83" s="26" t="n"/>
       <c r="I83" s="26">
@@ -18090,9 +18083,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K83" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
+      <c r="K83" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L83" s="5" t="inlineStr">
@@ -18111,12 +18104,12 @@
       <c r="D84" s="17" t="n"/>
       <c r="E84" s="29" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
+          <t>18.1 × 1.05 přesah = 19.0 m²</t>
         </is>
       </c>
       <c r="F84" s="17" t="n"/>
       <c r="G84" s="30" t="n">
-        <v>44.6</v>
+        <v>19</v>
       </c>
       <c r="H84" s="17" t="n"/>
       <c r="I84" s="17" t="n"/>
@@ -18135,12 +18128,12 @@
       </c>
       <c r="D85" s="24" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E85" s="24" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
@@ -18149,7 +18142,7 @@
         </is>
       </c>
       <c r="G85" s="25" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H85" s="26" t="n"/>
       <c r="I85" s="26">
@@ -18182,12 +18175,12 @@
       <c r="D86" s="17" t="n"/>
       <c r="E86" s="29" t="inlineStr">
         <is>
-          <t>IPE 790 kg + pororošt 630 kg = 1420 kg žárově zinkováno (IPE 6 ks)</t>
+          <t>6 ks IPE180 × 7.0 m × 18.8 kg/m = 789.6 → 790 kg (výkres D.1.1.02: 6 nosníků)</t>
         </is>
       </c>
       <c r="F86" s="17" t="n"/>
       <c r="G86" s="30" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H86" s="17" t="n"/>
       <c r="I86" s="17" t="n"/>
@@ -18196,125 +18189,146 @@
       <c r="L86" s="17" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="21" t="n"/>
-      <c r="C87" s="22" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D87" s="22" t="inlineStr">
-        <is>
-          <t>HSV-5</t>
-        </is>
-      </c>
-      <c r="E87" s="22" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + schodiště</t>
-        </is>
-      </c>
-      <c r="F87" s="21" t="n"/>
-      <c r="G87" s="21" t="n"/>
-      <c r="H87" s="21" t="n"/>
-      <c r="I87" s="21" t="n"/>
-      <c r="J87" s="21" t="n"/>
-      <c r="K87" s="21" t="n"/>
-      <c r="L87" s="21" t="n"/>
+      <c r="B87" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="C87" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>411321515</t>
+        </is>
+      </c>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G87" s="25" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H87" s="26" t="n"/>
+      <c r="I87" s="26">
+        <f>IF(H87="",0,G87*H87)</f>
+        <v/>
+      </c>
+      <c r="J87" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K87" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="B88" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="C88" s="23" t="inlineStr">
+      <c r="B88" s="17" t="n"/>
+      <c r="C88" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="n"/>
+      <c r="E88" s="29" t="inlineStr">
+        <is>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="n"/>
+      <c r="G88" s="30" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H88" s="17" t="n"/>
+      <c r="I88" s="17" t="n"/>
+      <c r="J88" s="17" t="n"/>
+      <c r="K88" s="17" t="n"/>
+      <c r="L88" s="17" t="n"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="23" t="n">
+        <v>27</v>
+      </c>
+      <c r="C89" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D88" s="24" t="inlineStr">
-        <is>
-          <t>121301101</t>
-        </is>
-      </c>
-      <c r="E88" s="24" t="inlineStr">
-        <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
-        </is>
-      </c>
-      <c r="F88" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G88" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H88" s="26" t="n"/>
-      <c r="I88" s="26">
-        <f>IF(H88="",0,G88*H88)</f>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>783201001</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G89" s="25" t="n">
+        <v>1420</v>
+      </c>
+      <c r="H89" s="26" t="n"/>
+      <c r="I89" s="26">
+        <f>IF(H89="",0,G89*H89)</f>
         <v/>
       </c>
-      <c r="J88" s="23" t="inlineStr">
+      <c r="J89" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K88" s="32" t="inlineStr">
+      <c r="K89" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L88" s="5" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + schodiště</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="17" t="n"/>
-      <c r="C89" s="28" t="inlineStr">
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="17" t="n"/>
+      <c r="C90" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D89" s="17" t="n"/>
-      <c r="E89" s="29" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
-        </is>
-      </c>
-      <c r="F89" s="17" t="n"/>
-      <c r="G89" s="30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H89" s="17" t="n"/>
-      <c r="I89" s="17" t="n"/>
-      <c r="J89" s="17" t="n"/>
-      <c r="K89" s="17" t="n"/>
-      <c r="L89" s="17" t="n"/>
-    </row>
-    <row r="90">
-      <c r="B90" s="19" t="n"/>
-      <c r="C90" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D90" s="20" t="inlineStr">
-        <is>
-          <t>PSV</t>
-        </is>
-      </c>
-      <c r="E90" s="20" t="inlineStr">
-        <is>
-          <t>Práce a dodávky PSV</t>
-        </is>
-      </c>
-      <c r="F90" s="19" t="n"/>
-      <c r="G90" s="19" t="n"/>
-      <c r="H90" s="19" t="n"/>
-      <c r="I90" s="19" t="n"/>
-      <c r="J90" s="19" t="n"/>
-      <c r="K90" s="19" t="n"/>
-      <c r="L90" s="19" t="n"/>
+      <c r="D90" s="17" t="n"/>
+      <c r="E90" s="29" t="inlineStr">
+        <is>
+          <t>IPE 790 kg + pororošt 630 kg = 1420 kg žárově zinkováno (IPE 6 ks)</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="n"/>
+      <c r="G90" s="30" t="n">
+        <v>1420</v>
+      </c>
+      <c r="H90" s="17" t="n"/>
+      <c r="I90" s="17" t="n"/>
+      <c r="J90" s="17" t="n"/>
+      <c r="K90" s="17" t="n"/>
+      <c r="L90" s="17" t="n"/>
     </row>
     <row r="91">
       <c r="B91" s="21" t="n"/>
@@ -18325,12 +18339,12 @@
       </c>
       <c r="D91" s="22" t="inlineStr">
         <is>
-          <t>PSV-76</t>
+          <t>HSV-5</t>
         </is>
       </c>
       <c r="E91" s="22" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="F91" s="21" t="n"/>
@@ -18343,7 +18357,7 @@
     </row>
     <row r="92">
       <c r="B92" s="23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C92" s="23" t="inlineStr">
         <is>
@@ -18352,21 +18366,21 @@
       </c>
       <c r="D92" s="24" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E92" s="24" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G92" s="25" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="H92" s="26" t="n"/>
       <c r="I92" s="26">
@@ -18385,7 +18399,7 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
     </row>
@@ -18399,12 +18413,12 @@
       <c r="D93" s="17" t="n"/>
       <c r="E93" s="29" t="inlineStr">
         <is>
-          <t>1 ks vstupní dveře skladu</t>
+          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
         </is>
       </c>
       <c r="F93" s="17" t="n"/>
       <c r="G93" s="30" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="H93" s="17" t="n"/>
       <c r="I93" s="17" t="n"/>
@@ -18413,212 +18427,216 @@
       <c r="L93" s="17" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="21" t="n"/>
-      <c r="C94" s="22" t="inlineStr">
+      <c r="B94" s="19" t="n"/>
+      <c r="C94" s="20" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D94" s="22" t="inlineStr">
+      <c r="D94" s="20" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="E94" s="20" t="inlineStr">
+        <is>
+          <t>Práce a dodávky PSV</t>
+        </is>
+      </c>
+      <c r="F94" s="19" t="n"/>
+      <c r="G94" s="19" t="n"/>
+      <c r="H94" s="19" t="n"/>
+      <c r="I94" s="19" t="n"/>
+      <c r="J94" s="19" t="n"/>
+      <c r="K94" s="19" t="n"/>
+      <c r="L94" s="19" t="n"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="21" t="n"/>
+      <c r="C95" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D95" s="22" t="inlineStr">
         <is>
           <t>PSV-76</t>
         </is>
       </c>
-      <c r="E94" s="22" t="inlineStr">
+      <c r="E95" s="22" t="inlineStr">
+        <is>
+          <t>PSV-76 Výplně otvorů</t>
+        </is>
+      </c>
+      <c r="F95" s="21" t="n"/>
+      <c r="G95" s="21" t="n"/>
+      <c r="H95" s="21" t="n"/>
+      <c r="I95" s="21" t="n"/>
+      <c r="J95" s="21" t="n"/>
+      <c r="K95" s="21" t="n"/>
+      <c r="L95" s="21" t="n"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="23" t="n">
+        <v>29</v>
+      </c>
+      <c r="C96" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D96" s="24" t="inlineStr">
+        <is>
+          <t>766682111</t>
+        </is>
+      </c>
+      <c r="E96" s="24" t="inlineStr">
+        <is>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+        </is>
+      </c>
+      <c r="F96" s="23" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G96" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="26" t="n"/>
+      <c r="I96" s="26">
+        <f>IF(H96="",0,G96*H96)</f>
+        <v/>
+      </c>
+      <c r="J96" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K96" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>PSV-76 Výplně otvorů</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="17" t="n"/>
+      <c r="C97" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D97" s="17" t="n"/>
+      <c r="E97" s="29" t="inlineStr">
+        <is>
+          <t>1 ks vstupní dveře skladu</t>
+        </is>
+      </c>
+      <c r="F97" s="17" t="n"/>
+      <c r="G97" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="17" t="n"/>
+      <c r="I97" s="17" t="n"/>
+      <c r="J97" s="17" t="n"/>
+      <c r="K97" s="17" t="n"/>
+      <c r="L97" s="17" t="n"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="21" t="n"/>
+      <c r="C98" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D98" s="22" t="inlineStr">
+        <is>
+          <t>PSV-76</t>
+        </is>
+      </c>
+      <c r="E98" s="22" t="inlineStr">
         <is>
           <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
-      <c r="F94" s="21" t="n"/>
-      <c r="G94" s="21" t="n"/>
-      <c r="H94" s="21" t="n"/>
-      <c r="I94" s="21" t="n"/>
-      <c r="J94" s="21" t="n"/>
-      <c r="K94" s="21" t="n"/>
-      <c r="L94" s="21" t="n"/>
-    </row>
-    <row r="95">
-      <c r="B95" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="C95" s="23" t="inlineStr">
+      <c r="F98" s="21" t="n"/>
+      <c r="G98" s="21" t="n"/>
+      <c r="H98" s="21" t="n"/>
+      <c r="I98" s="21" t="n"/>
+      <c r="J98" s="21" t="n"/>
+      <c r="K98" s="21" t="n"/>
+      <c r="L98" s="21" t="n"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="C99" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D95" s="24" t="inlineStr"/>
-      <c r="E95" s="24" t="inlineStr">
+      <c r="D99" s="24" t="inlineStr"/>
+      <c r="E99" s="24" t="inlineStr">
         <is>
           <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
-      <c r="F95" s="23" t="inlineStr">
+      <c r="F99" s="23" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="G95" s="25" t="n">
+      <c r="G99" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H95" s="26" t="n"/>
-      <c r="I95" s="26">
-        <f>IF(H95="",0,G95*H95)</f>
+      <c r="H99" s="26" t="n"/>
+      <c r="I99" s="26">
+        <f>IF(H99="",0,G99*H99)</f>
         <v/>
       </c>
-      <c r="J95" s="23" t="inlineStr">
+      <c r="J99" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K95" s="33" t="inlineStr">
+      <c r="K99" s="33" t="inlineStr">
         <is>
           <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
-      <c r="L95" s="5" t="inlineStr">
+      <c r="L99" s="5" t="inlineStr">
         <is>
           <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="17" t="n"/>
-      <c r="C96" s="28" t="inlineStr">
+    <row r="100">
+      <c r="B100" s="17" t="n"/>
+      <c r="C100" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D96" s="17" t="n"/>
-      <c r="E96" s="29">
+      <c r="D100" s="17" t="n"/>
+      <c r="E100" s="29">
         <f> 1 brána (Dodatek PD č.1)</f>
         <v/>
       </c>
-      <c r="F96" s="17" t="n"/>
-      <c r="G96" s="30" t="n">
+      <c r="F100" s="17" t="n"/>
+      <c r="G100" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H96" s="17" t="n"/>
-      <c r="I96" s="17" t="n"/>
-      <c r="J96" s="17" t="n"/>
-      <c r="K96" s="17" t="n"/>
-      <c r="L96" s="17" t="n"/>
-    </row>
-    <row r="97">
-      <c r="B97" s="21" t="n"/>
-      <c r="C97" s="22" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D97" s="22" t="inlineStr">
-        <is>
-          <t>PSV-77</t>
-        </is>
-      </c>
-      <c r="E97" s="22" t="inlineStr">
-        <is>
-          <t>PSV-77 Podlahy</t>
-        </is>
-      </c>
-      <c r="F97" s="21" t="n"/>
-      <c r="G97" s="21" t="n"/>
-      <c r="H97" s="21" t="n"/>
-      <c r="I97" s="21" t="n"/>
-      <c r="J97" s="21" t="n"/>
-      <c r="K97" s="21" t="n"/>
-      <c r="L97" s="21" t="n"/>
-    </row>
-    <row r="98">
-      <c r="B98" s="23" t="n">
-        <v>29</v>
-      </c>
-      <c r="C98" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D98" s="24" t="inlineStr"/>
-      <c r="E98" s="24" t="inlineStr">
-        <is>
-          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
-        </is>
-      </c>
-      <c r="F98" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G98" s="25" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="H98" s="26" t="n"/>
-      <c r="I98" s="26">
-        <f>IF(H98="",0,G98*H98)</f>
-        <v/>
-      </c>
-      <c r="J98" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K98" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
-        </is>
-      </c>
-      <c r="L98" s="5" t="inlineStr">
-        <is>
-          <t>PSV-77 Podlahy</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="17" t="n"/>
-      <c r="C99" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D99" s="17" t="n"/>
-      <c r="E99" s="29" t="inlineStr">
-        <is>
-          <t>plocha S01 = místnost 17.6 (legenda) + vynos za stěnu 6.0 (6010×1000 řez) = 23.6 m²</t>
-        </is>
-      </c>
-      <c r="F99" s="17" t="n"/>
-      <c r="G99" s="30" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="H99" s="17" t="n"/>
-      <c r="I99" s="17" t="n"/>
-      <c r="J99" s="17" t="n"/>
-      <c r="K99" s="17" t="n"/>
-      <c r="L99" s="17" t="n"/>
-    </row>
-    <row r="100">
-      <c r="B100" s="19" t="n"/>
-      <c r="C100" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D100" s="20" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E100" s="20" t="inlineStr">
-        <is>
-          <t>Vedlejší rozpočtové náklady</t>
-        </is>
-      </c>
-      <c r="F100" s="19" t="n"/>
-      <c r="G100" s="19" t="n"/>
-      <c r="H100" s="19" t="n"/>
-      <c r="I100" s="19" t="n"/>
-      <c r="J100" s="19" t="n"/>
-      <c r="K100" s="19" t="n"/>
-      <c r="L100" s="19" t="n"/>
+      <c r="H100" s="17" t="n"/>
+      <c r="I100" s="17" t="n"/>
+      <c r="J100" s="17" t="n"/>
+      <c r="K100" s="17" t="n"/>
+      <c r="L100" s="17" t="n"/>
     </row>
     <row r="101">
       <c r="B101" s="21" t="n"/>
@@ -18629,12 +18647,12 @@
       </c>
       <c r="D101" s="22" t="inlineStr">
         <is>
-          <t>VRN</t>
+          <t>PSV-77</t>
         </is>
       </c>
       <c r="E101" s="22" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="F101" s="21" t="n"/>
@@ -18647,30 +18665,26 @@
     </row>
     <row r="102">
       <c r="B102" s="23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C102" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D102" s="24" t="inlineStr">
-        <is>
-          <t>030001000</t>
-        </is>
-      </c>
+      <c r="D102" s="24" t="inlineStr"/>
       <c r="E102" s="24" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G102" s="25" t="n">
-        <v>1</v>
+        <v>23.6</v>
       </c>
       <c r="H102" s="26" t="n"/>
       <c r="I102" s="26">
@@ -18682,14 +18696,14 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K102" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K102" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
     </row>
@@ -18703,12 +18717,12 @@
       <c r="D103" s="17" t="n"/>
       <c r="E103" s="29" t="inlineStr">
         <is>
-          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+          <t>plocha S01 = místnost 17.6 (legenda) + vynos za stěnu 6.0 (6010×1000 řez) = 23.6 m²</t>
         </is>
       </c>
       <c r="F103" s="17" t="n"/>
       <c r="G103" s="30" t="n">
-        <v>1</v>
+        <v>23.6</v>
       </c>
       <c r="H103" s="17" t="n"/>
       <c r="I103" s="17" t="n"/>
@@ -18717,267 +18731,388 @@
       <c r="L103" s="17" t="n"/>
     </row>
     <row r="104">
-      <c r="B104" s="21" t="n"/>
-      <c r="C104" s="22" t="inlineStr">
+      <c r="B104" s="19" t="n"/>
+      <c r="C104" s="20" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D104" s="22" t="inlineStr">
+      <c r="D104" s="20" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E104" s="22" t="inlineStr">
+      <c r="E104" s="20" t="inlineStr">
+        <is>
+          <t>Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="F104" s="19" t="n"/>
+      <c r="G104" s="19" t="n"/>
+      <c r="H104" s="19" t="n"/>
+      <c r="I104" s="19" t="n"/>
+      <c r="J104" s="19" t="n"/>
+      <c r="K104" s="19" t="n"/>
+      <c r="L104" s="19" t="n"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="21" t="n"/>
+      <c r="C105" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E105" s="22" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="F105" s="21" t="n"/>
+      <c r="G105" s="21" t="n"/>
+      <c r="H105" s="21" t="n"/>
+      <c r="I105" s="21" t="n"/>
+      <c r="J105" s="21" t="n"/>
+      <c r="K105" s="21" t="n"/>
+      <c r="L105" s="21" t="n"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="C106" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D106" s="24" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E106" s="24" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F106" s="23" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G106" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="26" t="n"/>
+      <c r="I106" s="26">
+        <f>IF(H106="",0,G106*H106)</f>
+        <v/>
+      </c>
+      <c r="J106" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K106" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L106" s="5" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="17" t="n"/>
+      <c r="C107" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D107" s="17" t="n"/>
+      <c r="E107" s="29" t="inlineStr">
+        <is>
+          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+        </is>
+      </c>
+      <c r="F107" s="17" t="n"/>
+      <c r="G107" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" s="17" t="n"/>
+      <c r="I107" s="17" t="n"/>
+      <c r="J107" s="17" t="n"/>
+      <c r="K107" s="17" t="n"/>
+      <c r="L107" s="17" t="n"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="21" t="n"/>
+      <c r="C108" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D108" s="22" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E108" s="22" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
-      <c r="F104" s="21" t="n"/>
-      <c r="G104" s="21" t="n"/>
-      <c r="H104" s="21" t="n"/>
-      <c r="I104" s="21" t="n"/>
-      <c r="J104" s="21" t="n"/>
-      <c r="K104" s="21" t="n"/>
-      <c r="L104" s="21" t="n"/>
-    </row>
-    <row r="105">
-      <c r="B105" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="C105" s="23" t="inlineStr">
+      <c r="F108" s="21" t="n"/>
+      <c r="G108" s="21" t="n"/>
+      <c r="H108" s="21" t="n"/>
+      <c r="I108" s="21" t="n"/>
+      <c r="J108" s="21" t="n"/>
+      <c r="K108" s="21" t="n"/>
+      <c r="L108" s="21" t="n"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="23" t="n">
+        <v>33</v>
+      </c>
+      <c r="C109" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D105" s="24" t="inlineStr">
+      <c r="D109" s="24" t="inlineStr">
         <is>
           <t>031032000</t>
         </is>
       </c>
-      <c r="E105" s="24" t="inlineStr">
+      <c r="E109" s="24" t="inlineStr">
         <is>
           <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
-      <c r="F105" s="23" t="inlineStr">
+      <c r="F109" s="23" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="G105" s="25" t="n">
+      <c r="G109" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H105" s="26" t="n"/>
-      <c r="I105" s="26">
-        <f>IF(H105="",0,G105*H105)</f>
+      <c r="H109" s="26" t="n"/>
+      <c r="I109" s="26">
+        <f>IF(H109="",0,G109*H109)</f>
         <v/>
       </c>
-      <c r="J105" s="23" t="inlineStr">
+      <c r="J109" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K105" s="32" t="inlineStr">
+      <c r="K109" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L105" s="5" t="inlineStr">
+      <c r="L109" s="5" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="B106" s="17" t="n"/>
-      <c r="C106" s="28" t="inlineStr">
+    <row r="110">
+      <c r="B110" s="17" t="n"/>
+      <c r="C110" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D106" s="17" t="n"/>
-      <c r="E106" s="29" t="inlineStr">
+      <c r="D110" s="17" t="n"/>
+      <c r="E110" s="29" t="inlineStr">
         <is>
           <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
         </is>
       </c>
-      <c r="F106" s="17" t="n"/>
-      <c r="G106" s="30" t="n">
+      <c r="F110" s="17" t="n"/>
+      <c r="G110" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H106" s="17" t="n"/>
-      <c r="I106" s="17" t="n"/>
-      <c r="J106" s="17" t="n"/>
-      <c r="K106" s="17" t="n"/>
-      <c r="L106" s="17" t="n"/>
-    </row>
-    <row r="107">
-      <c r="B107" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="C107" s="23" t="inlineStr">
+      <c r="H110" s="17" t="n"/>
+      <c r="I110" s="17" t="n"/>
+      <c r="J110" s="17" t="n"/>
+      <c r="K110" s="17" t="n"/>
+      <c r="L110" s="17" t="n"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="C111" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D107" s="24" t="inlineStr">
+      <c r="D111" s="24" t="inlineStr">
         <is>
           <t>997013211</t>
         </is>
       </c>
-      <c r="E107" s="24" t="inlineStr">
+      <c r="E111" s="24" t="inlineStr">
         <is>
           <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
-      <c r="F107" s="23" t="inlineStr">
+      <c r="F111" s="23" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
-      <c r="G107" s="25" t="n">
+      <c r="G111" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="H107" s="26" t="n"/>
-      <c r="I107" s="26">
-        <f>IF(H107="",0,G107*H107)</f>
+      <c r="H111" s="26" t="n"/>
+      <c r="I111" s="26">
+        <f>IF(H111="",0,G111*H111)</f>
         <v/>
       </c>
-      <c r="J107" s="23" t="inlineStr">
+      <c r="J111" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K107" s="32" t="inlineStr">
+      <c r="K111" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L107" s="5" t="inlineStr">
+      <c r="L111" s="5" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="B108" s="17" t="n"/>
-      <c r="C108" s="28" t="inlineStr">
+    <row r="112">
+      <c r="B112" s="17" t="n"/>
+      <c r="C112" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D108" s="17" t="n"/>
-      <c r="E108" s="29" t="inlineStr">
+      <c r="D112" s="17" t="n"/>
+      <c r="E112" s="29" t="inlineStr">
         <is>
           <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
         </is>
       </c>
-      <c r="F108" s="17" t="n"/>
-      <c r="G108" s="30" t="n">
+      <c r="F112" s="17" t="n"/>
+      <c r="G112" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="H108" s="17" t="n"/>
-      <c r="I108" s="17" t="n"/>
-      <c r="J108" s="17" t="n"/>
-      <c r="K108" s="17" t="n"/>
-      <c r="L108" s="17" t="n"/>
-    </row>
-    <row r="109">
-      <c r="B109" s="21" t="n"/>
-      <c r="C109" s="22" t="inlineStr">
+      <c r="H112" s="17" t="n"/>
+      <c r="I112" s="17" t="n"/>
+      <c r="J112" s="17" t="n"/>
+      <c r="K112" s="17" t="n"/>
+      <c r="L112" s="17" t="n"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="21" t="n"/>
+      <c r="C113" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D109" s="22" t="inlineStr">
+      <c r="D113" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E109" s="22" t="inlineStr">
+      <c r="E113" s="22" t="inlineStr">
         <is>
           <t>VRN — Geodet</t>
         </is>
       </c>
-      <c r="F109" s="21" t="n"/>
-      <c r="G109" s="21" t="n"/>
-      <c r="H109" s="21" t="n"/>
-      <c r="I109" s="21" t="n"/>
-      <c r="J109" s="21" t="n"/>
-      <c r="K109" s="21" t="n"/>
-      <c r="L109" s="21" t="n"/>
-    </row>
-    <row r="110">
-      <c r="B110" s="23" t="n">
-        <v>33</v>
-      </c>
-      <c r="C110" s="23" t="inlineStr">
+      <c r="F113" s="21" t="n"/>
+      <c r="G113" s="21" t="n"/>
+      <c r="H113" s="21" t="n"/>
+      <c r="I113" s="21" t="n"/>
+      <c r="J113" s="21" t="n"/>
+      <c r="K113" s="21" t="n"/>
+      <c r="L113" s="21" t="n"/>
+    </row>
+    <row r="114">
+      <c r="B114" s="23" t="n">
+        <v>35</v>
+      </c>
+      <c r="C114" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D110" s="24" t="inlineStr">
+      <c r="D114" s="24" t="inlineStr">
         <is>
           <t>030141000</t>
         </is>
       </c>
-      <c r="E110" s="24" t="inlineStr">
+      <c r="E114" s="24" t="inlineStr">
         <is>
           <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
-      <c r="F110" s="23" t="inlineStr">
+      <c r="F114" s="23" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="G110" s="25" t="n">
+      <c r="G114" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H110" s="26" t="n"/>
-      <c r="I110" s="26">
-        <f>IF(H110="",0,G110*H110)</f>
+      <c r="H114" s="26" t="n"/>
+      <c r="I114" s="26">
+        <f>IF(H114="",0,G114*H114)</f>
         <v/>
       </c>
-      <c r="J110" s="23" t="inlineStr">
+      <c r="J114" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K110" s="32" t="inlineStr">
+      <c r="K114" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L110" s="5" t="inlineStr">
+      <c r="L114" s="5" t="inlineStr">
         <is>
           <t>VRN — Geodet</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="B111" s="17" t="n"/>
-      <c r="C111" s="28" t="inlineStr">
+    <row r="115">
+      <c r="B115" s="17" t="n"/>
+      <c r="C115" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D111" s="17" t="n"/>
-      <c r="E111" s="29" t="inlineStr">
+      <c r="D115" s="17" t="n"/>
+      <c r="E115" s="29" t="inlineStr">
         <is>
           <t>Standard geodet vytýčení pro nový objekt</t>
         </is>
       </c>
-      <c r="F111" s="17" t="n"/>
-      <c r="G111" s="30" t="n">
+      <c r="F115" s="17" t="n"/>
+      <c r="G115" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H111" s="17" t="n"/>
-      <c r="I111" s="17" t="n"/>
-      <c r="J111" s="17" t="n"/>
-      <c r="K111" s="17" t="n"/>
-      <c r="L111" s="17" t="n"/>
+      <c r="H115" s="17" t="n"/>
+      <c r="I115" s="17" t="n"/>
+      <c r="J115" s="17" t="n"/>
+      <c r="K115" s="17" t="n"/>
+      <c r="L115" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -19003,7 +19138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H257"/>
+  <dimension ref="B2:H266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -19082,7 +19217,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -19092,7 +19227,7 @@
         </is>
       </c>
       <c r="C10" s="34" t="n">
-        <v>234</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13">
@@ -26080,7 +26215,7 @@
       <c r="F229" s="24" t="inlineStr"/>
       <c r="G229" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 </t>
+          <t xml:space="preserve">Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 </t>
         </is>
       </c>
       <c r="H229" s="24" t="inlineStr">
@@ -26593,7 +26728,7 @@
       <c r="F246" s="24" t="inlineStr"/>
       <c r="G246" s="24" t="inlineStr">
         <is>
-          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic +</t>
+          <t xml:space="preserve">Vjezd Dvořákova (POZN 01) — zpevněná plocha z hladké betonové dlažby, </t>
         </is>
       </c>
       <c r="H246" s="24" t="inlineStr">
@@ -26924,6 +27059,283 @@
         </is>
       </c>
       <c r="H257" s="24" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.003</t>
+        </is>
+      </c>
+      <c r="C258" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D258" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="E258" s="24" t="inlineStr">
+        <is>
+          <t>564751111</t>
+        </is>
+      </c>
+      <c r="F258" s="24" t="inlineStr"/>
+      <c r="G258" s="24" t="inlineStr">
+        <is>
+          <t>Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
+        </is>
+      </c>
+      <c r="H258" s="24" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.004</t>
+        </is>
+      </c>
+      <c r="C259" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D259" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="E259" s="24" t="inlineStr">
+        <is>
+          <t>564861111</t>
+        </is>
+      </c>
+      <c r="F259" s="24" t="inlineStr"/>
+      <c r="G259" s="24" t="inlineStr">
+        <is>
+          <t>Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
+        </is>
+      </c>
+      <c r="H259" s="24" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.005</t>
+        </is>
+      </c>
+      <c r="C260" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D260" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="E260" s="24" t="inlineStr"/>
+      <c r="F260" s="24" t="inlineStr"/>
+      <c r="G260" s="24" t="inlineStr">
+        <is>
+          <t>Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
+        </is>
+      </c>
+      <c r="H260" s="24" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.006</t>
+        </is>
+      </c>
+      <c r="C261" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D261" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="E261" s="24" t="inlineStr">
+        <is>
+          <t>273321411</t>
+        </is>
+      </c>
+      <c r="F261" s="24" t="inlineStr"/>
+      <c r="G261" s="24" t="inlineStr">
+        <is>
+          <t>Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
+        </is>
+      </c>
+      <c r="H261" s="24" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.007</t>
+        </is>
+      </c>
+      <c r="C262" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D262" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="E262" s="24" t="inlineStr"/>
+      <c r="F262" s="24" t="inlineStr"/>
+      <c r="G262" s="24" t="inlineStr">
+        <is>
+          <t>Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="H262" s="24" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV1.009</t>
+        </is>
+      </c>
+      <c r="C263" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D263" s="24" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="E263" s="24" t="inlineStr"/>
+      <c r="F263" s="24" t="inlineStr"/>
+      <c r="G263" s="24" t="inlineStr">
+        <is>
+          <t>Trubka Ø ~150 mm v štěrkovém obsypu podél vysokého pasu — drenáž/odvět</t>
+        </is>
+      </c>
+      <c r="H263" s="24" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV1.010</t>
+        </is>
+      </c>
+      <c r="C264" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D264" s="24" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="E264" s="24" t="inlineStr"/>
+      <c r="F264" s="24" t="inlineStr"/>
+      <c r="G264" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trubka Ø 120-130 mm v štěrkovém obsypu podél stěny — drenáž/odvětrání </t>
+        </is>
+      </c>
+      <c r="H264" s="24" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.008</t>
+        </is>
+      </c>
+      <c r="C265" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D265" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="E265" s="24" t="inlineStr">
+        <is>
+          <t>273313611</t>
+        </is>
+      </c>
+      <c r="F265" s="24" t="inlineStr"/>
+      <c r="G265" s="24" t="inlineStr">
+        <is>
+          <t>Podkladní betonová deska pod prefa schodiště S05</t>
+        </is>
+      </c>
+      <c r="H265" s="24" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.009</t>
+        </is>
+      </c>
+      <c r="C266" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D266" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="E266" s="24" t="inlineStr"/>
+      <c r="F266" s="24" t="inlineStr"/>
+      <c r="G266" s="24" t="inlineStr">
+        <is>
+          <t>Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
+        </is>
+      </c>
+      <c r="H266" s="24" t="inlineStr">
         <is>
           <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
@@ -26951,7 +27363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N238"/>
+  <dimension ref="B2:N247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -36110,7 +36522,7 @@
       </c>
       <c r="D210" s="24" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + klad</t>
+          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipode</t>
         </is>
       </c>
       <c r="E210" s="24" t="inlineStr">
@@ -36743,7 +37155,7 @@
       </c>
       <c r="D227" s="24" t="inlineStr">
         <is>
-          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování</t>
+          <t>Vjezd Dvořákova (POZN 01) — zpevněná plocha z hladké betonové dlažby, napojení n</t>
         </is>
       </c>
       <c r="E227" s="24" t="inlineStr"/>
@@ -37134,6 +37546,319 @@
       <c r="M238" s="24" t="inlineStr"/>
       <c r="N238" s="24" t="inlineStr"/>
     </row>
+    <row r="239">
+      <c r="B239" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.003</t>
+        </is>
+      </c>
+      <c r="C239" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="D239" s="24" t="inlineStr">
+        <is>
+          <t>Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
+        </is>
+      </c>
+      <c r="E239" s="24" t="inlineStr">
+        <is>
+          <t>564751111</t>
+        </is>
+      </c>
+      <c r="F239" s="24" t="inlineStr"/>
+      <c r="G239" s="24" t="inlineStr"/>
+      <c r="H239" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I239" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J239" s="32" t="inlineStr"/>
+      <c r="K239" s="24" t="inlineStr"/>
+      <c r="L239" s="24" t="inlineStr"/>
+      <c r="M239" s="24" t="inlineStr"/>
+      <c r="N239" s="24" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="B240" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.004</t>
+        </is>
+      </c>
+      <c r="C240" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="D240" s="24" t="inlineStr">
+        <is>
+          <t>Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
+        </is>
+      </c>
+      <c r="E240" s="24" t="inlineStr">
+        <is>
+          <t>564861111</t>
+        </is>
+      </c>
+      <c r="F240" s="24" t="inlineStr"/>
+      <c r="G240" s="24" t="inlineStr"/>
+      <c r="H240" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I240" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J240" s="32" t="inlineStr"/>
+      <c r="K240" s="24" t="inlineStr"/>
+      <c r="L240" s="24" t="inlineStr"/>
+      <c r="M240" s="24" t="inlineStr"/>
+      <c r="N240" s="24" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="B241" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.005</t>
+        </is>
+      </c>
+      <c r="C241" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="D241" s="24" t="inlineStr">
+        <is>
+          <t>Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
+        </is>
+      </c>
+      <c r="E241" s="24" t="inlineStr"/>
+      <c r="F241" s="24" t="inlineStr"/>
+      <c r="G241" s="24" t="inlineStr"/>
+      <c r="H241" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I241" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J241" s="33" t="inlineStr"/>
+      <c r="K241" s="24" t="inlineStr"/>
+      <c r="L241" s="24" t="inlineStr"/>
+      <c r="M241" s="24" t="inlineStr"/>
+      <c r="N241" s="24" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="B242" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.006</t>
+        </is>
+      </c>
+      <c r="C242" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="D242" s="24" t="inlineStr">
+        <is>
+          <t>Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
+        </is>
+      </c>
+      <c r="E242" s="24" t="inlineStr">
+        <is>
+          <t>273321411</t>
+        </is>
+      </c>
+      <c r="F242" s="24" t="inlineStr"/>
+      <c r="G242" s="24" t="inlineStr"/>
+      <c r="H242" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I242" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J242" s="32" t="inlineStr"/>
+      <c r="K242" s="24" t="inlineStr"/>
+      <c r="L242" s="24" t="inlineStr"/>
+      <c r="M242" s="24" t="inlineStr"/>
+      <c r="N242" s="24" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="B243" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.007</t>
+        </is>
+      </c>
+      <c r="C243" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="D243" s="24" t="inlineStr">
+        <is>
+          <t>Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="E243" s="24" t="inlineStr"/>
+      <c r="F243" s="24" t="inlineStr"/>
+      <c r="G243" s="24" t="inlineStr"/>
+      <c r="H243" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I243" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J243" s="33" t="inlineStr"/>
+      <c r="K243" s="24" t="inlineStr"/>
+      <c r="L243" s="24" t="inlineStr"/>
+      <c r="M243" s="24" t="inlineStr"/>
+      <c r="N243" s="24" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="B244" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV1.009</t>
+        </is>
+      </c>
+      <c r="C244" s="24" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="D244" s="24" t="inlineStr">
+        <is>
+          <t>Trubka Ø ~150 mm v štěrkovém obsypu podél vysokého pasu — drenáž/odvětrání radon</t>
+        </is>
+      </c>
+      <c r="E244" s="24" t="inlineStr"/>
+      <c r="F244" s="24" t="inlineStr"/>
+      <c r="G244" s="24" t="inlineStr"/>
+      <c r="H244" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I244" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J244" s="33" t="inlineStr"/>
+      <c r="K244" s="24" t="inlineStr"/>
+      <c r="L244" s="24" t="inlineStr"/>
+      <c r="M244" s="24" t="inlineStr"/>
+      <c r="N244" s="24" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="B245" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV1.010</t>
+        </is>
+      </c>
+      <c r="C245" s="24" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="D245" s="24" t="inlineStr">
+        <is>
+          <t>Trubka Ø 120-130 mm v štěrkovém obsypu podél stěny — drenáž/odvětrání radonu (OV</t>
+        </is>
+      </c>
+      <c r="E245" s="24" t="inlineStr"/>
+      <c r="F245" s="24" t="inlineStr"/>
+      <c r="G245" s="24" t="inlineStr"/>
+      <c r="H245" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I245" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J245" s="33" t="inlineStr"/>
+      <c r="K245" s="24" t="inlineStr"/>
+      <c r="L245" s="24" t="inlineStr"/>
+      <c r="M245" s="24" t="inlineStr"/>
+      <c r="N245" s="24" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="B246" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.008</t>
+        </is>
+      </c>
+      <c r="C246" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="D246" s="24" t="inlineStr">
+        <is>
+          <t>Podkladní betonová deska pod prefa schodiště S05</t>
+        </is>
+      </c>
+      <c r="E246" s="24" t="inlineStr">
+        <is>
+          <t>273313611</t>
+        </is>
+      </c>
+      <c r="F246" s="24" t="inlineStr"/>
+      <c r="G246" s="24" t="inlineStr"/>
+      <c r="H246" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I246" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J246" s="32" t="inlineStr"/>
+      <c r="K246" s="24" t="inlineStr"/>
+      <c r="L246" s="24" t="inlineStr"/>
+      <c r="M246" s="24" t="inlineStr"/>
+      <c r="N246" s="24" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="B247" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.009</t>
+        </is>
+      </c>
+      <c r="C247" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="D247" s="24" t="inlineStr">
+        <is>
+          <t>Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
+        </is>
+      </c>
+      <c r="E247" s="24" t="inlineStr"/>
+      <c r="F247" s="24" t="inlineStr"/>
+      <c r="G247" s="24" t="inlineStr"/>
+      <c r="H247" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I247" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J247" s="33" t="inlineStr"/>
+      <c r="K247" s="24" t="inlineStr"/>
+      <c r="L247" s="24" t="inlineStr"/>
+      <c r="M247" s="24" t="inlineStr"/>
+      <c r="N247" s="24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-02_v3_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-02_v3_final.xlsx
@@ -17241,7 +17241,7 @@
       </c>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Patky parking horní část — zdivo z tvárnic ztraceného bednění 300×300 mm (lost formwork, zůstává v konstrukci), 6 patek á 300×300×500 mm</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
@@ -17283,7 +17283,7 @@
       <c r="D60" s="17" t="n"/>
       <c r="E60" s="29" t="inlineStr">
         <is>
-          <t>6 ks (= spodní, výkres D.1.1.02)</t>
+          <t>6 patek horní á 300×300×500 mm = 6 sloupků z tvárnic ZB 300×300 (á 2 řady po 250 = 12 tvárnic); zálivka C25/30 + výztuž samostatně (HSV2.004 / HSV3.003)</t>
         </is>
       </c>
       <c r="F60" s="17" t="n"/>
@@ -21954,7 +21954,7 @@
       <c r="F100" s="24" t="inlineStr"/>
       <c r="G100" s="24" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bedně</t>
+          <t xml:space="preserve">Patky parking horní část — zdivo z tvárnic ztraceného bednění 300×300 </t>
         </is>
       </c>
       <c r="H100" s="24" t="inlineStr">
@@ -28874,7 +28874,7 @@
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300</t>
+          <t>Patky parking horní část — zdivo z tvárnic ztraceného bednění 300×300 mm (lost f</t>
         </is>
       </c>
       <c r="E34" s="24" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-02_v3_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-02_v3_final.xlsx
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <f>SUM('SO_260217_Sklad'!I34:I114)</f>
+        <f>SUM('SO_260217_Sklad'!I34:I118)</f>
         <v/>
       </c>
       <c r="E15" s="7">
@@ -15954,7 +15954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L115"/>
+  <dimension ref="B2:L119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -16115,7 +16115,7 @@
         </is>
       </c>
       <c r="D16" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C16)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C16)</f>
         <v/>
       </c>
     </row>
@@ -16127,7 +16127,7 @@
         </is>
       </c>
       <c r="D17" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C17)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C17)</f>
         <v/>
       </c>
     </row>
@@ -16139,7 +16139,7 @@
         </is>
       </c>
       <c r="D18" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C18)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C18)</f>
         <v/>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
         </is>
       </c>
       <c r="D19" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C19)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C19)</f>
         <v/>
       </c>
     </row>
@@ -16163,7 +16163,7 @@
         </is>
       </c>
       <c r="D20" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C20)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C20)</f>
         <v/>
       </c>
     </row>
@@ -16175,7 +16175,7 @@
         </is>
       </c>
       <c r="D21" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C21)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C21)</f>
         <v/>
       </c>
     </row>
@@ -16187,7 +16187,7 @@
         </is>
       </c>
       <c r="D22" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C22)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C22)</f>
         <v/>
       </c>
     </row>
@@ -16199,7 +16199,7 @@
         </is>
       </c>
       <c r="D23" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C23)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C23)</f>
         <v/>
       </c>
     </row>
@@ -16211,7 +16211,7 @@
         </is>
       </c>
       <c r="D24" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C24)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C24)</f>
         <v/>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
         </is>
       </c>
       <c r="D25" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C25)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C25)</f>
         <v/>
       </c>
     </row>
@@ -16235,7 +16235,7 @@
         </is>
       </c>
       <c r="D26" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C26)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C26)</f>
         <v/>
       </c>
     </row>
@@ -17321,7 +17321,7 @@
         </is>
       </c>
       <c r="G61" s="25" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H61" s="26" t="n"/>
       <c r="I61" s="26">
@@ -17354,12 +17354,12 @@
       <c r="D62" s="17" t="n"/>
       <c r="E62" s="29" t="inlineStr">
         <is>
-          <t>patky horní (0.3×0.3×0.5×6 = 0.27) + věnec nad patkami 2 řady ztrac.bednění (0.5 v × 6.35 d × 0.3 š = 0.95) + zídka lemující (~0.5) = ~1.72 ≈ 1.75 m³</t>
+          <t>zálivka tvárnic ZB: patky horní (0.3×0.3×0.5×6=0.27) + věnec 2 řady (2×0.25 v × 0.3 š × 6.7 d=1.00) + zídka lemující (~0.5) = 1.77 m³</t>
         </is>
       </c>
       <c r="F62" s="17" t="n"/>
       <c r="G62" s="30" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H62" s="17" t="n"/>
       <c r="I62" s="17" t="n"/>
@@ -17510,171 +17510,171 @@
       <c r="L66" s="17" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="21" t="n"/>
-      <c r="C67" s="22" t="inlineStr">
+      <c r="B67" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="C67" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D67" s="24" t="inlineStr">
+        <is>
+          <t>273351215</t>
+        </is>
+      </c>
+      <c r="E67" s="24" t="inlineStr">
+        <is>
+          <t>Bednění základových pasů + spodních patek (prostý beton) — tradiční / systémové, oboustranné kde nelze betonovat do rýhy</t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G67" s="25" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="H67" s="26" t="n"/>
+      <c r="I67" s="26">
+        <f>IF(H67="",0,G67*H67)</f>
+        <v/>
+      </c>
+      <c r="J67" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="17" t="n"/>
+      <c r="C68" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="n"/>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>patky spodní 6×4×0.5×0.5=6.0 + pasy 2 strany×0.5×19.4 obvod=19.4 = 25.4 m² (část lze betonovat do rýhy → OVĚŘIT)</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="n"/>
+      <c r="G68" s="30" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="H68" s="17" t="n"/>
+      <c r="I68" s="17" t="n"/>
+      <c r="J68" s="17" t="n"/>
+      <c r="K68" s="17" t="n"/>
+      <c r="L68" s="17" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="C69" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D69" s="24" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
+      <c r="E69" s="24" t="inlineStr">
+        <is>
+          <t>Výztuž B500B vkládaná do tvárnic ztraceného bednění — patky horní (6 sloupků) + ztužující věnec nad patkami</t>
+        </is>
+      </c>
+      <c r="F69" s="23" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G69" s="25" t="n">
+        <v>153</v>
+      </c>
+      <c r="H69" s="26" t="n"/>
+      <c r="I69" s="26">
+        <f>IF(H69="",0,G69*H69)</f>
+        <v/>
+      </c>
+      <c r="J69" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="17" t="n"/>
+      <c r="C70" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="n"/>
+      <c r="E70" s="29" t="inlineStr">
+        <is>
+          <t>zálivka tvárnic ZB 1.27 m³ (patky horní 0.27 + věnec 1.00) × 120 kg/m³ (= stěna 30 kg/m² ÷ 0.25) = 153 kg</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="n"/>
+      <c r="G70" s="30" t="n">
+        <v>153</v>
+      </c>
+      <c r="H70" s="17" t="n"/>
+      <c r="I70" s="17" t="n"/>
+      <c r="J70" s="17" t="n"/>
+      <c r="K70" s="17" t="n"/>
+      <c r="L70" s="17" t="n"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="21" t="n"/>
+      <c r="C71" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D67" s="22" t="inlineStr">
+      <c r="D71" s="22" t="inlineStr">
         <is>
           <t>HSV-3</t>
         </is>
       </c>
-      <c r="E67" s="22" t="inlineStr">
+      <c r="E71" s="22" t="inlineStr">
         <is>
           <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
-      <c r="F67" s="21" t="n"/>
-      <c r="G67" s="21" t="n"/>
-      <c r="H67" s="21" t="n"/>
-      <c r="I67" s="21" t="n"/>
-      <c r="J67" s="21" t="n"/>
-      <c r="K67" s="21" t="n"/>
-      <c r="L67" s="21" t="n"/>
-    </row>
-    <row r="68">
-      <c r="B68" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="C68" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D68" s="24" t="inlineStr">
-        <is>
-          <t>311233815</t>
-        </is>
-      </c>
-      <c r="E68" s="24" t="inlineStr">
-        <is>
-          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
-        </is>
-      </c>
-      <c r="F68" s="23" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G68" s="25" t="n">
-        <v>18</v>
-      </c>
-      <c r="H68" s="26" t="n"/>
-      <c r="I68" s="26">
-        <f>IF(H68="",0,G68*H68)</f>
-        <v/>
-      </c>
-      <c r="J68" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L68" s="5" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="17" t="n"/>
-      <c r="C69" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D69" s="17" t="n"/>
-      <c r="E69" s="29" t="inlineStr">
-        <is>
-          <t>S04 líc 6.35 × 3.0 m = 19.05 m²; blok 1800×600 mm (výkres D.1.1.02/03: délka 1800, 5 řad × 600 výška = 3000) → 3 celé (1800×3=5400) + 1 kus 950 mm na řadu, vazba na zámek; 5 řad × ~3.5 bloku ≈ 18 ks</t>
-        </is>
-      </c>
-      <c r="F69" s="17" t="n"/>
-      <c r="G69" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="H69" s="17" t="n"/>
-      <c r="I69" s="17" t="n"/>
-      <c r="J69" s="17" t="n"/>
-      <c r="K69" s="17" t="n"/>
-      <c r="L69" s="17" t="n"/>
-    </row>
-    <row r="70">
-      <c r="B70" s="23" t="n">
-        <v>18</v>
-      </c>
-      <c r="C70" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D70" s="24" t="inlineStr">
-        <is>
-          <t>311233811</t>
-        </is>
-      </c>
-      <c r="E70" s="24" t="inlineStr">
-        <is>
-          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
-        </is>
-      </c>
-      <c r="F70" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G70" s="25" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="H70" s="26" t="n"/>
-      <c r="I70" s="26">
-        <f>IF(H70="",0,G70*H70)</f>
-        <v/>
-      </c>
-      <c r="J70" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L70" s="5" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="17" t="n"/>
-      <c r="C71" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D71" s="17" t="n"/>
-      <c r="E71" s="29" t="inlineStr">
-        <is>
-          <t>3 strany trapézu (6010-1000 dveře)+(7000-600 prefa)+(7033-600 prefa)=17843 mm = 17.84 m × výška 14 řad×0.25 = 3.5 m = 62.5 m²</t>
-        </is>
-      </c>
-      <c r="F71" s="17" t="n"/>
-      <c r="G71" s="30" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="H71" s="17" t="n"/>
-      <c r="I71" s="17" t="n"/>
-      <c r="J71" s="17" t="n"/>
-      <c r="K71" s="17" t="n"/>
-      <c r="L71" s="17" t="n"/>
+      <c r="F71" s="21" t="n"/>
+      <c r="G71" s="21" t="n"/>
+      <c r="H71" s="21" t="n"/>
+      <c r="I71" s="21" t="n"/>
+      <c r="J71" s="21" t="n"/>
+      <c r="K71" s="21" t="n"/>
+      <c r="L71" s="21" t="n"/>
     </row>
     <row r="72">
       <c r="B72" s="23" t="n">
@@ -17687,21 +17687,21 @@
       </c>
       <c r="D72" s="24" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>311233815</t>
         </is>
       </c>
       <c r="E72" s="24" t="inlineStr">
         <is>
-          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G72" s="25" t="n">
-        <v>1875</v>
+        <v>18</v>
       </c>
       <c r="H72" s="26" t="n"/>
       <c r="I72" s="26">
@@ -17713,9 +17713,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K72" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L72" s="5" t="inlineStr">
@@ -17734,12 +17734,12 @@
       <c r="D73" s="17" t="n"/>
       <c r="E73" s="29" t="inlineStr">
         <is>
-          <t>62.5 m² × 30 kg/m² (zalití C25/30) = 1875 kg</t>
+          <t>S04 líc 6.35 × 3.0 m = 19.05 m²; blok 1800×600 mm (výkres D.1.1.02/03: délka 1800, 5 řad × 600 výška = 3000) → 3 celé (1800×3=5400) + 1 kus 950 mm na řadu, vazba na zámek; 5 řad × ~3.5 bloku ≈ 18 ks</t>
         </is>
       </c>
       <c r="F73" s="17" t="n"/>
       <c r="G73" s="30" t="n">
-        <v>1875</v>
+        <v>18</v>
       </c>
       <c r="H73" s="17" t="n"/>
       <c r="I73" s="17" t="n"/>
@@ -17756,10 +17756,14 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D74" s="24" t="inlineStr"/>
+      <c r="D74" s="24" t="inlineStr">
+        <is>
+          <t>311233811</t>
+        </is>
+      </c>
       <c r="E74" s="24" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="F74" s="23" t="inlineStr">
@@ -17768,7 +17772,7 @@
         </is>
       </c>
       <c r="G74" s="25" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H74" s="26" t="n"/>
       <c r="I74" s="26">
@@ -17780,9 +17784,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K74" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L74" s="5" t="inlineStr">
@@ -17799,13 +17803,14 @@
         </is>
       </c>
       <c r="D75" s="17" t="n"/>
-      <c r="E75" s="29">
-        <f> S04 6.35×3.0 ≈19 + S03a 2×3.6×~2.0 ≈14 = 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
-        <v/>
+      <c r="E75" s="29" t="inlineStr">
+        <is>
+          <t>3 strany trapézu (6010-1000 dveře)+(7000-600 prefa)+(7033-600 prefa)=17843 mm = 17.84 m × výška 14 řad×0.25 = 3.5 m = 62.5 m²</t>
+        </is>
       </c>
       <c r="F75" s="17" t="n"/>
       <c r="G75" s="30" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H75" s="17" t="n"/>
       <c r="I75" s="17" t="n"/>
@@ -17822,19 +17827,23 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D76" s="24" t="inlineStr"/>
+      <c r="D76" s="24" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
       <c r="E76" s="24" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
         </is>
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G76" s="25" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H76" s="26" t="n"/>
       <c r="I76" s="26">
@@ -17846,9 +17855,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K76" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
+      <c r="K76" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
         </is>
       </c>
       <c r="L76" s="5" t="inlineStr">
@@ -17865,13 +17874,14 @@
         </is>
       </c>
       <c r="D77" s="17" t="n"/>
-      <c r="E77" s="29">
-        <f> plocha stěn pod terénem 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
-        <v/>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>62.5 m² × 30 kg/m² (zalití C25/30) = 1875 kg</t>
+        </is>
       </c>
       <c r="F77" s="17" t="n"/>
       <c r="G77" s="30" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H77" s="17" t="n"/>
       <c r="I77" s="17" t="n"/>
@@ -17880,171 +17890,161 @@
       <c r="L77" s="17" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="21" t="n"/>
-      <c r="C78" s="22" t="inlineStr">
+      <c r="B78" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C78" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D78" s="24" t="inlineStr"/>
+      <c r="E78" s="24" t="inlineStr">
+        <is>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+        </is>
+      </c>
+      <c r="F78" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G78" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="H78" s="26" t="n"/>
+      <c r="I78" s="26">
+        <f>IF(H78="",0,G78*H78)</f>
+        <v/>
+      </c>
+      <c r="J78" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K78" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="17" t="n"/>
+      <c r="C79" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D79" s="17" t="n"/>
+      <c r="E79" s="29">
+        <f> S04 6.35×3.0 ≈19 + S03a 2×3.6×~2.0 ≈14 = 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="F79" s="17" t="n"/>
+      <c r="G79" s="30" t="n">
+        <v>33</v>
+      </c>
+      <c r="H79" s="17" t="n"/>
+      <c r="I79" s="17" t="n"/>
+      <c r="J79" s="17" t="n"/>
+      <c r="K79" s="17" t="n"/>
+      <c r="L79" s="17" t="n"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="C80" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D80" s="24" t="inlineStr"/>
+      <c r="E80" s="24" t="inlineStr">
+        <is>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+        </is>
+      </c>
+      <c r="F80" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G80" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="H80" s="26" t="n"/>
+      <c r="I80" s="26">
+        <f>IF(H80="",0,G80*H80)</f>
+        <v/>
+      </c>
+      <c r="J80" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K80" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="17" t="n"/>
+      <c r="C81" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D81" s="17" t="n"/>
+      <c r="E81" s="29">
+        <f> plocha stěn pod terénem 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="F81" s="17" t="n"/>
+      <c r="G81" s="30" t="n">
+        <v>33</v>
+      </c>
+      <c r="H81" s="17" t="n"/>
+      <c r="I81" s="17" t="n"/>
+      <c r="J81" s="17" t="n"/>
+      <c r="K81" s="17" t="n"/>
+      <c r="L81" s="17" t="n"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="21" t="n"/>
+      <c r="C82" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D78" s="22" t="inlineStr">
+      <c r="D82" s="22" t="inlineStr">
         <is>
           <t>HSV-4</t>
         </is>
       </c>
-      <c r="E78" s="22" t="inlineStr">
+      <c r="E82" s="22" t="inlineStr">
         <is>
           <t>HSV-4 Vodorovné</t>
         </is>
       </c>
-      <c r="F78" s="21" t="n"/>
-      <c r="G78" s="21" t="n"/>
-      <c r="H78" s="21" t="n"/>
-      <c r="I78" s="21" t="n"/>
-      <c r="J78" s="21" t="n"/>
-      <c r="K78" s="21" t="n"/>
-      <c r="L78" s="21" t="n"/>
-    </row>
-    <row r="79">
-      <c r="B79" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="C79" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D79" s="24" t="inlineStr">
-        <is>
-          <t>762341110</t>
-        </is>
-      </c>
-      <c r="E79" s="24" t="inlineStr">
-        <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
-        </is>
-      </c>
-      <c r="F79" s="23" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G79" s="25" t="n">
-        <v>31</v>
-      </c>
-      <c r="H79" s="26" t="n"/>
-      <c r="I79" s="26">
-        <f>IF(H79="",0,G79*H79)</f>
-        <v/>
-      </c>
-      <c r="J79" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L79" s="5" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="17" t="n"/>
-      <c r="C80" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D80" s="17" t="n"/>
-      <c r="E80" s="29" t="inlineStr">
-        <is>
-          <t>10 ks (počítáno na výkrese D.1.1.02, rozteč 625 mm po 5850) × 3.1 m rozpon = 31 bm</t>
-        </is>
-      </c>
-      <c r="F80" s="17" t="n"/>
-      <c r="G80" s="30" t="n">
-        <v>31</v>
-      </c>
-      <c r="H80" s="17" t="n"/>
-      <c r="I80" s="17" t="n"/>
-      <c r="J80" s="17" t="n"/>
-      <c r="K80" s="17" t="n"/>
-      <c r="L80" s="17" t="n"/>
-    </row>
-    <row r="81">
-      <c r="B81" s="23" t="n">
-        <v>23</v>
-      </c>
-      <c r="C81" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D81" s="24" t="inlineStr">
-        <is>
-          <t>762331110</t>
-        </is>
-      </c>
-      <c r="E81" s="24" t="inlineStr">
-        <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
-        </is>
-      </c>
-      <c r="F81" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G81" s="25" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="H81" s="26" t="n"/>
-      <c r="I81" s="26">
-        <f>IF(H81="",0,G81*H81)</f>
-        <v/>
-      </c>
-      <c r="J81" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L81" s="5" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="17" t="n"/>
-      <c r="C82" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D82" s="17" t="n"/>
-      <c r="E82" s="29" t="inlineStr">
-        <is>
-          <t>strop skladu nad trámy = 5.85 × 3.1 = 18.1 m² (báze 10 trámů)</t>
-        </is>
-      </c>
-      <c r="F82" s="17" t="n"/>
-      <c r="G82" s="30" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="H82" s="17" t="n"/>
-      <c r="I82" s="17" t="n"/>
-      <c r="J82" s="17" t="n"/>
-      <c r="K82" s="17" t="n"/>
-      <c r="L82" s="17" t="n"/>
+      <c r="F82" s="21" t="n"/>
+      <c r="G82" s="21" t="n"/>
+      <c r="H82" s="21" t="n"/>
+      <c r="I82" s="21" t="n"/>
+      <c r="J82" s="21" t="n"/>
+      <c r="K82" s="21" t="n"/>
+      <c r="L82" s="21" t="n"/>
     </row>
     <row r="83">
       <c r="B83" s="23" t="n">
@@ -18057,21 +18057,21 @@
       </c>
       <c r="D83" s="24" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E83" s="24" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G83" s="25" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H83" s="26" t="n"/>
       <c r="I83" s="26">
@@ -18104,12 +18104,12 @@
       <c r="D84" s="17" t="n"/>
       <c r="E84" s="29" t="inlineStr">
         <is>
-          <t>18.1 × 1.05 přesah = 19.0 m²</t>
+          <t>10 ks (počítáno na výkrese D.1.1.02, rozteč 625 mm po 5850) × 3.1 m rozpon = 31 bm</t>
         </is>
       </c>
       <c r="F84" s="17" t="n"/>
       <c r="G84" s="30" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H84" s="17" t="n"/>
       <c r="I84" s="17" t="n"/>
@@ -18128,21 +18128,21 @@
       </c>
       <c r="D85" s="24" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E85" s="24" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G85" s="25" t="n">
-        <v>790</v>
+        <v>18.1</v>
       </c>
       <c r="H85" s="26" t="n"/>
       <c r="I85" s="26">
@@ -18175,12 +18175,12 @@
       <c r="D86" s="17" t="n"/>
       <c r="E86" s="29" t="inlineStr">
         <is>
-          <t>6 ks IPE180 × 7.0 m × 18.8 kg/m = 789.6 → 790 kg (výkres D.1.1.02: 6 nosníků)</t>
+          <t>strop skladu nad trámy = 5.85 × 3.1 = 18.1 m² (báze 10 trámů)</t>
         </is>
       </c>
       <c r="F86" s="17" t="n"/>
       <c r="G86" s="30" t="n">
-        <v>790</v>
+        <v>18.1</v>
       </c>
       <c r="H86" s="17" t="n"/>
       <c r="I86" s="17" t="n"/>
@@ -18199,12 +18199,12 @@
       </c>
       <c r="D87" s="24" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E87" s="24" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
@@ -18213,7 +18213,7 @@
         </is>
       </c>
       <c r="G87" s="25" t="n">
-        <v>44.6</v>
+        <v>19</v>
       </c>
       <c r="H87" s="26" t="n"/>
       <c r="I87" s="26">
@@ -18225,9 +18225,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K87" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
+      <c r="K87" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L87" s="5" t="inlineStr">
@@ -18246,12 +18246,12 @@
       <c r="D88" s="17" t="n"/>
       <c r="E88" s="29" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
+          <t>18.1 × 1.05 přesah = 19.0 m²</t>
         </is>
       </c>
       <c r="F88" s="17" t="n"/>
       <c r="G88" s="30" t="n">
-        <v>44.6</v>
+        <v>19</v>
       </c>
       <c r="H88" s="17" t="n"/>
       <c r="I88" s="17" t="n"/>
@@ -18270,12 +18270,12 @@
       </c>
       <c r="D89" s="24" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E89" s="24" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
@@ -18284,7 +18284,7 @@
         </is>
       </c>
       <c r="G89" s="25" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H89" s="26" t="n"/>
       <c r="I89" s="26">
@@ -18317,12 +18317,12 @@
       <c r="D90" s="17" t="n"/>
       <c r="E90" s="29" t="inlineStr">
         <is>
-          <t>IPE 790 kg + pororošt 630 kg = 1420 kg žárově zinkováno (IPE 6 ks)</t>
+          <t>6 ks IPE180 × 7.0 m × 18.8 kg/m = 789.6 → 790 kg (výkres D.1.1.02: 6 nosníků)</t>
         </is>
       </c>
       <c r="F90" s="17" t="n"/>
       <c r="G90" s="30" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H90" s="17" t="n"/>
       <c r="I90" s="17" t="n"/>
@@ -18331,125 +18331,146 @@
       <c r="L90" s="17" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="21" t="n"/>
-      <c r="C91" s="22" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D91" s="22" t="inlineStr">
-        <is>
-          <t>HSV-5</t>
-        </is>
-      </c>
-      <c r="E91" s="22" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + schodiště</t>
-        </is>
-      </c>
-      <c r="F91" s="21" t="n"/>
-      <c r="G91" s="21" t="n"/>
-      <c r="H91" s="21" t="n"/>
-      <c r="I91" s="21" t="n"/>
-      <c r="J91" s="21" t="n"/>
-      <c r="K91" s="21" t="n"/>
-      <c r="L91" s="21" t="n"/>
+      <c r="B91" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="C91" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>411321515</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G91" s="25" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H91" s="26" t="n"/>
+      <c r="I91" s="26">
+        <f>IF(H91="",0,G91*H91)</f>
+        <v/>
+      </c>
+      <c r="J91" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K91" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="B92" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="C92" s="23" t="inlineStr">
+      <c r="B92" s="17" t="n"/>
+      <c r="C92" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="n"/>
+      <c r="E92" s="29" t="inlineStr">
+        <is>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
+        </is>
+      </c>
+      <c r="F92" s="17" t="n"/>
+      <c r="G92" s="30" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H92" s="17" t="n"/>
+      <c r="I92" s="17" t="n"/>
+      <c r="J92" s="17" t="n"/>
+      <c r="K92" s="17" t="n"/>
+      <c r="L92" s="17" t="n"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="23" t="n">
+        <v>29</v>
+      </c>
+      <c r="C93" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D92" s="24" t="inlineStr">
-        <is>
-          <t>121301101</t>
-        </is>
-      </c>
-      <c r="E92" s="24" t="inlineStr">
-        <is>
-          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
-        </is>
-      </c>
-      <c r="F92" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G92" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H92" s="26" t="n"/>
-      <c r="I92" s="26">
-        <f>IF(H92="",0,G92*H92)</f>
+      <c r="D93" s="24" t="inlineStr">
+        <is>
+          <t>783201001</t>
+        </is>
+      </c>
+      <c r="E93" s="24" t="inlineStr">
+        <is>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G93" s="25" t="n">
+        <v>1420</v>
+      </c>
+      <c r="H93" s="26" t="n"/>
+      <c r="I93" s="26">
+        <f>IF(H93="",0,G93*H93)</f>
         <v/>
       </c>
-      <c r="J92" s="23" t="inlineStr">
+      <c r="J93" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K92" s="32" t="inlineStr">
+      <c r="K93" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L92" s="5" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + schodiště</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="17" t="n"/>
-      <c r="C93" s="28" t="inlineStr">
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="17" t="n"/>
+      <c r="C94" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D93" s="17" t="n"/>
-      <c r="E93" s="29" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
-        </is>
-      </c>
-      <c r="F93" s="17" t="n"/>
-      <c r="G93" s="30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H93" s="17" t="n"/>
-      <c r="I93" s="17" t="n"/>
-      <c r="J93" s="17" t="n"/>
-      <c r="K93" s="17" t="n"/>
-      <c r="L93" s="17" t="n"/>
-    </row>
-    <row r="94">
-      <c r="B94" s="19" t="n"/>
-      <c r="C94" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D94" s="20" t="inlineStr">
-        <is>
-          <t>PSV</t>
-        </is>
-      </c>
-      <c r="E94" s="20" t="inlineStr">
-        <is>
-          <t>Práce a dodávky PSV</t>
-        </is>
-      </c>
-      <c r="F94" s="19" t="n"/>
-      <c r="G94" s="19" t="n"/>
-      <c r="H94" s="19" t="n"/>
-      <c r="I94" s="19" t="n"/>
-      <c r="J94" s="19" t="n"/>
-      <c r="K94" s="19" t="n"/>
-      <c r="L94" s="19" t="n"/>
+      <c r="D94" s="17" t="n"/>
+      <c r="E94" s="29" t="inlineStr">
+        <is>
+          <t>IPE 790 kg + pororošt 630 kg = 1420 kg žárově zinkováno (IPE 6 ks)</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="n"/>
+      <c r="G94" s="30" t="n">
+        <v>1420</v>
+      </c>
+      <c r="H94" s="17" t="n"/>
+      <c r="I94" s="17" t="n"/>
+      <c r="J94" s="17" t="n"/>
+      <c r="K94" s="17" t="n"/>
+      <c r="L94" s="17" t="n"/>
     </row>
     <row r="95">
       <c r="B95" s="21" t="n"/>
@@ -18460,12 +18481,12 @@
       </c>
       <c r="D95" s="22" t="inlineStr">
         <is>
-          <t>PSV-76</t>
+          <t>HSV-5</t>
         </is>
       </c>
       <c r="E95" s="22" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="F95" s="21" t="n"/>
@@ -18478,7 +18499,7 @@
     </row>
     <row r="96">
       <c r="B96" s="23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C96" s="23" t="inlineStr">
         <is>
@@ -18487,21 +18508,21 @@
       </c>
       <c r="D96" s="24" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E96" s="24" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G96" s="25" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="H96" s="26" t="n"/>
       <c r="I96" s="26">
@@ -18520,7 +18541,7 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
     </row>
@@ -18534,12 +18555,12 @@
       <c r="D97" s="17" t="n"/>
       <c r="E97" s="29" t="inlineStr">
         <is>
-          <t>1 ks vstupní dveře skladu</t>
+          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
         </is>
       </c>
       <c r="F97" s="17" t="n"/>
       <c r="G97" s="30" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="H97" s="17" t="n"/>
       <c r="I97" s="17" t="n"/>
@@ -18548,212 +18569,216 @@
       <c r="L97" s="17" t="n"/>
     </row>
     <row r="98">
-      <c r="B98" s="21" t="n"/>
-      <c r="C98" s="22" t="inlineStr">
+      <c r="B98" s="19" t="n"/>
+      <c r="C98" s="20" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D98" s="22" t="inlineStr">
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="E98" s="20" t="inlineStr">
+        <is>
+          <t>Práce a dodávky PSV</t>
+        </is>
+      </c>
+      <c r="F98" s="19" t="n"/>
+      <c r="G98" s="19" t="n"/>
+      <c r="H98" s="19" t="n"/>
+      <c r="I98" s="19" t="n"/>
+      <c r="J98" s="19" t="n"/>
+      <c r="K98" s="19" t="n"/>
+      <c r="L98" s="19" t="n"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="21" t="n"/>
+      <c r="C99" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="inlineStr">
         <is>
           <t>PSV-76</t>
         </is>
       </c>
-      <c r="E98" s="22" t="inlineStr">
+      <c r="E99" s="22" t="inlineStr">
+        <is>
+          <t>PSV-76 Výplně otvorů</t>
+        </is>
+      </c>
+      <c r="F99" s="21" t="n"/>
+      <c r="G99" s="21" t="n"/>
+      <c r="H99" s="21" t="n"/>
+      <c r="I99" s="21" t="n"/>
+      <c r="J99" s="21" t="n"/>
+      <c r="K99" s="21" t="n"/>
+      <c r="L99" s="21" t="n"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="C100" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D100" s="24" t="inlineStr">
+        <is>
+          <t>766682111</t>
+        </is>
+      </c>
+      <c r="E100" s="24" t="inlineStr">
+        <is>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+        </is>
+      </c>
+      <c r="F100" s="23" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G100" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" s="26" t="n"/>
+      <c r="I100" s="26">
+        <f>IF(H100="",0,G100*H100)</f>
+        <v/>
+      </c>
+      <c r="J100" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K100" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L100" s="5" t="inlineStr">
+        <is>
+          <t>PSV-76 Výplně otvorů</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="17" t="n"/>
+      <c r="C101" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D101" s="17" t="n"/>
+      <c r="E101" s="29" t="inlineStr">
+        <is>
+          <t>1 ks vstupní dveře skladu</t>
+        </is>
+      </c>
+      <c r="F101" s="17" t="n"/>
+      <c r="G101" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="17" t="n"/>
+      <c r="I101" s="17" t="n"/>
+      <c r="J101" s="17" t="n"/>
+      <c r="K101" s="17" t="n"/>
+      <c r="L101" s="17" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="21" t="n"/>
+      <c r="C102" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="inlineStr">
+        <is>
+          <t>PSV-76</t>
+        </is>
+      </c>
+      <c r="E102" s="22" t="inlineStr">
         <is>
           <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
-      <c r="F98" s="21" t="n"/>
-      <c r="G98" s="21" t="n"/>
-      <c r="H98" s="21" t="n"/>
-      <c r="I98" s="21" t="n"/>
-      <c r="J98" s="21" t="n"/>
-      <c r="K98" s="21" t="n"/>
-      <c r="L98" s="21" t="n"/>
-    </row>
-    <row r="99">
-      <c r="B99" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="C99" s="23" t="inlineStr">
+      <c r="F102" s="21" t="n"/>
+      <c r="G102" s="21" t="n"/>
+      <c r="H102" s="21" t="n"/>
+      <c r="I102" s="21" t="n"/>
+      <c r="J102" s="21" t="n"/>
+      <c r="K102" s="21" t="n"/>
+      <c r="L102" s="21" t="n"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="C103" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D99" s="24" t="inlineStr"/>
-      <c r="E99" s="24" t="inlineStr">
+      <c r="D103" s="24" t="inlineStr"/>
+      <c r="E103" s="24" t="inlineStr">
         <is>
           <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
-      <c r="F99" s="23" t="inlineStr">
+      <c r="F103" s="23" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="G99" s="25" t="n">
+      <c r="G103" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H99" s="26" t="n"/>
-      <c r="I99" s="26">
-        <f>IF(H99="",0,G99*H99)</f>
+      <c r="H103" s="26" t="n"/>
+      <c r="I103" s="26">
+        <f>IF(H103="",0,G103*H103)</f>
         <v/>
       </c>
-      <c r="J99" s="23" t="inlineStr">
+      <c r="J103" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K99" s="33" t="inlineStr">
+      <c r="K103" s="33" t="inlineStr">
         <is>
           <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
-      <c r="L99" s="5" t="inlineStr">
+      <c r="L103" s="5" t="inlineStr">
         <is>
           <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" s="17" t="n"/>
-      <c r="C100" s="28" t="inlineStr">
+    <row r="104">
+      <c r="B104" s="17" t="n"/>
+      <c r="C104" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D100" s="17" t="n"/>
-      <c r="E100" s="29">
+      <c r="D104" s="17" t="n"/>
+      <c r="E104" s="29">
         <f> 1 brána (Dodatek PD č.1)</f>
         <v/>
       </c>
-      <c r="F100" s="17" t="n"/>
-      <c r="G100" s="30" t="n">
+      <c r="F104" s="17" t="n"/>
+      <c r="G104" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H100" s="17" t="n"/>
-      <c r="I100" s="17" t="n"/>
-      <c r="J100" s="17" t="n"/>
-      <c r="K100" s="17" t="n"/>
-      <c r="L100" s="17" t="n"/>
-    </row>
-    <row r="101">
-      <c r="B101" s="21" t="n"/>
-      <c r="C101" s="22" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D101" s="22" t="inlineStr">
-        <is>
-          <t>PSV-77</t>
-        </is>
-      </c>
-      <c r="E101" s="22" t="inlineStr">
-        <is>
-          <t>PSV-77 Podlahy</t>
-        </is>
-      </c>
-      <c r="F101" s="21" t="n"/>
-      <c r="G101" s="21" t="n"/>
-      <c r="H101" s="21" t="n"/>
-      <c r="I101" s="21" t="n"/>
-      <c r="J101" s="21" t="n"/>
-      <c r="K101" s="21" t="n"/>
-      <c r="L101" s="21" t="n"/>
-    </row>
-    <row r="102">
-      <c r="B102" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="C102" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D102" s="24" t="inlineStr"/>
-      <c r="E102" s="24" t="inlineStr">
-        <is>
-          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
-        </is>
-      </c>
-      <c r="F102" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G102" s="25" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="H102" s="26" t="n"/>
-      <c r="I102" s="26">
-        <f>IF(H102="",0,G102*H102)</f>
-        <v/>
-      </c>
-      <c r="J102" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K102" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
-        </is>
-      </c>
-      <c r="L102" s="5" t="inlineStr">
-        <is>
-          <t>PSV-77 Podlahy</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" s="17" t="n"/>
-      <c r="C103" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D103" s="17" t="n"/>
-      <c r="E103" s="29" t="inlineStr">
-        <is>
-          <t>plocha S01 = místnost 17.6 (legenda) + vynos za stěnu 6.0 (6010×1000 řez) = 23.6 m²</t>
-        </is>
-      </c>
-      <c r="F103" s="17" t="n"/>
-      <c r="G103" s="30" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="H103" s="17" t="n"/>
-      <c r="I103" s="17" t="n"/>
-      <c r="J103" s="17" t="n"/>
-      <c r="K103" s="17" t="n"/>
-      <c r="L103" s="17" t="n"/>
-    </row>
-    <row r="104">
-      <c r="B104" s="19" t="n"/>
-      <c r="C104" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D104" s="20" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E104" s="20" t="inlineStr">
-        <is>
-          <t>Vedlejší rozpočtové náklady</t>
-        </is>
-      </c>
-      <c r="F104" s="19" t="n"/>
-      <c r="G104" s="19" t="n"/>
-      <c r="H104" s="19" t="n"/>
-      <c r="I104" s="19" t="n"/>
-      <c r="J104" s="19" t="n"/>
-      <c r="K104" s="19" t="n"/>
-      <c r="L104" s="19" t="n"/>
+      <c r="H104" s="17" t="n"/>
+      <c r="I104" s="17" t="n"/>
+      <c r="J104" s="17" t="n"/>
+      <c r="K104" s="17" t="n"/>
+      <c r="L104" s="17" t="n"/>
     </row>
     <row r="105">
       <c r="B105" s="21" t="n"/>
@@ -18764,12 +18789,12 @@
       </c>
       <c r="D105" s="22" t="inlineStr">
         <is>
-          <t>VRN</t>
+          <t>PSV-77</t>
         </is>
       </c>
       <c r="E105" s="22" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="F105" s="21" t="n"/>
@@ -18782,30 +18807,26 @@
     </row>
     <row r="106">
       <c r="B106" s="23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C106" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D106" s="24" t="inlineStr">
-        <is>
-          <t>030001000</t>
-        </is>
-      </c>
+      <c r="D106" s="24" t="inlineStr"/>
       <c r="E106" s="24" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G106" s="25" t="n">
-        <v>1</v>
+        <v>23.6</v>
       </c>
       <c r="H106" s="26" t="n"/>
       <c r="I106" s="26">
@@ -18817,14 +18838,14 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K106" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K106" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
     </row>
@@ -18838,12 +18859,12 @@
       <c r="D107" s="17" t="n"/>
       <c r="E107" s="29" t="inlineStr">
         <is>
-          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+          <t>plocha S01 = místnost 17.6 (legenda) + vynos za stěnu 6.0 (6010×1000 řez) = 23.6 m²</t>
         </is>
       </c>
       <c r="F107" s="17" t="n"/>
       <c r="G107" s="30" t="n">
-        <v>1</v>
+        <v>23.6</v>
       </c>
       <c r="H107" s="17" t="n"/>
       <c r="I107" s="17" t="n"/>
@@ -18852,267 +18873,388 @@
       <c r="L107" s="17" t="n"/>
     </row>
     <row r="108">
-      <c r="B108" s="21" t="n"/>
-      <c r="C108" s="22" t="inlineStr">
+      <c r="B108" s="19" t="n"/>
+      <c r="C108" s="20" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D108" s="22" t="inlineStr">
+      <c r="D108" s="20" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E108" s="22" t="inlineStr">
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="F108" s="19" t="n"/>
+      <c r="G108" s="19" t="n"/>
+      <c r="H108" s="19" t="n"/>
+      <c r="I108" s="19" t="n"/>
+      <c r="J108" s="19" t="n"/>
+      <c r="K108" s="19" t="n"/>
+      <c r="L108" s="19" t="n"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="21" t="n"/>
+      <c r="C109" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D109" s="22" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E109" s="22" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="F109" s="21" t="n"/>
+      <c r="G109" s="21" t="n"/>
+      <c r="H109" s="21" t="n"/>
+      <c r="I109" s="21" t="n"/>
+      <c r="J109" s="21" t="n"/>
+      <c r="K109" s="21" t="n"/>
+      <c r="L109" s="21" t="n"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="C110" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D110" s="24" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E110" s="24" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F110" s="23" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G110" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="26" t="n"/>
+      <c r="I110" s="26">
+        <f>IF(H110="",0,G110*H110)</f>
+        <v/>
+      </c>
+      <c r="J110" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K110" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="17" t="n"/>
+      <c r="C111" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D111" s="17" t="n"/>
+      <c r="E111" s="29" t="inlineStr">
+        <is>
+          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+        </is>
+      </c>
+      <c r="F111" s="17" t="n"/>
+      <c r="G111" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="17" t="n"/>
+      <c r="I111" s="17" t="n"/>
+      <c r="J111" s="17" t="n"/>
+      <c r="K111" s="17" t="n"/>
+      <c r="L111" s="17" t="n"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="21" t="n"/>
+      <c r="C112" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D112" s="22" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E112" s="22" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
-      <c r="F108" s="21" t="n"/>
-      <c r="G108" s="21" t="n"/>
-      <c r="H108" s="21" t="n"/>
-      <c r="I108" s="21" t="n"/>
-      <c r="J108" s="21" t="n"/>
-      <c r="K108" s="21" t="n"/>
-      <c r="L108" s="21" t="n"/>
-    </row>
-    <row r="109">
-      <c r="B109" s="23" t="n">
-        <v>33</v>
-      </c>
-      <c r="C109" s="23" t="inlineStr">
+      <c r="F112" s="21" t="n"/>
+      <c r="G112" s="21" t="n"/>
+      <c r="H112" s="21" t="n"/>
+      <c r="I112" s="21" t="n"/>
+      <c r="J112" s="21" t="n"/>
+      <c r="K112" s="21" t="n"/>
+      <c r="L112" s="21" t="n"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="23" t="n">
+        <v>35</v>
+      </c>
+      <c r="C113" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D109" s="24" t="inlineStr">
+      <c r="D113" s="24" t="inlineStr">
         <is>
           <t>031032000</t>
         </is>
       </c>
-      <c r="E109" s="24" t="inlineStr">
+      <c r="E113" s="24" t="inlineStr">
         <is>
           <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
-      <c r="F109" s="23" t="inlineStr">
+      <c r="F113" s="23" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="G109" s="25" t="n">
+      <c r="G113" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H109" s="26" t="n"/>
-      <c r="I109" s="26">
-        <f>IF(H109="",0,G109*H109)</f>
+      <c r="H113" s="26" t="n"/>
+      <c r="I113" s="26">
+        <f>IF(H113="",0,G113*H113)</f>
         <v/>
       </c>
-      <c r="J109" s="23" t="inlineStr">
+      <c r="J113" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K109" s="32" t="inlineStr">
+      <c r="K113" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L109" s="5" t="inlineStr">
+      <c r="L113" s="5" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="B110" s="17" t="n"/>
-      <c r="C110" s="28" t="inlineStr">
+    <row r="114">
+      <c r="B114" s="17" t="n"/>
+      <c r="C114" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D110" s="17" t="n"/>
-      <c r="E110" s="29" t="inlineStr">
+      <c r="D114" s="17" t="n"/>
+      <c r="E114" s="29" t="inlineStr">
         <is>
           <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
         </is>
       </c>
-      <c r="F110" s="17" t="n"/>
-      <c r="G110" s="30" t="n">
+      <c r="F114" s="17" t="n"/>
+      <c r="G114" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H110" s="17" t="n"/>
-      <c r="I110" s="17" t="n"/>
-      <c r="J110" s="17" t="n"/>
-      <c r="K110" s="17" t="n"/>
-      <c r="L110" s="17" t="n"/>
-    </row>
-    <row r="111">
-      <c r="B111" s="23" t="n">
-        <v>34</v>
-      </c>
-      <c r="C111" s="23" t="inlineStr">
+      <c r="H114" s="17" t="n"/>
+      <c r="I114" s="17" t="n"/>
+      <c r="J114" s="17" t="n"/>
+      <c r="K114" s="17" t="n"/>
+      <c r="L114" s="17" t="n"/>
+    </row>
+    <row r="115">
+      <c r="B115" s="23" t="n">
+        <v>36</v>
+      </c>
+      <c r="C115" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D111" s="24" t="inlineStr">
+      <c r="D115" s="24" t="inlineStr">
         <is>
           <t>997013211</t>
         </is>
       </c>
-      <c r="E111" s="24" t="inlineStr">
+      <c r="E115" s="24" t="inlineStr">
         <is>
           <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
-      <c r="F111" s="23" t="inlineStr">
+      <c r="F115" s="23" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
-      <c r="G111" s="25" t="n">
+      <c r="G115" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="H111" s="26" t="n"/>
-      <c r="I111" s="26">
-        <f>IF(H111="",0,G111*H111)</f>
+      <c r="H115" s="26" t="n"/>
+      <c r="I115" s="26">
+        <f>IF(H115="",0,G115*H115)</f>
         <v/>
       </c>
-      <c r="J111" s="23" t="inlineStr">
+      <c r="J115" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K111" s="32" t="inlineStr">
+      <c r="K115" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L111" s="5" t="inlineStr">
+      <c r="L115" s="5" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="B112" s="17" t="n"/>
-      <c r="C112" s="28" t="inlineStr">
+    <row r="116">
+      <c r="B116" s="17" t="n"/>
+      <c r="C116" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D112" s="17" t="n"/>
-      <c r="E112" s="29" t="inlineStr">
+      <c r="D116" s="17" t="n"/>
+      <c r="E116" s="29" t="inlineStr">
         <is>
           <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
         </is>
       </c>
-      <c r="F112" s="17" t="n"/>
-      <c r="G112" s="30" t="n">
+      <c r="F116" s="17" t="n"/>
+      <c r="G116" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="H112" s="17" t="n"/>
-      <c r="I112" s="17" t="n"/>
-      <c r="J112" s="17" t="n"/>
-      <c r="K112" s="17" t="n"/>
-      <c r="L112" s="17" t="n"/>
-    </row>
-    <row r="113">
-      <c r="B113" s="21" t="n"/>
-      <c r="C113" s="22" t="inlineStr">
+      <c r="H116" s="17" t="n"/>
+      <c r="I116" s="17" t="n"/>
+      <c r="J116" s="17" t="n"/>
+      <c r="K116" s="17" t="n"/>
+      <c r="L116" s="17" t="n"/>
+    </row>
+    <row r="117">
+      <c r="B117" s="21" t="n"/>
+      <c r="C117" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D113" s="22" t="inlineStr">
+      <c r="D117" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E113" s="22" t="inlineStr">
+      <c r="E117" s="22" t="inlineStr">
         <is>
           <t>VRN — Geodet</t>
         </is>
       </c>
-      <c r="F113" s="21" t="n"/>
-      <c r="G113" s="21" t="n"/>
-      <c r="H113" s="21" t="n"/>
-      <c r="I113" s="21" t="n"/>
-      <c r="J113" s="21" t="n"/>
-      <c r="K113" s="21" t="n"/>
-      <c r="L113" s="21" t="n"/>
-    </row>
-    <row r="114">
-      <c r="B114" s="23" t="n">
-        <v>35</v>
-      </c>
-      <c r="C114" s="23" t="inlineStr">
+      <c r="F117" s="21" t="n"/>
+      <c r="G117" s="21" t="n"/>
+      <c r="H117" s="21" t="n"/>
+      <c r="I117" s="21" t="n"/>
+      <c r="J117" s="21" t="n"/>
+      <c r="K117" s="21" t="n"/>
+      <c r="L117" s="21" t="n"/>
+    </row>
+    <row r="118">
+      <c r="B118" s="23" t="n">
+        <v>37</v>
+      </c>
+      <c r="C118" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D114" s="24" t="inlineStr">
+      <c r="D118" s="24" t="inlineStr">
         <is>
           <t>030141000</t>
         </is>
       </c>
-      <c r="E114" s="24" t="inlineStr">
+      <c r="E118" s="24" t="inlineStr">
         <is>
           <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
-      <c r="F114" s="23" t="inlineStr">
+      <c r="F118" s="23" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="G114" s="25" t="n">
+      <c r="G118" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H114" s="26" t="n"/>
-      <c r="I114" s="26">
-        <f>IF(H114="",0,G114*H114)</f>
+      <c r="H118" s="26" t="n"/>
+      <c r="I118" s="26">
+        <f>IF(H118="",0,G118*H118)</f>
         <v/>
       </c>
-      <c r="J114" s="23" t="inlineStr">
+      <c r="J118" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K114" s="32" t="inlineStr">
+      <c r="K118" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L114" s="5" t="inlineStr">
+      <c r="L118" s="5" t="inlineStr">
         <is>
           <t>VRN — Geodet</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="B115" s="17" t="n"/>
-      <c r="C115" s="28" t="inlineStr">
+    <row r="119">
+      <c r="B119" s="17" t="n"/>
+      <c r="C119" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D115" s="17" t="n"/>
-      <c r="E115" s="29" t="inlineStr">
+      <c r="D119" s="17" t="n"/>
+      <c r="E119" s="29" t="inlineStr">
         <is>
           <t>Standard geodet vytýčení pro nový objekt</t>
         </is>
       </c>
-      <c r="F115" s="17" t="n"/>
-      <c r="G115" s="30" t="n">
+      <c r="F119" s="17" t="n"/>
+      <c r="G119" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H115" s="17" t="n"/>
-      <c r="I115" s="17" t="n"/>
-      <c r="J115" s="17" t="n"/>
-      <c r="K115" s="17" t="n"/>
-      <c r="L115" s="17" t="n"/>
+      <c r="H119" s="17" t="n"/>
+      <c r="I119" s="17" t="n"/>
+      <c r="J119" s="17" t="n"/>
+      <c r="K119" s="17" t="n"/>
+      <c r="L119" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -19138,7 +19280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H266"/>
+  <dimension ref="B2:H268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -19217,7 +19359,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -19227,7 +19369,7 @@
         </is>
       </c>
       <c r="C10" s="34" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13">
@@ -27338,6 +27480,80 @@
       <c r="H266" s="24" t="inlineStr">
         <is>
           <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.007</t>
+        </is>
+      </c>
+      <c r="C267" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D267" s="24" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="E267" s="24" t="inlineStr">
+        <is>
+          <t>273351215</t>
+        </is>
+      </c>
+      <c r="F267" s="24" t="inlineStr">
+        <is>
+          <t>271313</t>
+        </is>
+      </c>
+      <c r="G267" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bednění základových pasů + spodních patek (prostý beton) — tradiční / </t>
+        </is>
+      </c>
+      <c r="H267" s="24" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.008</t>
+        </is>
+      </c>
+      <c r="C268" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D268" s="24" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="E268" s="24" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
+      <c r="F268" s="24" t="inlineStr">
+        <is>
+          <t>271313</t>
+        </is>
+      </c>
+      <c r="G268" s="24" t="inlineStr">
+        <is>
+          <t>Výztuž B500B vkládaná do tvárnic ztraceného bednění — patky horní (6 s</t>
+        </is>
+      </c>
+      <c r="H268" s="24" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N247"/>
+  <dimension ref="B2:N249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -37859,6 +38075,104 @@
       <c r="M247" s="24" t="inlineStr"/>
       <c r="N247" s="24" t="inlineStr"/>
     </row>
+    <row r="248">
+      <c r="B248" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.007</t>
+        </is>
+      </c>
+      <c r="C248" s="24" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="D248" s="24" t="inlineStr">
+        <is>
+          <t>Bednění základových pasů + spodních patek (prostý beton) — tradiční / systémové,</t>
+        </is>
+      </c>
+      <c r="E248" s="24" t="inlineStr">
+        <is>
+          <t>273351215</t>
+        </is>
+      </c>
+      <c r="F248" s="24" t="inlineStr"/>
+      <c r="G248" s="24" t="inlineStr">
+        <is>
+          <t>271313</t>
+        </is>
+      </c>
+      <c r="H248" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I248" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J248" s="32" t="inlineStr"/>
+      <c r="K248" s="24" t="inlineStr"/>
+      <c r="L248" s="24" t="inlineStr">
+        <is>
+          <t>273313811</t>
+        </is>
+      </c>
+      <c r="M248" s="24" t="inlineStr"/>
+      <c r="N248" s="24" t="inlineStr">
+        <is>
+          <t>WebSearch verified WRONG LEAF: URS leaf = ZÁKLADY DESKY C 25/30, item = ZÁKLADOVÉ PASY C16/20 XC0. Hint: Základové pasy = TKP 271 (pasy), NOT 273 (desky); class C16/20 leaf needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.008</t>
+        </is>
+      </c>
+      <c r="C249" s="24" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="D249" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Výztuž B500B vkládaná do tvárnic ztraceného bednění — patky horní (6 sloupků) + </t>
+        </is>
+      </c>
+      <c r="E249" s="24" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
+      <c r="F249" s="24" t="inlineStr"/>
+      <c r="G249" s="24" t="inlineStr">
+        <is>
+          <t>271313</t>
+        </is>
+      </c>
+      <c r="H249" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I249" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J249" s="32" t="inlineStr"/>
+      <c r="K249" s="24" t="inlineStr"/>
+      <c r="L249" s="24" t="inlineStr">
+        <is>
+          <t>273313811</t>
+        </is>
+      </c>
+      <c r="M249" s="24" t="inlineStr"/>
+      <c r="N249" s="24" t="inlineStr">
+        <is>
+          <t>WebSearch verified WRONG LEAF: URS leaf = ZÁKLADY DESKY C 25/30, item = ZÁKLADOVÉ PASY C16/20 XC0. Hint: Základové pasy = TKP 271 (pasy), NOT 273 (desky); class C16/20 leaf needed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-02_v3_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-02_v3_final.xlsx
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <f>SUM('SO_260217_Sklad'!I34:I114)</f>
+        <f>SUM('SO_260217_Sklad'!I34:I118)</f>
         <v/>
       </c>
       <c r="E15" s="7">
@@ -15954,7 +15954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L115"/>
+  <dimension ref="B2:L119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -16115,7 +16115,7 @@
         </is>
       </c>
       <c r="D16" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C16)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C16)</f>
         <v/>
       </c>
     </row>
@@ -16127,7 +16127,7 @@
         </is>
       </c>
       <c r="D17" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C17)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C17)</f>
         <v/>
       </c>
     </row>
@@ -16139,7 +16139,7 @@
         </is>
       </c>
       <c r="D18" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C18)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C18)</f>
         <v/>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
         </is>
       </c>
       <c r="D19" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C19)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C19)</f>
         <v/>
       </c>
     </row>
@@ -16163,7 +16163,7 @@
         </is>
       </c>
       <c r="D20" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C20)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C20)</f>
         <v/>
       </c>
     </row>
@@ -16175,7 +16175,7 @@
         </is>
       </c>
       <c r="D21" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C21)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C21)</f>
         <v/>
       </c>
     </row>
@@ -16187,7 +16187,7 @@
         </is>
       </c>
       <c r="D22" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C22)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C22)</f>
         <v/>
       </c>
     </row>
@@ -16199,7 +16199,7 @@
         </is>
       </c>
       <c r="D23" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C23)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C23)</f>
         <v/>
       </c>
     </row>
@@ -16211,7 +16211,7 @@
         </is>
       </c>
       <c r="D24" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C24)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C24)</f>
         <v/>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
         </is>
       </c>
       <c r="D25" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C25)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C25)</f>
         <v/>
       </c>
     </row>
@@ -16235,7 +16235,7 @@
         </is>
       </c>
       <c r="D26" s="7">
-        <f>SUMIFS(I32:I115,L32:L115,C26)</f>
+        <f>SUMIFS(I32:I119,L32:L119,C26)</f>
         <v/>
       </c>
     </row>
@@ -17241,7 +17241,7 @@
       </c>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Patky parking horní část — zdivo z tvárnic ztraceného bednění 300×300 mm (lost formwork, zůstává v konstrukci), 6 patek á 300×300×500 mm</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
@@ -17283,7 +17283,7 @@
       <c r="D60" s="17" t="n"/>
       <c r="E60" s="29" t="inlineStr">
         <is>
-          <t>6 ks (= spodní, výkres D.1.1.02)</t>
+          <t>6 patek horní á 300×300×500 mm = 6 sloupků z tvárnic ZB 300×300 (á 2 řady po 250 = 12 tvárnic); zálivka C25/30 + výztuž samostatně (HSV2.004 / HSV3.003)</t>
         </is>
       </c>
       <c r="F60" s="17" t="n"/>
@@ -17321,7 +17321,7 @@
         </is>
       </c>
       <c r="G61" s="25" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H61" s="26" t="n"/>
       <c r="I61" s="26">
@@ -17354,12 +17354,12 @@
       <c r="D62" s="17" t="n"/>
       <c r="E62" s="29" t="inlineStr">
         <is>
-          <t>patky horní (0.3×0.3×0.5×6 = 0.27) + věnec nad patkami 2 řady ztrac.bednění (0.5 v × 6.35 d × 0.3 š = 0.95) + zídka lemující (~0.5) = ~1.72 ≈ 1.75 m³</t>
+          <t>zálivka tvárnic ZB: patky horní (0.3×0.3×0.5×6=0.27) + věnec 2 řady (2×0.25 v × 0.3 š × 6.7 d=1.00) + zídka lemující (~0.5) = 1.77 m³</t>
         </is>
       </c>
       <c r="F62" s="17" t="n"/>
       <c r="G62" s="30" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H62" s="17" t="n"/>
       <c r="I62" s="17" t="n"/>
@@ -17510,171 +17510,171 @@
       <c r="L66" s="17" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="21" t="n"/>
-      <c r="C67" s="22" t="inlineStr">
+      <c r="B67" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="C67" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D67" s="24" t="inlineStr">
+        <is>
+          <t>273351215</t>
+        </is>
+      </c>
+      <c r="E67" s="24" t="inlineStr">
+        <is>
+          <t>Bednění základových pasů + spodních patek (prostý beton) — tradiční / systémové, oboustranné kde nelze betonovat do rýhy</t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G67" s="25" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="H67" s="26" t="n"/>
+      <c r="I67" s="26">
+        <f>IF(H67="",0,G67*H67)</f>
+        <v/>
+      </c>
+      <c r="J67" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="17" t="n"/>
+      <c r="C68" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="n"/>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>patky spodní 6×4×0.5×0.5=6.0 + pasy 2 strany×0.5×19.4 obvod=19.4 = 25.4 m² (část lze betonovat do rýhy → OVĚŘIT)</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="n"/>
+      <c r="G68" s="30" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="H68" s="17" t="n"/>
+      <c r="I68" s="17" t="n"/>
+      <c r="J68" s="17" t="n"/>
+      <c r="K68" s="17" t="n"/>
+      <c r="L68" s="17" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="C69" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D69" s="24" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
+      <c r="E69" s="24" t="inlineStr">
+        <is>
+          <t>Výztuž B500B vkládaná do tvárnic ztraceného bednění — patky horní (6 sloupků) + ztužující věnec nad patkami</t>
+        </is>
+      </c>
+      <c r="F69" s="23" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G69" s="25" t="n">
+        <v>153</v>
+      </c>
+      <c r="H69" s="26" t="n"/>
+      <c r="I69" s="26">
+        <f>IF(H69="",0,G69*H69)</f>
+        <v/>
+      </c>
+      <c r="J69" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="17" t="n"/>
+      <c r="C70" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="n"/>
+      <c r="E70" s="29" t="inlineStr">
+        <is>
+          <t>zálivka tvárnic ZB 1.27 m³ (patky horní 0.27 + věnec 1.00) × 120 kg/m³ (= stěna 30 kg/m² ÷ 0.25) = 153 kg</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="n"/>
+      <c r="G70" s="30" t="n">
+        <v>153</v>
+      </c>
+      <c r="H70" s="17" t="n"/>
+      <c r="I70" s="17" t="n"/>
+      <c r="J70" s="17" t="n"/>
+      <c r="K70" s="17" t="n"/>
+      <c r="L70" s="17" t="n"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="21" t="n"/>
+      <c r="C71" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D67" s="22" t="inlineStr">
+      <c r="D71" s="22" t="inlineStr">
         <is>
           <t>HSV-3</t>
         </is>
       </c>
-      <c r="E67" s="22" t="inlineStr">
+      <c r="E71" s="22" t="inlineStr">
         <is>
           <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
-      <c r="F67" s="21" t="n"/>
-      <c r="G67" s="21" t="n"/>
-      <c r="H67" s="21" t="n"/>
-      <c r="I67" s="21" t="n"/>
-      <c r="J67" s="21" t="n"/>
-      <c r="K67" s="21" t="n"/>
-      <c r="L67" s="21" t="n"/>
-    </row>
-    <row r="68">
-      <c r="B68" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="C68" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D68" s="24" t="inlineStr">
-        <is>
-          <t>311233815</t>
-        </is>
-      </c>
-      <c r="E68" s="24" t="inlineStr">
-        <is>
-          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
-        </is>
-      </c>
-      <c r="F68" s="23" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G68" s="25" t="n">
-        <v>18</v>
-      </c>
-      <c r="H68" s="26" t="n"/>
-      <c r="I68" s="26">
-        <f>IF(H68="",0,G68*H68)</f>
-        <v/>
-      </c>
-      <c r="J68" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L68" s="5" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="17" t="n"/>
-      <c r="C69" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D69" s="17" t="n"/>
-      <c r="E69" s="29" t="inlineStr">
-        <is>
-          <t>S04 líc 6.35 × 3.0 m = 19.05 m²; blok 1800×600 mm (výkres D.1.1.02/03: délka 1800, 5 řad × 600 výška = 3000) → 3 celé (1800×3=5400) + 1 kus 950 mm na řadu, vazba na zámek; 5 řad × ~3.5 bloku ≈ 18 ks</t>
-        </is>
-      </c>
-      <c r="F69" s="17" t="n"/>
-      <c r="G69" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="H69" s="17" t="n"/>
-      <c r="I69" s="17" t="n"/>
-      <c r="J69" s="17" t="n"/>
-      <c r="K69" s="17" t="n"/>
-      <c r="L69" s="17" t="n"/>
-    </row>
-    <row r="70">
-      <c r="B70" s="23" t="n">
-        <v>18</v>
-      </c>
-      <c r="C70" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D70" s="24" t="inlineStr">
-        <is>
-          <t>311233811</t>
-        </is>
-      </c>
-      <c r="E70" s="24" t="inlineStr">
-        <is>
-          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
-        </is>
-      </c>
-      <c r="F70" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G70" s="25" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="H70" s="26" t="n"/>
-      <c r="I70" s="26">
-        <f>IF(H70="",0,G70*H70)</f>
-        <v/>
-      </c>
-      <c r="J70" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L70" s="5" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="17" t="n"/>
-      <c r="C71" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D71" s="17" t="n"/>
-      <c r="E71" s="29" t="inlineStr">
-        <is>
-          <t>3 strany trapézu (6010-1000 dveře)+(7000-600 prefa)+(7033-600 prefa)=17843 mm = 17.84 m × výška 14 řad×0.25 = 3.5 m = 62.5 m²</t>
-        </is>
-      </c>
-      <c r="F71" s="17" t="n"/>
-      <c r="G71" s="30" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="H71" s="17" t="n"/>
-      <c r="I71" s="17" t="n"/>
-      <c r="J71" s="17" t="n"/>
-      <c r="K71" s="17" t="n"/>
-      <c r="L71" s="17" t="n"/>
+      <c r="F71" s="21" t="n"/>
+      <c r="G71" s="21" t="n"/>
+      <c r="H71" s="21" t="n"/>
+      <c r="I71" s="21" t="n"/>
+      <c r="J71" s="21" t="n"/>
+      <c r="K71" s="21" t="n"/>
+      <c r="L71" s="21" t="n"/>
     </row>
     <row r="72">
       <c r="B72" s="23" t="n">
@@ -17687,21 +17687,21 @@
       </c>
       <c r="D72" s="24" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>311233815</t>
         </is>
       </c>
       <c r="E72" s="24" t="inlineStr">
         <is>
-          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G72" s="25" t="n">
-        <v>1875</v>
+        <v>18</v>
       </c>
       <c r="H72" s="26" t="n"/>
       <c r="I72" s="26">
@@ -17713,9 +17713,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K72" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L72" s="5" t="inlineStr">
@@ -17734,12 +17734,12 @@
       <c r="D73" s="17" t="n"/>
       <c r="E73" s="29" t="inlineStr">
         <is>
-          <t>62.5 m² × 30 kg/m² (zalití C25/30) = 1875 kg</t>
+          <t>S04 líc 6.35 × 3.0 m = 19.05 m²; blok 1800×600 mm (výkres D.1.1.02/03: délka 1800, 5 řad × 600 výška = 3000) → 3 celé (1800×3=5400) + 1 kus 950 mm na řadu, vazba na zámek; 5 řad × ~3.5 bloku ≈ 18 ks</t>
         </is>
       </c>
       <c r="F73" s="17" t="n"/>
       <c r="G73" s="30" t="n">
-        <v>1875</v>
+        <v>18</v>
       </c>
       <c r="H73" s="17" t="n"/>
       <c r="I73" s="17" t="n"/>
@@ -17756,10 +17756,14 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D74" s="24" t="inlineStr"/>
+      <c r="D74" s="24" t="inlineStr">
+        <is>
+          <t>311233811</t>
+        </is>
+      </c>
       <c r="E74" s="24" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="F74" s="23" t="inlineStr">
@@ -17768,7 +17772,7 @@
         </is>
       </c>
       <c r="G74" s="25" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H74" s="26" t="n"/>
       <c r="I74" s="26">
@@ -17780,9 +17784,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K74" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L74" s="5" t="inlineStr">
@@ -17799,13 +17803,14 @@
         </is>
       </c>
       <c r="D75" s="17" t="n"/>
-      <c r="E75" s="29">
-        <f> S04 6.35×3.0 ≈19 + S03a 2×3.6×~2.0 ≈14 = 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
-        <v/>
+      <c r="E75" s="29" t="inlineStr">
+        <is>
+          <t>3 strany trapézu (6010-1000 dveře)+(7000-600 prefa)+(7033-600 prefa)=17843 mm = 17.84 m × výška 14 řad×0.25 = 3.5 m = 62.5 m²</t>
+        </is>
       </c>
       <c r="F75" s="17" t="n"/>
       <c r="G75" s="30" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H75" s="17" t="n"/>
       <c r="I75" s="17" t="n"/>
@@ -17822,19 +17827,23 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D76" s="24" t="inlineStr"/>
+      <c r="D76" s="24" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
       <c r="E76" s="24" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
         </is>
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G76" s="25" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H76" s="26" t="n"/>
       <c r="I76" s="26">
@@ -17846,9 +17855,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K76" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
+      <c r="K76" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
         </is>
       </c>
       <c r="L76" s="5" t="inlineStr">
@@ -17865,13 +17874,14 @@
         </is>
       </c>
       <c r="D77" s="17" t="n"/>
-      <c r="E77" s="29">
-        <f> plocha stěn pod terénem 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
-        <v/>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>62.5 m² × 30 kg/m² (zalití C25/30) = 1875 kg</t>
+        </is>
       </c>
       <c r="F77" s="17" t="n"/>
       <c r="G77" s="30" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H77" s="17" t="n"/>
       <c r="I77" s="17" t="n"/>
@@ -17880,171 +17890,161 @@
       <c r="L77" s="17" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="21" t="n"/>
-      <c r="C78" s="22" t="inlineStr">
+      <c r="B78" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C78" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D78" s="24" t="inlineStr"/>
+      <c r="E78" s="24" t="inlineStr">
+        <is>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+        </is>
+      </c>
+      <c r="F78" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G78" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="H78" s="26" t="n"/>
+      <c r="I78" s="26">
+        <f>IF(H78="",0,G78*H78)</f>
+        <v/>
+      </c>
+      <c r="J78" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K78" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="17" t="n"/>
+      <c r="C79" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D79" s="17" t="n"/>
+      <c r="E79" s="29">
+        <f> S04 6.35×3.0 ≈19 + S03a 2×3.6×~2.0 ≈14 = 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="F79" s="17" t="n"/>
+      <c r="G79" s="30" t="n">
+        <v>33</v>
+      </c>
+      <c r="H79" s="17" t="n"/>
+      <c r="I79" s="17" t="n"/>
+      <c r="J79" s="17" t="n"/>
+      <c r="K79" s="17" t="n"/>
+      <c r="L79" s="17" t="n"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="C80" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D80" s="24" t="inlineStr"/>
+      <c r="E80" s="24" t="inlineStr">
+        <is>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+        </is>
+      </c>
+      <c r="F80" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G80" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="H80" s="26" t="n"/>
+      <c r="I80" s="26">
+        <f>IF(H80="",0,G80*H80)</f>
+        <v/>
+      </c>
+      <c r="J80" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K80" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="17" t="n"/>
+      <c r="C81" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D81" s="17" t="n"/>
+      <c r="E81" s="29">
+        <f> plocha stěn pod terénem 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="F81" s="17" t="n"/>
+      <c r="G81" s="30" t="n">
+        <v>33</v>
+      </c>
+      <c r="H81" s="17" t="n"/>
+      <c r="I81" s="17" t="n"/>
+      <c r="J81" s="17" t="n"/>
+      <c r="K81" s="17" t="n"/>
+      <c r="L81" s="17" t="n"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="21" t="n"/>
+      <c r="C82" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D78" s="22" t="inlineStr">
+      <c r="D82" s="22" t="inlineStr">
         <is>
           <t>HSV-4</t>
         </is>
       </c>
-      <c r="E78" s="22" t="inlineStr">
+      <c r="E82" s="22" t="inlineStr">
         <is>
           <t>HSV-4 Vodorovné</t>
         </is>
       </c>
-      <c r="F78" s="21" t="n"/>
-      <c r="G78" s="21" t="n"/>
-      <c r="H78" s="21" t="n"/>
-      <c r="I78" s="21" t="n"/>
-      <c r="J78" s="21" t="n"/>
-      <c r="K78" s="21" t="n"/>
-      <c r="L78" s="21" t="n"/>
-    </row>
-    <row r="79">
-      <c r="B79" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="C79" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D79" s="24" t="inlineStr">
-        <is>
-          <t>762341110</t>
-        </is>
-      </c>
-      <c r="E79" s="24" t="inlineStr">
-        <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
-        </is>
-      </c>
-      <c r="F79" s="23" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G79" s="25" t="n">
-        <v>31</v>
-      </c>
-      <c r="H79" s="26" t="n"/>
-      <c r="I79" s="26">
-        <f>IF(H79="",0,G79*H79)</f>
-        <v/>
-      </c>
-      <c r="J79" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L79" s="5" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="17" t="n"/>
-      <c r="C80" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D80" s="17" t="n"/>
-      <c r="E80" s="29" t="inlineStr">
-        <is>
-          <t>10 ks (počítáno na výkrese D.1.1.02, rozteč 625 mm po 5850) × 3.1 m rozpon = 31 bm</t>
-        </is>
-      </c>
-      <c r="F80" s="17" t="n"/>
-      <c r="G80" s="30" t="n">
-        <v>31</v>
-      </c>
-      <c r="H80" s="17" t="n"/>
-      <c r="I80" s="17" t="n"/>
-      <c r="J80" s="17" t="n"/>
-      <c r="K80" s="17" t="n"/>
-      <c r="L80" s="17" t="n"/>
-    </row>
-    <row r="81">
-      <c r="B81" s="23" t="n">
-        <v>23</v>
-      </c>
-      <c r="C81" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D81" s="24" t="inlineStr">
-        <is>
-          <t>762331110</t>
-        </is>
-      </c>
-      <c r="E81" s="24" t="inlineStr">
-        <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
-        </is>
-      </c>
-      <c r="F81" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G81" s="25" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="H81" s="26" t="n"/>
-      <c r="I81" s="26">
-        <f>IF(H81="",0,G81*H81)</f>
-        <v/>
-      </c>
-      <c r="J81" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L81" s="5" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="17" t="n"/>
-      <c r="C82" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D82" s="17" t="n"/>
-      <c r="E82" s="29" t="inlineStr">
-        <is>
-          <t>strop skladu nad trámy = 5.85 × 3.1 = 18.1 m² (báze 10 trámů)</t>
-        </is>
-      </c>
-      <c r="F82" s="17" t="n"/>
-      <c r="G82" s="30" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="H82" s="17" t="n"/>
-      <c r="I82" s="17" t="n"/>
-      <c r="J82" s="17" t="n"/>
-      <c r="K82" s="17" t="n"/>
-      <c r="L82" s="17" t="n"/>
+      <c r="F82" s="21" t="n"/>
+      <c r="G82" s="21" t="n"/>
+      <c r="H82" s="21" t="n"/>
+      <c r="I82" s="21" t="n"/>
+      <c r="J82" s="21" t="n"/>
+      <c r="K82" s="21" t="n"/>
+      <c r="L82" s="21" t="n"/>
     </row>
     <row r="83">
       <c r="B83" s="23" t="n">
@@ -18057,21 +18057,21 @@
       </c>
       <c r="D83" s="24" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E83" s="24" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G83" s="25" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H83" s="26" t="n"/>
       <c r="I83" s="26">
@@ -18104,12 +18104,12 @@
       <c r="D84" s="17" t="n"/>
       <c r="E84" s="29" t="inlineStr">
         <is>
-          <t>18.1 × 1.05 přesah = 19.0 m²</t>
+          <t>10 ks (počítáno na výkrese D.1.1.02, rozteč 625 mm po 5850) × 3.1 m rozpon = 31 bm</t>
         </is>
       </c>
       <c r="F84" s="17" t="n"/>
       <c r="G84" s="30" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H84" s="17" t="n"/>
       <c r="I84" s="17" t="n"/>
@@ -18128,21 +18128,21 @@
       </c>
       <c r="D85" s="24" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E85" s="24" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G85" s="25" t="n">
-        <v>790</v>
+        <v>18.1</v>
       </c>
       <c r="H85" s="26" t="n"/>
       <c r="I85" s="26">
@@ -18175,12 +18175,12 @@
       <c r="D86" s="17" t="n"/>
       <c r="E86" s="29" t="inlineStr">
         <is>
-          <t>6 ks IPE180 × 7.0 m × 18.8 kg/m = 789.6 → 790 kg (výkres D.1.1.02: 6 nosníků)</t>
+          <t>strop skladu nad trámy = 5.85 × 3.1 = 18.1 m² (báze 10 trámů)</t>
         </is>
       </c>
       <c r="F86" s="17" t="n"/>
       <c r="G86" s="30" t="n">
-        <v>790</v>
+        <v>18.1</v>
       </c>
       <c r="H86" s="17" t="n"/>
       <c r="I86" s="17" t="n"/>
@@ -18199,12 +18199,12 @@
       </c>
       <c r="D87" s="24" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E87" s="24" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
@@ -18213,7 +18213,7 @@
         </is>
       </c>
       <c r="G87" s="25" t="n">
-        <v>44.6</v>
+        <v>19</v>
       </c>
       <c r="H87" s="26" t="n"/>
       <c r="I87" s="26">
@@ -18225,9 +18225,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K87" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
+      <c r="K87" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L87" s="5" t="inlineStr">
@@ -18246,12 +18246,12 @@
       <c r="D88" s="17" t="n"/>
       <c r="E88" s="29" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
+          <t>18.1 × 1.05 přesah = 19.0 m²</t>
         </is>
       </c>
       <c r="F88" s="17" t="n"/>
       <c r="G88" s="30" t="n">
-        <v>44.6</v>
+        <v>19</v>
       </c>
       <c r="H88" s="17" t="n"/>
       <c r="I88" s="17" t="n"/>
@@ -18270,12 +18270,12 @@
       </c>
       <c r="D89" s="24" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E89" s="24" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
@@ -18284,7 +18284,7 @@
         </is>
       </c>
       <c r="G89" s="25" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H89" s="26" t="n"/>
       <c r="I89" s="26">
@@ -18317,12 +18317,12 @@
       <c r="D90" s="17" t="n"/>
       <c r="E90" s="29" t="inlineStr">
         <is>
-          <t>IPE 790 kg + pororošt 630 kg = 1420 kg žárově zinkováno (IPE 6 ks)</t>
+          <t>6 ks IPE180 × 7.0 m × 18.8 kg/m = 789.6 → 790 kg (výkres D.1.1.02: 6 nosníků)</t>
         </is>
       </c>
       <c r="F90" s="17" t="n"/>
       <c r="G90" s="30" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H90" s="17" t="n"/>
       <c r="I90" s="17" t="n"/>
@@ -18331,125 +18331,146 @@
       <c r="L90" s="17" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="21" t="n"/>
-      <c r="C91" s="22" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D91" s="22" t="inlineStr">
-        <is>
-          <t>HSV-5</t>
-        </is>
-      </c>
-      <c r="E91" s="22" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + schodiště</t>
-        </is>
-      </c>
-      <c r="F91" s="21" t="n"/>
-      <c r="G91" s="21" t="n"/>
-      <c r="H91" s="21" t="n"/>
-      <c r="I91" s="21" t="n"/>
-      <c r="J91" s="21" t="n"/>
-      <c r="K91" s="21" t="n"/>
-      <c r="L91" s="21" t="n"/>
+      <c r="B91" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="C91" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>411321515</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G91" s="25" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H91" s="26" t="n"/>
+      <c r="I91" s="26">
+        <f>IF(H91="",0,G91*H91)</f>
+        <v/>
+      </c>
+      <c r="J91" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K91" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="B92" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="C92" s="23" t="inlineStr">
+      <c r="B92" s="17" t="n"/>
+      <c r="C92" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="n"/>
+      <c r="E92" s="29" t="inlineStr">
+        <is>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
+        </is>
+      </c>
+      <c r="F92" s="17" t="n"/>
+      <c r="G92" s="30" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H92" s="17" t="n"/>
+      <c r="I92" s="17" t="n"/>
+      <c r="J92" s="17" t="n"/>
+      <c r="K92" s="17" t="n"/>
+      <c r="L92" s="17" t="n"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="23" t="n">
+        <v>29</v>
+      </c>
+      <c r="C93" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D92" s="24" t="inlineStr">
-        <is>
-          <t>121301101</t>
-        </is>
-      </c>
-      <c r="E92" s="24" t="inlineStr">
-        <is>
-          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
-        </is>
-      </c>
-      <c r="F92" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G92" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H92" s="26" t="n"/>
-      <c r="I92" s="26">
-        <f>IF(H92="",0,G92*H92)</f>
+      <c r="D93" s="24" t="inlineStr">
+        <is>
+          <t>783201001</t>
+        </is>
+      </c>
+      <c r="E93" s="24" t="inlineStr">
+        <is>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G93" s="25" t="n">
+        <v>1420</v>
+      </c>
+      <c r="H93" s="26" t="n"/>
+      <c r="I93" s="26">
+        <f>IF(H93="",0,G93*H93)</f>
         <v/>
       </c>
-      <c r="J92" s="23" t="inlineStr">
+      <c r="J93" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K92" s="32" t="inlineStr">
+      <c r="K93" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L92" s="5" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + schodiště</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="17" t="n"/>
-      <c r="C93" s="28" t="inlineStr">
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="17" t="n"/>
+      <c r="C94" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D93" s="17" t="n"/>
-      <c r="E93" s="29" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
-        </is>
-      </c>
-      <c r="F93" s="17" t="n"/>
-      <c r="G93" s="30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H93" s="17" t="n"/>
-      <c r="I93" s="17" t="n"/>
-      <c r="J93" s="17" t="n"/>
-      <c r="K93" s="17" t="n"/>
-      <c r="L93" s="17" t="n"/>
-    </row>
-    <row r="94">
-      <c r="B94" s="19" t="n"/>
-      <c r="C94" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D94" s="20" t="inlineStr">
-        <is>
-          <t>PSV</t>
-        </is>
-      </c>
-      <c r="E94" s="20" t="inlineStr">
-        <is>
-          <t>Práce a dodávky PSV</t>
-        </is>
-      </c>
-      <c r="F94" s="19" t="n"/>
-      <c r="G94" s="19" t="n"/>
-      <c r="H94" s="19" t="n"/>
-      <c r="I94" s="19" t="n"/>
-      <c r="J94" s="19" t="n"/>
-      <c r="K94" s="19" t="n"/>
-      <c r="L94" s="19" t="n"/>
+      <c r="D94" s="17" t="n"/>
+      <c r="E94" s="29" t="inlineStr">
+        <is>
+          <t>IPE 790 kg + pororošt 630 kg = 1420 kg žárově zinkováno (IPE 6 ks)</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="n"/>
+      <c r="G94" s="30" t="n">
+        <v>1420</v>
+      </c>
+      <c r="H94" s="17" t="n"/>
+      <c r="I94" s="17" t="n"/>
+      <c r="J94" s="17" t="n"/>
+      <c r="K94" s="17" t="n"/>
+      <c r="L94" s="17" t="n"/>
     </row>
     <row r="95">
       <c r="B95" s="21" t="n"/>
@@ -18460,12 +18481,12 @@
       </c>
       <c r="D95" s="22" t="inlineStr">
         <is>
-          <t>PSV-76</t>
+          <t>HSV-5</t>
         </is>
       </c>
       <c r="E95" s="22" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="F95" s="21" t="n"/>
@@ -18478,7 +18499,7 @@
     </row>
     <row r="96">
       <c r="B96" s="23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C96" s="23" t="inlineStr">
         <is>
@@ -18487,21 +18508,21 @@
       </c>
       <c r="D96" s="24" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E96" s="24" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G96" s="25" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="H96" s="26" t="n"/>
       <c r="I96" s="26">
@@ -18520,7 +18541,7 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
     </row>
@@ -18534,12 +18555,12 @@
       <c r="D97" s="17" t="n"/>
       <c r="E97" s="29" t="inlineStr">
         <is>
-          <t>1 ks vstupní dveře skladu</t>
+          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
         </is>
       </c>
       <c r="F97" s="17" t="n"/>
       <c r="G97" s="30" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="H97" s="17" t="n"/>
       <c r="I97" s="17" t="n"/>
@@ -18548,212 +18569,216 @@
       <c r="L97" s="17" t="n"/>
     </row>
     <row r="98">
-      <c r="B98" s="21" t="n"/>
-      <c r="C98" s="22" t="inlineStr">
+      <c r="B98" s="19" t="n"/>
+      <c r="C98" s="20" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D98" s="22" t="inlineStr">
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="E98" s="20" t="inlineStr">
+        <is>
+          <t>Práce a dodávky PSV</t>
+        </is>
+      </c>
+      <c r="F98" s="19" t="n"/>
+      <c r="G98" s="19" t="n"/>
+      <c r="H98" s="19" t="n"/>
+      <c r="I98" s="19" t="n"/>
+      <c r="J98" s="19" t="n"/>
+      <c r="K98" s="19" t="n"/>
+      <c r="L98" s="19" t="n"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="21" t="n"/>
+      <c r="C99" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="inlineStr">
         <is>
           <t>PSV-76</t>
         </is>
       </c>
-      <c r="E98" s="22" t="inlineStr">
+      <c r="E99" s="22" t="inlineStr">
+        <is>
+          <t>PSV-76 Výplně otvorů</t>
+        </is>
+      </c>
+      <c r="F99" s="21" t="n"/>
+      <c r="G99" s="21" t="n"/>
+      <c r="H99" s="21" t="n"/>
+      <c r="I99" s="21" t="n"/>
+      <c r="J99" s="21" t="n"/>
+      <c r="K99" s="21" t="n"/>
+      <c r="L99" s="21" t="n"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="C100" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D100" s="24" t="inlineStr">
+        <is>
+          <t>766682111</t>
+        </is>
+      </c>
+      <c r="E100" s="24" t="inlineStr">
+        <is>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+        </is>
+      </c>
+      <c r="F100" s="23" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G100" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" s="26" t="n"/>
+      <c r="I100" s="26">
+        <f>IF(H100="",0,G100*H100)</f>
+        <v/>
+      </c>
+      <c r="J100" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K100" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L100" s="5" t="inlineStr">
+        <is>
+          <t>PSV-76 Výplně otvorů</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="17" t="n"/>
+      <c r="C101" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D101" s="17" t="n"/>
+      <c r="E101" s="29" t="inlineStr">
+        <is>
+          <t>1 ks vstupní dveře skladu</t>
+        </is>
+      </c>
+      <c r="F101" s="17" t="n"/>
+      <c r="G101" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="17" t="n"/>
+      <c r="I101" s="17" t="n"/>
+      <c r="J101" s="17" t="n"/>
+      <c r="K101" s="17" t="n"/>
+      <c r="L101" s="17" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="21" t="n"/>
+      <c r="C102" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="inlineStr">
+        <is>
+          <t>PSV-76</t>
+        </is>
+      </c>
+      <c r="E102" s="22" t="inlineStr">
         <is>
           <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
-      <c r="F98" s="21" t="n"/>
-      <c r="G98" s="21" t="n"/>
-      <c r="H98" s="21" t="n"/>
-      <c r="I98" s="21" t="n"/>
-      <c r="J98" s="21" t="n"/>
-      <c r="K98" s="21" t="n"/>
-      <c r="L98" s="21" t="n"/>
-    </row>
-    <row r="99">
-      <c r="B99" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="C99" s="23" t="inlineStr">
+      <c r="F102" s="21" t="n"/>
+      <c r="G102" s="21" t="n"/>
+      <c r="H102" s="21" t="n"/>
+      <c r="I102" s="21" t="n"/>
+      <c r="J102" s="21" t="n"/>
+      <c r="K102" s="21" t="n"/>
+      <c r="L102" s="21" t="n"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="C103" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D99" s="24" t="inlineStr"/>
-      <c r="E99" s="24" t="inlineStr">
+      <c r="D103" s="24" t="inlineStr"/>
+      <c r="E103" s="24" t="inlineStr">
         <is>
           <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
-      <c r="F99" s="23" t="inlineStr">
+      <c r="F103" s="23" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="G99" s="25" t="n">
+      <c r="G103" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H99" s="26" t="n"/>
-      <c r="I99" s="26">
-        <f>IF(H99="",0,G99*H99)</f>
+      <c r="H103" s="26" t="n"/>
+      <c r="I103" s="26">
+        <f>IF(H103="",0,G103*H103)</f>
         <v/>
       </c>
-      <c r="J99" s="23" t="inlineStr">
+      <c r="J103" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K99" s="33" t="inlineStr">
+      <c r="K103" s="33" t="inlineStr">
         <is>
           <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
-      <c r="L99" s="5" t="inlineStr">
+      <c r="L103" s="5" t="inlineStr">
         <is>
           <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" s="17" t="n"/>
-      <c r="C100" s="28" t="inlineStr">
+    <row r="104">
+      <c r="B104" s="17" t="n"/>
+      <c r="C104" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D100" s="17" t="n"/>
-      <c r="E100" s="29">
+      <c r="D104" s="17" t="n"/>
+      <c r="E104" s="29">
         <f> 1 brána (Dodatek PD č.1)</f>
         <v/>
       </c>
-      <c r="F100" s="17" t="n"/>
-      <c r="G100" s="30" t="n">
+      <c r="F104" s="17" t="n"/>
+      <c r="G104" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H100" s="17" t="n"/>
-      <c r="I100" s="17" t="n"/>
-      <c r="J100" s="17" t="n"/>
-      <c r="K100" s="17" t="n"/>
-      <c r="L100" s="17" t="n"/>
-    </row>
-    <row r="101">
-      <c r="B101" s="21" t="n"/>
-      <c r="C101" s="22" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D101" s="22" t="inlineStr">
-        <is>
-          <t>PSV-77</t>
-        </is>
-      </c>
-      <c r="E101" s="22" t="inlineStr">
-        <is>
-          <t>PSV-77 Podlahy</t>
-        </is>
-      </c>
-      <c r="F101" s="21" t="n"/>
-      <c r="G101" s="21" t="n"/>
-      <c r="H101" s="21" t="n"/>
-      <c r="I101" s="21" t="n"/>
-      <c r="J101" s="21" t="n"/>
-      <c r="K101" s="21" t="n"/>
-      <c r="L101" s="21" t="n"/>
-    </row>
-    <row r="102">
-      <c r="B102" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="C102" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D102" s="24" t="inlineStr"/>
-      <c r="E102" s="24" t="inlineStr">
-        <is>
-          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
-        </is>
-      </c>
-      <c r="F102" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G102" s="25" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="H102" s="26" t="n"/>
-      <c r="I102" s="26">
-        <f>IF(H102="",0,G102*H102)</f>
-        <v/>
-      </c>
-      <c r="J102" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K102" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
-        </is>
-      </c>
-      <c r="L102" s="5" t="inlineStr">
-        <is>
-          <t>PSV-77 Podlahy</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" s="17" t="n"/>
-      <c r="C103" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D103" s="17" t="n"/>
-      <c r="E103" s="29" t="inlineStr">
-        <is>
-          <t>plocha S01 = místnost 17.6 (legenda) + vynos za stěnu 6.0 (6010×1000 řez) = 23.6 m²</t>
-        </is>
-      </c>
-      <c r="F103" s="17" t="n"/>
-      <c r="G103" s="30" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="H103" s="17" t="n"/>
-      <c r="I103" s="17" t="n"/>
-      <c r="J103" s="17" t="n"/>
-      <c r="K103" s="17" t="n"/>
-      <c r="L103" s="17" t="n"/>
-    </row>
-    <row r="104">
-      <c r="B104" s="19" t="n"/>
-      <c r="C104" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D104" s="20" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E104" s="20" t="inlineStr">
-        <is>
-          <t>Vedlejší rozpočtové náklady</t>
-        </is>
-      </c>
-      <c r="F104" s="19" t="n"/>
-      <c r="G104" s="19" t="n"/>
-      <c r="H104" s="19" t="n"/>
-      <c r="I104" s="19" t="n"/>
-      <c r="J104" s="19" t="n"/>
-      <c r="K104" s="19" t="n"/>
-      <c r="L104" s="19" t="n"/>
+      <c r="H104" s="17" t="n"/>
+      <c r="I104" s="17" t="n"/>
+      <c r="J104" s="17" t="n"/>
+      <c r="K104" s="17" t="n"/>
+      <c r="L104" s="17" t="n"/>
     </row>
     <row r="105">
       <c r="B105" s="21" t="n"/>
@@ -18764,12 +18789,12 @@
       </c>
       <c r="D105" s="22" t="inlineStr">
         <is>
-          <t>VRN</t>
+          <t>PSV-77</t>
         </is>
       </c>
       <c r="E105" s="22" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="F105" s="21" t="n"/>
@@ -18782,30 +18807,26 @@
     </row>
     <row r="106">
       <c r="B106" s="23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C106" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D106" s="24" t="inlineStr">
-        <is>
-          <t>030001000</t>
-        </is>
-      </c>
+      <c r="D106" s="24" t="inlineStr"/>
       <c r="E106" s="24" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G106" s="25" t="n">
-        <v>1</v>
+        <v>23.6</v>
       </c>
       <c r="H106" s="26" t="n"/>
       <c r="I106" s="26">
@@ -18817,14 +18838,14 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K106" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K106" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
     </row>
@@ -18838,12 +18859,12 @@
       <c r="D107" s="17" t="n"/>
       <c r="E107" s="29" t="inlineStr">
         <is>
-          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+          <t>plocha S01 = místnost 17.6 (legenda) + vynos za stěnu 6.0 (6010×1000 řez) = 23.6 m²</t>
         </is>
       </c>
       <c r="F107" s="17" t="n"/>
       <c r="G107" s="30" t="n">
-        <v>1</v>
+        <v>23.6</v>
       </c>
       <c r="H107" s="17" t="n"/>
       <c r="I107" s="17" t="n"/>
@@ -18852,267 +18873,388 @@
       <c r="L107" s="17" t="n"/>
     </row>
     <row r="108">
-      <c r="B108" s="21" t="n"/>
-      <c r="C108" s="22" t="inlineStr">
+      <c r="B108" s="19" t="n"/>
+      <c r="C108" s="20" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D108" s="22" t="inlineStr">
+      <c r="D108" s="20" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E108" s="22" t="inlineStr">
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="F108" s="19" t="n"/>
+      <c r="G108" s="19" t="n"/>
+      <c r="H108" s="19" t="n"/>
+      <c r="I108" s="19" t="n"/>
+      <c r="J108" s="19" t="n"/>
+      <c r="K108" s="19" t="n"/>
+      <c r="L108" s="19" t="n"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="21" t="n"/>
+      <c r="C109" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D109" s="22" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E109" s="22" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="F109" s="21" t="n"/>
+      <c r="G109" s="21" t="n"/>
+      <c r="H109" s="21" t="n"/>
+      <c r="I109" s="21" t="n"/>
+      <c r="J109" s="21" t="n"/>
+      <c r="K109" s="21" t="n"/>
+      <c r="L109" s="21" t="n"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="C110" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D110" s="24" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E110" s="24" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F110" s="23" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G110" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="26" t="n"/>
+      <c r="I110" s="26">
+        <f>IF(H110="",0,G110*H110)</f>
+        <v/>
+      </c>
+      <c r="J110" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K110" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="17" t="n"/>
+      <c r="C111" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D111" s="17" t="n"/>
+      <c r="E111" s="29" t="inlineStr">
+        <is>
+          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+        </is>
+      </c>
+      <c r="F111" s="17" t="n"/>
+      <c r="G111" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="17" t="n"/>
+      <c r="I111" s="17" t="n"/>
+      <c r="J111" s="17" t="n"/>
+      <c r="K111" s="17" t="n"/>
+      <c r="L111" s="17" t="n"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="21" t="n"/>
+      <c r="C112" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D112" s="22" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E112" s="22" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
-      <c r="F108" s="21" t="n"/>
-      <c r="G108" s="21" t="n"/>
-      <c r="H108" s="21" t="n"/>
-      <c r="I108" s="21" t="n"/>
-      <c r="J108" s="21" t="n"/>
-      <c r="K108" s="21" t="n"/>
-      <c r="L108" s="21" t="n"/>
-    </row>
-    <row r="109">
-      <c r="B109" s="23" t="n">
-        <v>33</v>
-      </c>
-      <c r="C109" s="23" t="inlineStr">
+      <c r="F112" s="21" t="n"/>
+      <c r="G112" s="21" t="n"/>
+      <c r="H112" s="21" t="n"/>
+      <c r="I112" s="21" t="n"/>
+      <c r="J112" s="21" t="n"/>
+      <c r="K112" s="21" t="n"/>
+      <c r="L112" s="21" t="n"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="23" t="n">
+        <v>35</v>
+      </c>
+      <c r="C113" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D109" s="24" t="inlineStr">
+      <c r="D113" s="24" t="inlineStr">
         <is>
           <t>031032000</t>
         </is>
       </c>
-      <c r="E109" s="24" t="inlineStr">
+      <c r="E113" s="24" t="inlineStr">
         <is>
           <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
-      <c r="F109" s="23" t="inlineStr">
+      <c r="F113" s="23" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="G109" s="25" t="n">
+      <c r="G113" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H109" s="26" t="n"/>
-      <c r="I109" s="26">
-        <f>IF(H109="",0,G109*H109)</f>
+      <c r="H113" s="26" t="n"/>
+      <c r="I113" s="26">
+        <f>IF(H113="",0,G113*H113)</f>
         <v/>
       </c>
-      <c r="J109" s="23" t="inlineStr">
+      <c r="J113" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K109" s="32" t="inlineStr">
+      <c r="K113" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L109" s="5" t="inlineStr">
+      <c r="L113" s="5" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="B110" s="17" t="n"/>
-      <c r="C110" s="28" t="inlineStr">
+    <row r="114">
+      <c r="B114" s="17" t="n"/>
+      <c r="C114" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D110" s="17" t="n"/>
-      <c r="E110" s="29" t="inlineStr">
+      <c r="D114" s="17" t="n"/>
+      <c r="E114" s="29" t="inlineStr">
         <is>
           <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
         </is>
       </c>
-      <c r="F110" s="17" t="n"/>
-      <c r="G110" s="30" t="n">
+      <c r="F114" s="17" t="n"/>
+      <c r="G114" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H110" s="17" t="n"/>
-      <c r="I110" s="17" t="n"/>
-      <c r="J110" s="17" t="n"/>
-      <c r="K110" s="17" t="n"/>
-      <c r="L110" s="17" t="n"/>
-    </row>
-    <row r="111">
-      <c r="B111" s="23" t="n">
-        <v>34</v>
-      </c>
-      <c r="C111" s="23" t="inlineStr">
+      <c r="H114" s="17" t="n"/>
+      <c r="I114" s="17" t="n"/>
+      <c r="J114" s="17" t="n"/>
+      <c r="K114" s="17" t="n"/>
+      <c r="L114" s="17" t="n"/>
+    </row>
+    <row r="115">
+      <c r="B115" s="23" t="n">
+        <v>36</v>
+      </c>
+      <c r="C115" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D111" s="24" t="inlineStr">
+      <c r="D115" s="24" t="inlineStr">
         <is>
           <t>997013211</t>
         </is>
       </c>
-      <c r="E111" s="24" t="inlineStr">
+      <c r="E115" s="24" t="inlineStr">
         <is>
           <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
-      <c r="F111" s="23" t="inlineStr">
+      <c r="F115" s="23" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
-      <c r="G111" s="25" t="n">
+      <c r="G115" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="H111" s="26" t="n"/>
-      <c r="I111" s="26">
-        <f>IF(H111="",0,G111*H111)</f>
+      <c r="H115" s="26" t="n"/>
+      <c r="I115" s="26">
+        <f>IF(H115="",0,G115*H115)</f>
         <v/>
       </c>
-      <c r="J111" s="23" t="inlineStr">
+      <c r="J115" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K111" s="32" t="inlineStr">
+      <c r="K115" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L111" s="5" t="inlineStr">
+      <c r="L115" s="5" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="B112" s="17" t="n"/>
-      <c r="C112" s="28" t="inlineStr">
+    <row r="116">
+      <c r="B116" s="17" t="n"/>
+      <c r="C116" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D112" s="17" t="n"/>
-      <c r="E112" s="29" t="inlineStr">
+      <c r="D116" s="17" t="n"/>
+      <c r="E116" s="29" t="inlineStr">
         <is>
           <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
         </is>
       </c>
-      <c r="F112" s="17" t="n"/>
-      <c r="G112" s="30" t="n">
+      <c r="F116" s="17" t="n"/>
+      <c r="G116" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="H112" s="17" t="n"/>
-      <c r="I112" s="17" t="n"/>
-      <c r="J112" s="17" t="n"/>
-      <c r="K112" s="17" t="n"/>
-      <c r="L112" s="17" t="n"/>
-    </row>
-    <row r="113">
-      <c r="B113" s="21" t="n"/>
-      <c r="C113" s="22" t="inlineStr">
+      <c r="H116" s="17" t="n"/>
+      <c r="I116" s="17" t="n"/>
+      <c r="J116" s="17" t="n"/>
+      <c r="K116" s="17" t="n"/>
+      <c r="L116" s="17" t="n"/>
+    </row>
+    <row r="117">
+      <c r="B117" s="21" t="n"/>
+      <c r="C117" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D113" s="22" t="inlineStr">
+      <c r="D117" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E113" s="22" t="inlineStr">
+      <c r="E117" s="22" t="inlineStr">
         <is>
           <t>VRN — Geodet</t>
         </is>
       </c>
-      <c r="F113" s="21" t="n"/>
-      <c r="G113" s="21" t="n"/>
-      <c r="H113" s="21" t="n"/>
-      <c r="I113" s="21" t="n"/>
-      <c r="J113" s="21" t="n"/>
-      <c r="K113" s="21" t="n"/>
-      <c r="L113" s="21" t="n"/>
-    </row>
-    <row r="114">
-      <c r="B114" s="23" t="n">
-        <v>35</v>
-      </c>
-      <c r="C114" s="23" t="inlineStr">
+      <c r="F117" s="21" t="n"/>
+      <c r="G117" s="21" t="n"/>
+      <c r="H117" s="21" t="n"/>
+      <c r="I117" s="21" t="n"/>
+      <c r="J117" s="21" t="n"/>
+      <c r="K117" s="21" t="n"/>
+      <c r="L117" s="21" t="n"/>
+    </row>
+    <row r="118">
+      <c r="B118" s="23" t="n">
+        <v>37</v>
+      </c>
+      <c r="C118" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D114" s="24" t="inlineStr">
+      <c r="D118" s="24" t="inlineStr">
         <is>
           <t>030141000</t>
         </is>
       </c>
-      <c r="E114" s="24" t="inlineStr">
+      <c r="E118" s="24" t="inlineStr">
         <is>
           <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
-      <c r="F114" s="23" t="inlineStr">
+      <c r="F118" s="23" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="G114" s="25" t="n">
+      <c r="G118" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H114" s="26" t="n"/>
-      <c r="I114" s="26">
-        <f>IF(H114="",0,G114*H114)</f>
+      <c r="H118" s="26" t="n"/>
+      <c r="I118" s="26">
+        <f>IF(H118="",0,G118*H118)</f>
         <v/>
       </c>
-      <c r="J114" s="23" t="inlineStr">
+      <c r="J118" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K114" s="32" t="inlineStr">
+      <c r="K118" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L114" s="5" t="inlineStr">
+      <c r="L118" s="5" t="inlineStr">
         <is>
           <t>VRN — Geodet</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="B115" s="17" t="n"/>
-      <c r="C115" s="28" t="inlineStr">
+    <row r="119">
+      <c r="B119" s="17" t="n"/>
+      <c r="C119" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D115" s="17" t="n"/>
-      <c r="E115" s="29" t="inlineStr">
+      <c r="D119" s="17" t="n"/>
+      <c r="E119" s="29" t="inlineStr">
         <is>
           <t>Standard geodet vytýčení pro nový objekt</t>
         </is>
       </c>
-      <c r="F115" s="17" t="n"/>
-      <c r="G115" s="30" t="n">
+      <c r="F119" s="17" t="n"/>
+      <c r="G119" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H115" s="17" t="n"/>
-      <c r="I115" s="17" t="n"/>
-      <c r="J115" s="17" t="n"/>
-      <c r="K115" s="17" t="n"/>
-      <c r="L115" s="17" t="n"/>
+      <c r="H119" s="17" t="n"/>
+      <c r="I119" s="17" t="n"/>
+      <c r="J119" s="17" t="n"/>
+      <c r="K119" s="17" t="n"/>
+      <c r="L119" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -19138,7 +19280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H266"/>
+  <dimension ref="B2:H268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -19217,7 +19359,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -19227,7 +19369,7 @@
         </is>
       </c>
       <c r="C10" s="34" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13">
@@ -21954,7 +22096,7 @@
       <c r="F100" s="24" t="inlineStr"/>
       <c r="G100" s="24" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bedně</t>
+          <t xml:space="preserve">Patky parking horní část — zdivo z tvárnic ztraceného bednění 300×300 </t>
         </is>
       </c>
       <c r="H100" s="24" t="inlineStr">
@@ -27338,6 +27480,80 @@
       <c r="H266" s="24" t="inlineStr">
         <is>
           <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.007</t>
+        </is>
+      </c>
+      <c r="C267" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D267" s="24" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="E267" s="24" t="inlineStr">
+        <is>
+          <t>273351215</t>
+        </is>
+      </c>
+      <c r="F267" s="24" t="inlineStr">
+        <is>
+          <t>271313</t>
+        </is>
+      </c>
+      <c r="G267" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bednění základových pasů + spodních patek (prostý beton) — tradiční / </t>
+        </is>
+      </c>
+      <c r="H267" s="24" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.008</t>
+        </is>
+      </c>
+      <c r="C268" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D268" s="24" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="E268" s="24" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
+      <c r="F268" s="24" t="inlineStr">
+        <is>
+          <t>271313</t>
+        </is>
+      </c>
+      <c r="G268" s="24" t="inlineStr">
+        <is>
+          <t>Výztuž B500B vkládaná do tvárnic ztraceného bednění — patky horní (6 s</t>
+        </is>
+      </c>
+      <c r="H268" s="24" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N247"/>
+  <dimension ref="B2:N249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -28874,7 +29090,7 @@
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300</t>
+          <t>Patky parking horní část — zdivo z tvárnic ztraceného bednění 300×300 mm (lost f</t>
         </is>
       </c>
       <c r="E34" s="24" t="inlineStr">
@@ -37859,6 +38075,104 @@
       <c r="M247" s="24" t="inlineStr"/>
       <c r="N247" s="24" t="inlineStr"/>
     </row>
+    <row r="248">
+      <c r="B248" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.007</t>
+        </is>
+      </c>
+      <c r="C248" s="24" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="D248" s="24" t="inlineStr">
+        <is>
+          <t>Bednění základových pasů + spodních patek (prostý beton) — tradiční / systémové,</t>
+        </is>
+      </c>
+      <c r="E248" s="24" t="inlineStr">
+        <is>
+          <t>273351215</t>
+        </is>
+      </c>
+      <c r="F248" s="24" t="inlineStr"/>
+      <c r="G248" s="24" t="inlineStr">
+        <is>
+          <t>271313</t>
+        </is>
+      </c>
+      <c r="H248" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I248" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J248" s="32" t="inlineStr"/>
+      <c r="K248" s="24" t="inlineStr"/>
+      <c r="L248" s="24" t="inlineStr">
+        <is>
+          <t>273313811</t>
+        </is>
+      </c>
+      <c r="M248" s="24" t="inlineStr"/>
+      <c r="N248" s="24" t="inlineStr">
+        <is>
+          <t>WebSearch verified WRONG LEAF: URS leaf = ZÁKLADY DESKY C 25/30, item = ZÁKLADOVÉ PASY C16/20 XC0. Hint: Základové pasy = TKP 271 (pasy), NOT 273 (desky); class C16/20 leaf needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.008</t>
+        </is>
+      </c>
+      <c r="C249" s="24" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="D249" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Výztuž B500B vkládaná do tvárnic ztraceného bednění — patky horní (6 sloupků) + </t>
+        </is>
+      </c>
+      <c r="E249" s="24" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
+      <c r="F249" s="24" t="inlineStr"/>
+      <c r="G249" s="24" t="inlineStr">
+        <is>
+          <t>271313</t>
+        </is>
+      </c>
+      <c r="H249" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I249" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J249" s="32" t="inlineStr"/>
+      <c r="K249" s="24" t="inlineStr"/>
+      <c r="L249" s="24" t="inlineStr">
+        <is>
+          <t>273313811</t>
+        </is>
+      </c>
+      <c r="M249" s="24" t="inlineStr"/>
+      <c r="N249" s="24" t="inlineStr">
+        <is>
+          <t>WebSearch verified WRONG LEAF: URS leaf = ZÁKLADY DESKY C 25/30, item = ZÁKLADOVÉ PASY C16/20 XC0. Hint: Základové pasy = TKP 271 (pasy), NOT 273 (desky); class C16/20 leaf needed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
